--- a/data/mosfet_data.xlsx
+++ b/data/mosfet_data.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://renesasgroup-my.sharepoint.com/personal/gary_kidwell_wz_renesas_com/Documents/python/charger/mathmodels/pdis_2or3lvl_bb/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="529" documentId="13_ncr:1_{B6E73BC3-DAD1-4207-9F29-342E0D899D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C203AE90-BADD-4D73-AA29-BD809D3D7C35}"/>
+  <xr:revisionPtr revIDLastSave="663" documentId="13_ncr:1_{B6E73BC3-DAD1-4207-9F29-342E0D899D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFAAD25C-EA45-4727-9926-51328176FE62}"/>
   <bookViews>
-    <workbookView xWindow="3570" yWindow="3225" windowWidth="21600" windowHeight="11385" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="column_data_old" sheetId="1" r:id="rId1"/>
     <sheet name="transpose" sheetId="5" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">transpose!$A$4:$Z$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">transpose!$A$4:$AA$51</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="120">
   <si>
     <t>description</t>
   </si>
@@ -391,6 +391,18 @@
   </si>
   <si>
     <t>RBE023N04</t>
+  </si>
+  <si>
+    <t>AONP38324U_HS</t>
+  </si>
+  <si>
+    <t>AONP38324U_LS</t>
+  </si>
+  <si>
+    <t>RthJA</t>
+  </si>
+  <si>
+    <t>degC/W</t>
   </si>
 </sst>
 </file>
@@ -4219,30 +4231,29 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E69B3F4A-D7AE-43B6-8CEC-20724C077B7B}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:Z49"/>
+  <dimension ref="A1:AA51"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" customWidth="1"/>
-    <col min="4" max="5" width="15.5703125" customWidth="1"/>
-    <col min="6" max="6" width="16.5703125" customWidth="1"/>
-    <col min="10" max="10" width="15.85546875" customWidth="1"/>
-    <col min="11" max="11" width="10.140625" customWidth="1"/>
-    <col min="12" max="12" width="10.42578125" customWidth="1"/>
-    <col min="13" max="13" width="9.85546875" customWidth="1"/>
-    <col min="15" max="15" width="13.85546875" customWidth="1"/>
-    <col min="16" max="16" width="12.28515625" customWidth="1"/>
-    <col min="18" max="18" width="12.42578125" customWidth="1"/>
-    <col min="21" max="21" width="11.140625" customWidth="1"/>
-    <col min="23" max="23" width="11.140625" customWidth="1"/>
-    <col min="24" max="24" width="11.5703125" customWidth="1"/>
-    <col min="25" max="25" width="15.7109375" customWidth="1"/>
-    <col min="26" max="26" width="14" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" customWidth="1"/>
+    <col min="5" max="6" width="15.5703125" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" customWidth="1"/>
+    <col min="11" max="11" width="15.85546875" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" customWidth="1"/>
+    <col min="13" max="13" width="10.42578125" customWidth="1"/>
+    <col min="14" max="14" width="9.85546875" customWidth="1"/>
+    <col min="16" max="16" width="13.85546875" customWidth="1"/>
+    <col min="17" max="17" width="12.28515625" customWidth="1"/>
+    <col min="19" max="19" width="12.42578125" customWidth="1"/>
+    <col min="22" max="22" width="11.140625" customWidth="1"/>
+    <col min="24" max="24" width="11.140625" customWidth="1"/>
+    <col min="25" max="25" width="11.5703125" customWidth="1"/>
+    <col min="26" max="26" width="15.7109375" customWidth="1"/>
+    <col min="27" max="27" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -4250,79 +4261,82 @@
         <v>43</v>
       </c>
       <c r="C1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1" t="s">
         <v>53</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>56</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>59</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>62</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>64</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>67</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>69</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>71</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>73</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>75</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>77</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>79</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>81</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>84</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>86</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>88</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>90</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>93</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>96</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>98</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>101</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>104</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>106</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -4330,19 +4344,19 @@
         <v>44</v>
       </c>
       <c r="C2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D2" t="s">
         <v>54</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>57</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>60</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>57</v>
-      </c>
-      <c r="G2" t="s">
-        <v>65</v>
       </c>
       <c r="H2" t="s">
         <v>65</v>
@@ -4351,10 +4365,10 @@
         <v>65</v>
       </c>
       <c r="J2" t="s">
+        <v>65</v>
+      </c>
+      <c r="K2" t="s">
         <v>57</v>
-      </c>
-      <c r="K2" t="s">
-        <v>65</v>
       </c>
       <c r="L2" t="s">
         <v>65</v>
@@ -4363,66 +4377,69 @@
         <v>65</v>
       </c>
       <c r="N2" t="s">
+        <v>65</v>
+      </c>
+      <c r="O2" t="s">
         <v>60</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>82</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>57</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>60</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>57</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>91</v>
-      </c>
-      <c r="T2" t="s">
-        <v>94</v>
       </c>
       <c r="U2" t="s">
         <v>94</v>
       </c>
       <c r="V2" t="s">
+        <v>94</v>
+      </c>
+      <c r="W2" t="s">
         <v>99</v>
-      </c>
-      <c r="W2" t="s">
-        <v>102</v>
       </c>
       <c r="X2" t="s">
         <v>102</v>
       </c>
       <c r="Y2" t="s">
+        <v>102</v>
+      </c>
+      <c r="Z2" t="s">
         <v>57</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AA2" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1">
         <v>9.9999999999999995E-7</v>
       </c>
-      <c r="D3" s="1">
-        <v>1</v>
-      </c>
       <c r="E3" s="1">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1">
         <v>1.0000000000000001E-9</v>
       </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3" s="1">
-        <v>9.9999999999999998E-13</v>
+      <c r="G3">
+        <v>1</v>
       </c>
       <c r="H3" s="1">
         <v>9.9999999999999998E-13</v>
@@ -4430,11 +4447,11 @@
       <c r="I3" s="1">
         <v>9.9999999999999998E-13</v>
       </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3" s="1">
+      <c r="J3" s="1">
         <v>9.9999999999999998E-13</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
       </c>
       <c r="L3" s="1">
         <v>9.9999999999999998E-13</v>
@@ -4443,46 +4460,49 @@
         <v>9.9999999999999998E-13</v>
       </c>
       <c r="N3" s="1">
+        <v>9.9999999999999998E-13</v>
+      </c>
+      <c r="O3" s="1">
         <v>1.0000000000000001E-9</v>
       </c>
-      <c r="O3">
-        <v>1</v>
-      </c>
       <c r="P3">
         <v>1</v>
       </c>
-      <c r="Q3" s="1">
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3" s="1">
         <v>1.0000000000000001E-9</v>
       </c>
-      <c r="R3">
-        <v>1</v>
-      </c>
-      <c r="S3" s="1">
+      <c r="S3">
         <v>1</v>
       </c>
       <c r="T3" s="1">
-        <v>1E-3</v>
+        <v>1</v>
       </c>
       <c r="U3" s="1">
         <v>1E-3</v>
       </c>
-      <c r="V3">
-        <v>1</v>
-      </c>
-      <c r="W3" s="1">
-        <v>1.0000000000000001E-9</v>
+      <c r="V3" s="1">
+        <v>1E-3</v>
+      </c>
+      <c r="W3">
+        <v>1</v>
       </c>
       <c r="X3" s="1">
         <v>1.0000000000000001E-9</v>
       </c>
-      <c r="Y3">
-        <v>1</v>
+      <c r="Y3" s="1">
+        <v>1.0000000000000001E-9</v>
       </c>
       <c r="Z3">
         <v>1</v>
       </c>
+      <c r="AA3">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:26" ht="51" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" ht="51" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
         <v>0</v>
       </c>
@@ -4490,3690 +4510,3988 @@
         <v>43</v>
       </c>
       <c r="C4" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="D4" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="E4" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="F4" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="G4" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="H4" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="I4" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="J4" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="K4" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="K4" s="9" t="s">
+      <c r="L4" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="L4" s="9" t="s">
+      <c r="M4" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="M4" s="9" t="s">
+      <c r="N4" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="N4" s="9" t="s">
+      <c r="O4" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="O4" s="9" t="s">
+      <c r="P4" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="P4" s="9" t="s">
+      <c r="Q4" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="Q4" s="9" t="s">
+      <c r="R4" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="R4" s="9" t="s">
+      <c r="S4" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="S4" s="9" t="s">
+      <c r="T4" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="T4" s="9" t="s">
+      <c r="U4" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="U4" s="9" t="s">
+      <c r="V4" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="V4" s="9" t="s">
+      <c r="W4" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="W4" s="9" t="s">
+      <c r="X4" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="X4" s="9" t="s">
+      <c r="Y4" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="Y4" s="9" t="s">
+      <c r="Z4" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="Z4" s="9" t="s">
+      <c r="AA4" s="9" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="5" spans="1:26" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C5">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>11.56</v>
       </c>
       <c r="E5">
-        <v>2.5</v>
+        <v>30</v>
       </c>
       <c r="F5">
-        <v>10</v>
-      </c>
-      <c r="G5" s="2">
-        <v>1250</v>
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>10</v>
       </c>
       <c r="H5" s="2">
-        <v>1100</v>
+        <v>1700</v>
       </c>
       <c r="I5" s="2">
+        <v>1050</v>
+      </c>
+      <c r="J5" s="2">
         <v>200</v>
       </c>
-      <c r="J5" s="2">
-        <v>15</v>
-      </c>
       <c r="K5" s="2">
-        <v>1200</v>
+        <v>20</v>
       </c>
       <c r="L5" s="2">
-        <v>400</v>
+        <v>1500</v>
       </c>
       <c r="M5" s="2">
-        <v>62</v>
+        <v>300</v>
       </c>
       <c r="N5" s="2">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="O5" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P5" s="2">
-        <v>15</v>
-      </c>
-      <c r="Q5" s="6">
-        <v>3</v>
-      </c>
-      <c r="R5" s="2">
-        <v>15</v>
+        <v>20</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>15</v>
+      </c>
+      <c r="R5" s="6">
+        <v>2.2000000000000002</v>
       </c>
       <c r="S5" s="2">
-        <v>57</v>
-      </c>
-      <c r="T5" s="6">
+        <v>15</v>
+      </c>
+      <c r="T5" s="2">
+        <v>108</v>
+      </c>
+      <c r="U5" s="3">
+        <v>3.7</v>
+      </c>
+      <c r="V5" s="3">
+        <v>3.05</v>
+      </c>
+      <c r="W5" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="X5" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="Y5" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="Z5" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="AA5" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6">
+        <v>32</v>
+      </c>
+      <c r="D6">
+        <v>11.56</v>
+      </c>
+      <c r="E6">
+        <v>30</v>
+      </c>
+      <c r="F6">
+        <v>3.2</v>
+      </c>
+      <c r="G6">
+        <v>10</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1340</v>
+      </c>
+      <c r="I6" s="2">
+        <v>900</v>
+      </c>
+      <c r="J6" s="2">
+        <v>140</v>
+      </c>
+      <c r="K6" s="2">
+        <v>20</v>
+      </c>
+      <c r="L6" s="2">
+        <v>1210</v>
+      </c>
+      <c r="M6" s="2">
+        <v>240</v>
+      </c>
+      <c r="N6" s="2">
+        <v>30</v>
+      </c>
+      <c r="O6" s="2">
+        <v>15</v>
+      </c>
+      <c r="P6" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>15</v>
+      </c>
+      <c r="R6" s="6">
+        <v>1</v>
+      </c>
+      <c r="S6" s="2">
+        <v>15</v>
+      </c>
+      <c r="T6" s="2">
+        <v>125</v>
+      </c>
+      <c r="U6" s="6">
+        <v>4.7</v>
+      </c>
+      <c r="V6" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="W6" s="6">
+        <v>1.9</v>
+      </c>
+      <c r="X6" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="Y6" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="Z6" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="AA6" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7">
+        <v>32</v>
+      </c>
+      <c r="D7">
+        <v>11.56</v>
+      </c>
+      <c r="E7">
+        <v>30</v>
+      </c>
+      <c r="F7">
         <v>5.2</v>
       </c>
-      <c r="U5" s="6">
-        <v>3.5</v>
-      </c>
-      <c r="V5" s="6">
+      <c r="G7">
+        <v>10</v>
+      </c>
+      <c r="H7" s="2">
+        <v>2300</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1750</v>
+      </c>
+      <c r="J7" s="2">
+        <v>300</v>
+      </c>
+      <c r="K7" s="2">
+        <v>15</v>
+      </c>
+      <c r="L7" s="2">
+        <v>2050</v>
+      </c>
+      <c r="M7" s="2">
+        <v>500</v>
+      </c>
+      <c r="N7" s="2">
+        <v>50</v>
+      </c>
+      <c r="O7" s="2">
+        <v>32</v>
+      </c>
+      <c r="P7" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>15</v>
+      </c>
+      <c r="R7" s="6">
+        <v>2.1</v>
+      </c>
+      <c r="S7" s="2">
+        <v>15</v>
+      </c>
+      <c r="T7" s="2">
+        <v>135</v>
+      </c>
+      <c r="U7" s="6">
+        <v>2.4</v>
+      </c>
+      <c r="V7" s="6">
+        <v>2</v>
+      </c>
+      <c r="W7" s="6">
         <v>1.2</v>
-      </c>
-      <c r="W5" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="X5" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="Y5" s="6">
-        <v>0.7</v>
-      </c>
-      <c r="Z5" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6">
-        <v>45</v>
-      </c>
-      <c r="D6">
-        <v>30</v>
-      </c>
-      <c r="E6">
-        <v>5.5</v>
-      </c>
-      <c r="F6">
-        <v>10</v>
-      </c>
-      <c r="G6" s="2">
-        <v>2550</v>
-      </c>
-      <c r="H6" s="2">
-        <v>2000</v>
-      </c>
-      <c r="I6" s="2">
-        <v>400</v>
-      </c>
-      <c r="J6" s="2">
-        <v>15</v>
-      </c>
-      <c r="K6" s="2">
-        <v>2250</v>
-      </c>
-      <c r="L6" s="2">
-        <v>650</v>
-      </c>
-      <c r="M6" s="2">
-        <v>100</v>
-      </c>
-      <c r="N6" s="2">
-        <v>30</v>
-      </c>
-      <c r="O6" s="2">
-        <v>20</v>
-      </c>
-      <c r="P6" s="2">
-        <v>15</v>
-      </c>
-      <c r="Q6" s="6">
-        <v>4.5</v>
-      </c>
-      <c r="R6" s="2">
-        <v>15</v>
-      </c>
-      <c r="S6" s="2">
-        <v>110</v>
-      </c>
-      <c r="T6" s="6">
-        <v>2.6</v>
-      </c>
-      <c r="U6" s="6">
-        <v>1.5</v>
-      </c>
-      <c r="V6" s="6">
-        <v>1.4</v>
-      </c>
-      <c r="W6" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="X6" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="Y6" s="6">
-        <v>0.7</v>
-      </c>
-      <c r="Z6" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7">
-        <v>45</v>
-      </c>
-      <c r="D7">
-        <v>30</v>
-      </c>
-      <c r="E7">
-        <v>4.5</v>
-      </c>
-      <c r="F7">
-        <v>10</v>
-      </c>
-      <c r="G7" s="2">
-        <v>2200</v>
-      </c>
-      <c r="H7" s="2">
-        <v>1300</v>
-      </c>
-      <c r="I7" s="2">
-        <v>300</v>
-      </c>
-      <c r="J7" s="2">
-        <v>15</v>
-      </c>
-      <c r="K7" s="2">
-        <v>1900</v>
-      </c>
-      <c r="L7" s="2">
-        <v>400</v>
-      </c>
-      <c r="M7" s="2">
-        <v>50</v>
-      </c>
-      <c r="N7" s="2">
-        <v>21.5</v>
-      </c>
-      <c r="O7" s="2">
-        <v>20</v>
-      </c>
-      <c r="P7" s="2">
-        <v>15</v>
-      </c>
-      <c r="Q7" s="6">
-        <v>3.6</v>
-      </c>
-      <c r="R7" s="2">
-        <v>15</v>
-      </c>
-      <c r="S7" s="2">
-        <v>165</v>
-      </c>
-      <c r="T7" s="10">
-        <v>2.8</v>
-      </c>
-      <c r="U7" s="10">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="V7" s="6">
-        <v>1.8</v>
-      </c>
-      <c r="W7" s="6">
-        <v>0.8</v>
       </c>
       <c r="X7" s="6">
         <v>0.8</v>
       </c>
-      <c r="Y7" s="3">
-        <v>0.68</v>
+      <c r="Y7" s="6">
+        <v>0.8</v>
       </c>
       <c r="Z7" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="AA7" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:26" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>117</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C8">
+        <v>32</v>
+      </c>
+      <c r="D8">
         <v>11.56</v>
       </c>
-      <c r="D8">
-        <v>30</v>
-      </c>
       <c r="E8">
-        <v>8.5</v>
+        <v>30</v>
       </c>
       <c r="F8">
-        <v>10</v>
-      </c>
-      <c r="G8" s="2">
-        <v>3200</v>
+        <v>5.5</v>
+      </c>
+      <c r="G8">
+        <v>10</v>
       </c>
       <c r="H8" s="2">
-        <v>2500</v>
+        <v>2300</v>
       </c>
       <c r="I8" s="2">
-        <v>500</v>
+        <v>1600</v>
       </c>
       <c r="J8" s="2">
+        <v>275</v>
+      </c>
+      <c r="K8" s="2">
+        <v>15</v>
+      </c>
+      <c r="L8" s="2">
+        <v>1950</v>
+      </c>
+      <c r="M8" s="2">
+        <v>475</v>
+      </c>
+      <c r="N8" s="2">
+        <v>50</v>
+      </c>
+      <c r="O8" s="2">
+        <v>24</v>
+      </c>
+      <c r="P8" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>15</v>
+      </c>
+      <c r="R8" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="S8" s="2">
+        <v>15</v>
+      </c>
+      <c r="T8" s="2">
+        <v>150</v>
+      </c>
+      <c r="U8" s="6">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="V8" s="6">
+        <v>1.9</v>
+      </c>
+      <c r="W8" s="6">
+        <v>1.2</v>
+      </c>
+      <c r="X8" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="Y8" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="Z8" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="AA8" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9">
         <v>25</v>
       </c>
-      <c r="K8" s="2">
-        <v>2800</v>
-      </c>
-      <c r="L8" s="2">
-        <v>600</v>
-      </c>
-      <c r="M8" s="2">
-        <v>50</v>
-      </c>
-      <c r="N8" s="2">
-        <v>36.5</v>
-      </c>
-      <c r="O8" s="2">
-        <v>20</v>
-      </c>
-      <c r="P8" s="2">
-        <v>15</v>
-      </c>
-      <c r="Q8" s="6">
-        <v>4</v>
-      </c>
-      <c r="R8" s="2">
-        <v>15</v>
-      </c>
-      <c r="S8" s="2">
-        <v>125</v>
-      </c>
-      <c r="T8" s="6">
-        <v>2.4500000000000002</v>
-      </c>
-      <c r="U8" s="6">
-        <v>1.55</v>
-      </c>
-      <c r="V8" s="6">
+      <c r="D9">
+        <v>45</v>
+      </c>
+      <c r="E9">
+        <v>30</v>
+      </c>
+      <c r="F9">
+        <v>5.5</v>
+      </c>
+      <c r="G9">
+        <v>10</v>
+      </c>
+      <c r="H9" s="2">
+        <v>2550</v>
+      </c>
+      <c r="I9" s="2">
+        <v>2000</v>
+      </c>
+      <c r="J9" s="2">
+        <v>400</v>
+      </c>
+      <c r="K9" s="2">
+        <v>15</v>
+      </c>
+      <c r="L9" s="2">
+        <v>2250</v>
+      </c>
+      <c r="M9" s="2">
+        <v>650</v>
+      </c>
+      <c r="N9" s="2">
+        <v>100</v>
+      </c>
+      <c r="O9" s="2">
+        <v>30</v>
+      </c>
+      <c r="P9" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>15</v>
+      </c>
+      <c r="R9" s="6">
+        <v>4.5</v>
+      </c>
+      <c r="S9" s="2">
+        <v>15</v>
+      </c>
+      <c r="T9" s="2">
+        <v>110</v>
+      </c>
+      <c r="U9" s="6">
+        <v>2.6</v>
+      </c>
+      <c r="V9" s="6">
+        <v>1.5</v>
+      </c>
+      <c r="W9" s="6">
+        <v>1.4</v>
+      </c>
+      <c r="X9" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Y9" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="Z9" s="6">
         <v>0.7</v>
       </c>
-      <c r="W8" s="6">
+      <c r="AA9" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10">
+        <v>25</v>
+      </c>
+      <c r="D10">
+        <v>45</v>
+      </c>
+      <c r="E10">
+        <v>30</v>
+      </c>
+      <c r="F10">
+        <v>2.5</v>
+      </c>
+      <c r="G10">
+        <v>10</v>
+      </c>
+      <c r="H10" s="2">
+        <v>1250</v>
+      </c>
+      <c r="I10" s="2">
+        <v>1100</v>
+      </c>
+      <c r="J10" s="2">
+        <v>200</v>
+      </c>
+      <c r="K10" s="2">
+        <v>15</v>
+      </c>
+      <c r="L10" s="2">
+        <v>1200</v>
+      </c>
+      <c r="M10" s="2">
+        <v>400</v>
+      </c>
+      <c r="N10" s="2">
+        <v>62</v>
+      </c>
+      <c r="O10" s="2">
+        <v>20</v>
+      </c>
+      <c r="P10" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>15</v>
+      </c>
+      <c r="R10" s="6">
+        <v>3</v>
+      </c>
+      <c r="S10" s="2">
+        <v>15</v>
+      </c>
+      <c r="T10" s="2">
+        <v>57</v>
+      </c>
+      <c r="U10" s="6">
+        <v>5.2</v>
+      </c>
+      <c r="V10" s="6">
+        <v>3.5</v>
+      </c>
+      <c r="W10" s="6">
+        <v>1.2</v>
+      </c>
+      <c r="X10" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="Y10" s="6">
         <v>0.5</v>
       </c>
-      <c r="X8" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="Y8" s="6">
-        <v>0.68</v>
-      </c>
-      <c r="Z8" s="6">
+      <c r="Z10" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="AA10" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:26" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9">
-        <v>11.56</v>
-      </c>
-      <c r="D9">
-        <v>30</v>
-      </c>
-      <c r="E9">
-        <v>4</v>
-      </c>
-      <c r="F9">
-        <v>10</v>
-      </c>
-      <c r="G9" s="2">
-        <v>1700</v>
-      </c>
-      <c r="H9" s="2">
-        <v>1050</v>
-      </c>
-      <c r="I9" s="2">
-        <v>200</v>
-      </c>
-      <c r="J9" s="2">
-        <v>20</v>
-      </c>
-      <c r="K9" s="2">
-        <v>1500</v>
-      </c>
-      <c r="L9" s="2">
-        <v>300</v>
-      </c>
-      <c r="M9" s="2">
-        <v>50</v>
-      </c>
-      <c r="N9" s="2">
-        <v>21</v>
-      </c>
-      <c r="O9" s="2">
-        <v>20</v>
-      </c>
-      <c r="P9" s="2">
-        <v>15</v>
-      </c>
-      <c r="Q9" s="6">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="R9" s="2">
-        <v>15</v>
-      </c>
-      <c r="S9" s="2">
-        <v>108</v>
-      </c>
-      <c r="T9" s="3">
-        <v>3.7</v>
-      </c>
-      <c r="U9" s="3">
-        <v>3.05</v>
-      </c>
-      <c r="V9" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="W9" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="X9" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="Y9" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="Z9" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" t="s">
-        <v>50</v>
-      </c>
-      <c r="C10">
-        <v>11.56</v>
-      </c>
-      <c r="D10">
-        <v>30</v>
-      </c>
-      <c r="E10">
-        <v>3.2</v>
-      </c>
-      <c r="F10">
-        <v>10</v>
-      </c>
-      <c r="G10" s="2">
-        <v>1340</v>
-      </c>
-      <c r="H10" s="2">
-        <v>900</v>
-      </c>
-      <c r="I10" s="2">
-        <v>140</v>
-      </c>
-      <c r="J10" s="2">
-        <v>20</v>
-      </c>
-      <c r="K10" s="2">
-        <v>1210</v>
-      </c>
-      <c r="L10" s="2">
-        <v>240</v>
-      </c>
-      <c r="M10" s="2">
-        <v>30</v>
-      </c>
-      <c r="N10" s="2">
-        <v>15</v>
-      </c>
-      <c r="O10" s="2">
-        <v>20</v>
-      </c>
-      <c r="P10" s="2">
-        <v>15</v>
-      </c>
-      <c r="Q10" s="6">
-        <v>1</v>
-      </c>
-      <c r="R10" s="2">
-        <v>15</v>
-      </c>
-      <c r="S10" s="2">
-        <v>125</v>
-      </c>
-      <c r="T10" s="6">
-        <v>4.7</v>
-      </c>
-      <c r="U10" s="6">
-        <v>3.9</v>
-      </c>
-      <c r="V10" s="6">
-        <v>1.9</v>
-      </c>
-      <c r="W10" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="X10" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="Z10" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
         <v>46</v>
       </c>
       <c r="C11">
+        <v>30</v>
+      </c>
+      <c r="D11">
         <v>11.56</v>
       </c>
-      <c r="D11">
-        <v>30</v>
-      </c>
       <c r="E11">
-        <v>3.6</v>
+        <v>30</v>
       </c>
       <c r="F11">
-        <v>10</v>
-      </c>
-      <c r="G11" s="2">
-        <v>1450</v>
+        <v>11.3</v>
+      </c>
+      <c r="G11">
+        <v>4.5</v>
       </c>
       <c r="H11" s="2">
-        <v>1100</v>
+        <v>4000</v>
       </c>
       <c r="I11" s="2">
-        <v>200</v>
+        <v>3000</v>
       </c>
       <c r="J11" s="2">
-        <v>25</v>
+        <v>500</v>
       </c>
       <c r="K11" s="2">
-        <v>1300</v>
+        <v>12</v>
       </c>
       <c r="L11" s="2">
-        <v>250</v>
+        <v>3500</v>
       </c>
       <c r="M11" s="2">
-        <v>30</v>
+        <v>1400</v>
       </c>
       <c r="N11" s="2">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="O11" s="2">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="P11" s="2">
-        <v>15</v>
-      </c>
-      <c r="Q11" s="6">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="R11" s="2">
-        <v>15</v>
-      </c>
-      <c r="S11" s="2">
-        <v>77</v>
-      </c>
-      <c r="T11" s="6">
-        <v>6</v>
-      </c>
-      <c r="U11" s="6">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="V11" s="6">
-        <v>1.7</v>
-      </c>
-      <c r="W11" s="6">
+        <v>10</v>
+      </c>
+      <c r="Q11">
+        <v>15</v>
+      </c>
+      <c r="R11">
+        <v>3</v>
+      </c>
+      <c r="S11">
+        <v>15</v>
+      </c>
+      <c r="T11">
+        <v>117</v>
+      </c>
+      <c r="U11">
+        <v>1.25</v>
+      </c>
+      <c r="V11">
+        <v>0.88</v>
+      </c>
+      <c r="W11">
+        <v>0.75</v>
+      </c>
+      <c r="X11" s="3">
         <v>0.8</v>
       </c>
-      <c r="X11" s="6">
+      <c r="Y11" s="3">
         <v>0.8</v>
       </c>
-      <c r="Y11" s="6">
-        <v>0.7</v>
-      </c>
-      <c r="Z11" s="6">
-        <v>1</v>
+      <c r="Z11">
+        <v>0.73</v>
+      </c>
+      <c r="AA11">
+        <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:26" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="B12" t="s">
         <v>46</v>
       </c>
       <c r="C12">
+        <v>30</v>
+      </c>
+      <c r="D12">
+        <v>11.56</v>
+      </c>
+      <c r="E12">
+        <v>30</v>
+      </c>
+      <c r="F12">
+        <v>9.6</v>
+      </c>
+      <c r="G12">
+        <v>4.5</v>
+      </c>
+      <c r="H12" s="2">
+        <v>3000</v>
+      </c>
+      <c r="I12" s="2">
+        <v>3000</v>
+      </c>
+      <c r="J12" s="2">
+        <v>500</v>
+      </c>
+      <c r="K12" s="2">
+        <v>12</v>
+      </c>
+      <c r="L12" s="2">
+        <v>2975</v>
+      </c>
+      <c r="M12" s="2">
+        <v>1200</v>
+      </c>
+      <c r="N12" s="2">
+        <v>200</v>
+      </c>
+      <c r="O12" s="2">
+        <v>25</v>
+      </c>
+      <c r="P12" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q12">
+        <v>15</v>
+      </c>
+      <c r="R12">
+        <v>3.9</v>
+      </c>
+      <c r="S12">
+        <v>15</v>
+      </c>
+      <c r="T12">
+        <v>95</v>
+      </c>
+      <c r="U12">
+        <v>1.5</v>
+      </c>
+      <c r="V12">
+        <v>0.95</v>
+      </c>
+      <c r="W12">
+        <v>0.42</v>
+      </c>
+      <c r="X12" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="Y12" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="Z12">
+        <v>0.73</v>
+      </c>
+      <c r="AA12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13">
+        <v>30</v>
+      </c>
+      <c r="D13">
+        <v>11.56</v>
+      </c>
+      <c r="E13">
+        <v>30</v>
+      </c>
+      <c r="F13">
+        <v>11.2</v>
+      </c>
+      <c r="G13">
+        <v>4.5</v>
+      </c>
+      <c r="H13" s="2">
+        <v>4000</v>
+      </c>
+      <c r="I13" s="2">
+        <v>4000</v>
+      </c>
+      <c r="J13" s="2">
+        <v>550</v>
+      </c>
+      <c r="K13" s="2">
+        <v>15</v>
+      </c>
+      <c r="L13" s="2">
+        <v>3700</v>
+      </c>
+      <c r="M13" s="2">
+        <v>1800</v>
+      </c>
+      <c r="N13" s="2">
+        <v>160</v>
+      </c>
+      <c r="O13" s="2">
+        <v>45</v>
+      </c>
+      <c r="P13" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>15</v>
+      </c>
+      <c r="R13" s="2">
+        <v>5.8</v>
+      </c>
+      <c r="S13" s="2">
+        <v>15</v>
+      </c>
+      <c r="T13" s="2">
+        <v>84</v>
+      </c>
+      <c r="U13" s="3">
+        <v>1.75</v>
+      </c>
+      <c r="V13" s="3">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="W13" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="X13" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="Z13" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="AA13" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14">
+        <v>30</v>
+      </c>
+      <c r="D14">
+        <v>11.56</v>
+      </c>
+      <c r="E14">
+        <v>30</v>
+      </c>
+      <c r="F14">
+        <v>8.5</v>
+      </c>
+      <c r="G14">
+        <v>10</v>
+      </c>
+      <c r="H14" s="2">
+        <v>3200</v>
+      </c>
+      <c r="I14" s="2">
+        <v>2500</v>
+      </c>
+      <c r="J14" s="2">
+        <v>500</v>
+      </c>
+      <c r="K14" s="2">
+        <v>25</v>
+      </c>
+      <c r="L14" s="2">
+        <v>2800</v>
+      </c>
+      <c r="M14" s="2">
+        <v>600</v>
+      </c>
+      <c r="N14" s="2">
+        <v>50</v>
+      </c>
+      <c r="O14" s="2">
+        <v>36.5</v>
+      </c>
+      <c r="P14" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>15</v>
+      </c>
+      <c r="R14" s="6">
+        <v>4</v>
+      </c>
+      <c r="S14" s="2">
+        <v>15</v>
+      </c>
+      <c r="T14" s="2">
+        <v>125</v>
+      </c>
+      <c r="U14" s="6">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="V14" s="6">
+        <v>1.55</v>
+      </c>
+      <c r="W14" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="X14" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Y14" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Z14" s="6">
+        <v>0.68</v>
+      </c>
+      <c r="AA14" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15">
+        <v>30</v>
+      </c>
+      <c r="D15">
         <f>3.4*3.4</f>
         <v>11.559999999999999</v>
       </c>
-      <c r="D12">
+      <c r="E15">
         <v>80</v>
       </c>
-      <c r="E12">
+      <c r="F15">
         <v>7.5</v>
       </c>
-      <c r="F12">
-        <v>10</v>
-      </c>
-      <c r="G12">
+      <c r="G15">
+        <v>10</v>
+      </c>
+      <c r="H15">
         <v>2750</v>
       </c>
-      <c r="H12">
+      <c r="I15">
         <v>1700</v>
       </c>
-      <c r="I12">
+      <c r="J15">
         <v>200</v>
       </c>
-      <c r="J12">
+      <c r="K15">
         <v>40</v>
       </c>
-      <c r="K12">
+      <c r="L15">
         <v>2400</v>
       </c>
-      <c r="L12">
+      <c r="M15">
         <v>250</v>
       </c>
-      <c r="M12">
-        <v>10</v>
-      </c>
-      <c r="N12">
+      <c r="N15">
+        <v>10</v>
+      </c>
+      <c r="O15">
         <v>100</v>
       </c>
-      <c r="O12">
+      <c r="P15">
         <v>18</v>
       </c>
-      <c r="P12">
+      <c r="Q15">
         <v>40</v>
       </c>
-      <c r="Q12">
+      <c r="R15">
         <v>4</v>
       </c>
-      <c r="R12">
+      <c r="S15">
         <v>40</v>
       </c>
-      <c r="S12">
+      <c r="T15">
         <v>54</v>
       </c>
-      <c r="T12">
+      <c r="U15">
         <v>5.5</v>
       </c>
-      <c r="U12">
+      <c r="V15">
         <v>5.5</v>
       </c>
-      <c r="V12">
+      <c r="W15">
         <v>1.35</v>
       </c>
-      <c r="W12">
+      <c r="X15">
         <v>0.5</v>
       </c>
-      <c r="X12">
+      <c r="Y15">
         <v>0.5</v>
       </c>
-      <c r="Y12">
+      <c r="Z15">
         <v>0.7</v>
       </c>
-      <c r="Z12">
+      <c r="AA15">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:26" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
         <v>21</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B16" t="s">
         <v>46</v>
       </c>
-      <c r="C13">
+      <c r="C16">
+        <v>30</v>
+      </c>
+      <c r="D16">
         <v>11.56</v>
       </c>
-      <c r="D13">
+      <c r="E16">
         <v>40</v>
       </c>
-      <c r="E13" s="7">
+      <c r="F16" s="7">
         <v>2.75</v>
       </c>
-      <c r="F13" s="7">
+      <c r="G16" s="7">
         <v>4.5</v>
       </c>
-      <c r="G13" s="2">
+      <c r="H16" s="2">
         <v>1550</v>
       </c>
-      <c r="H13" s="2">
+      <c r="I16" s="2">
         <v>1000</v>
       </c>
-      <c r="I13" s="2">
+      <c r="J16" s="2">
         <v>100</v>
       </c>
-      <c r="J13" s="2">
-        <v>30</v>
-      </c>
-      <c r="K13" s="2">
+      <c r="K16" s="2">
+        <v>30</v>
+      </c>
+      <c r="L16" s="2">
         <v>1450</v>
       </c>
-      <c r="L13" s="2">
+      <c r="M16" s="2">
         <v>200</v>
-      </c>
-      <c r="M13" s="2">
-        <v>13</v>
-      </c>
-      <c r="N13" s="2">
-        <v>21</v>
-      </c>
-      <c r="O13" s="2">
-        <v>20</v>
-      </c>
-      <c r="P13" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q13" s="6">
-        <v>3</v>
-      </c>
-      <c r="R13" s="2">
-        <v>20</v>
-      </c>
-      <c r="S13" s="2">
-        <v>70</v>
-      </c>
-      <c r="T13" s="6">
-        <v>7.4</v>
-      </c>
-      <c r="U13" s="6">
-        <v>5</v>
-      </c>
-      <c r="V13" s="6">
-        <v>1.8</v>
-      </c>
-      <c r="W13" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="X13" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="Y13" s="6">
-        <v>0.7</v>
-      </c>
-      <c r="Z13" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14">
-        <v>45</v>
-      </c>
-      <c r="D14">
-        <v>30</v>
-      </c>
-      <c r="E14">
-        <v>19</v>
-      </c>
-      <c r="F14">
-        <v>4.5</v>
-      </c>
-      <c r="G14" s="2">
-        <v>8500</v>
-      </c>
-      <c r="H14" s="2">
-        <v>6000</v>
-      </c>
-      <c r="I14" s="2">
-        <v>1000</v>
-      </c>
-      <c r="J14" s="2">
-        <v>24</v>
-      </c>
-      <c r="K14" s="2">
-        <v>7500</v>
-      </c>
-      <c r="L14" s="2">
-        <v>1400</v>
-      </c>
-      <c r="M14" s="2">
-        <v>75</v>
-      </c>
-      <c r="N14" s="2">
-        <v>20</v>
-      </c>
-      <c r="O14" s="2">
-        <v>87</v>
-      </c>
-      <c r="P14" s="2">
-        <v>15</v>
-      </c>
-      <c r="Q14" s="2">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="R14" s="2">
-        <v>15</v>
-      </c>
-      <c r="S14" s="2">
-        <v>120</v>
-      </c>
-      <c r="T14" s="3">
-        <v>2</v>
-      </c>
-      <c r="U14" s="3">
-        <v>1.7</v>
-      </c>
-      <c r="V14" s="3">
-        <v>1.9</v>
-      </c>
-      <c r="W14" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="X14" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>0.81</v>
-      </c>
-      <c r="Z14" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15" t="s">
-        <v>47</v>
-      </c>
-      <c r="C15">
-        <v>45</v>
-      </c>
-      <c r="D15">
-        <v>60</v>
-      </c>
-      <c r="E15">
-        <v>10</v>
-      </c>
-      <c r="F15">
-        <v>10</v>
-      </c>
-      <c r="G15" s="2">
-        <v>4000</v>
-      </c>
-      <c r="H15" s="2">
-        <v>3000</v>
-      </c>
-      <c r="I15" s="2">
-        <v>700</v>
-      </c>
-      <c r="J15" s="2">
-        <v>25</v>
-      </c>
-      <c r="K15" s="2">
-        <v>3300</v>
-      </c>
-      <c r="L15" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M15" s="2">
-        <v>50</v>
-      </c>
-      <c r="N15" s="2">
-        <v>73</v>
-      </c>
-      <c r="O15" s="2">
-        <v>20</v>
-      </c>
-      <c r="P15" s="2">
-        <v>30</v>
-      </c>
-      <c r="Q15" s="6">
-        <v>8.5</v>
-      </c>
-      <c r="R15" s="2">
-        <v>30</v>
-      </c>
-      <c r="S15" s="2">
-        <v>100</v>
-      </c>
-      <c r="T15" s="6">
-        <v>3.1</v>
-      </c>
-      <c r="U15" s="6">
-        <v>2.4</v>
-      </c>
-      <c r="V15" s="6">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="W15" s="6">
-        <v>0.75</v>
-      </c>
-      <c r="X15" s="6">
-        <v>0.75</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>0.69</v>
-      </c>
-      <c r="Z15" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16">
-        <v>45</v>
-      </c>
-      <c r="D16">
-        <v>30</v>
-      </c>
-      <c r="E16">
-        <v>4.5</v>
-      </c>
-      <c r="F16">
-        <v>4.5</v>
-      </c>
-      <c r="G16" s="2">
-        <v>1600</v>
-      </c>
-      <c r="H16" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I16" s="2">
-        <v>200</v>
-      </c>
-      <c r="J16" s="2">
-        <v>15</v>
-      </c>
-      <c r="K16" s="2">
-        <v>1500</v>
-      </c>
-      <c r="L16" s="2">
-        <v>520</v>
-      </c>
-      <c r="M16" s="2">
-        <v>38</v>
       </c>
       <c r="N16" s="2">
         <v>13</v>
       </c>
       <c r="O16" s="2">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="P16" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Q16" s="2">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="R16" s="2">
-        <v>15</v>
+        <v>20</v>
+      </c>
+      <c r="R16" s="6">
+        <v>3</v>
       </c>
       <c r="S16" s="2">
+        <v>20</v>
+      </c>
+      <c r="T16" s="2">
+        <v>70</v>
+      </c>
+      <c r="U16" s="6">
+        <v>7.4</v>
+      </c>
+      <c r="V16" s="6">
+        <v>5</v>
+      </c>
+      <c r="W16" s="6">
+        <v>1.8</v>
+      </c>
+      <c r="X16" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Y16" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Z16" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="AA16" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17">
+        <v>30</v>
+      </c>
+      <c r="D17">
+        <v>11.56</v>
+      </c>
+      <c r="E17">
+        <v>30</v>
+      </c>
+      <c r="F17">
+        <v>4.2</v>
+      </c>
+      <c r="G17">
+        <v>4.5</v>
+      </c>
+      <c r="H17" s="2">
+        <v>1700</v>
+      </c>
+      <c r="I17" s="2">
+        <v>1600</v>
+      </c>
+      <c r="J17" s="2">
+        <v>250</v>
+      </c>
+      <c r="K17" s="2">
+        <v>15</v>
+      </c>
+      <c r="L17" s="2">
+        <v>1550</v>
+      </c>
+      <c r="M17" s="2">
+        <v>550</v>
+      </c>
+      <c r="N17" s="2">
+        <v>60</v>
+      </c>
+      <c r="O17" s="2">
+        <v>37</v>
+      </c>
+      <c r="P17" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>15</v>
+      </c>
+      <c r="R17" s="2">
+        <v>2.6</v>
+      </c>
+      <c r="S17" s="2">
+        <v>15</v>
+      </c>
+      <c r="T17" s="2">
+        <v>67</v>
+      </c>
+      <c r="U17" s="3">
+        <v>4.8</v>
+      </c>
+      <c r="V17" s="3">
+        <v>2.7</v>
+      </c>
+      <c r="W17" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="X17" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="Y17" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="Z17" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="AA17" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18">
+        <v>30</v>
+      </c>
+      <c r="D18">
+        <v>11.56</v>
+      </c>
+      <c r="E18">
+        <v>40</v>
+      </c>
+      <c r="F18">
+        <v>4.7</v>
+      </c>
+      <c r="G18">
+        <v>10</v>
+      </c>
+      <c r="H18">
+        <v>2000</v>
+      </c>
+      <c r="I18">
+        <v>2500</v>
+      </c>
+      <c r="J18">
+        <v>360</v>
+      </c>
+      <c r="K18">
+        <v>25</v>
+      </c>
+      <c r="L18">
+        <v>1800</v>
+      </c>
+      <c r="M18">
+        <v>500</v>
+      </c>
+      <c r="N18">
+        <v>17</v>
+      </c>
+      <c r="O18">
+        <v>44</v>
+      </c>
+      <c r="P18">
+        <v>20</v>
+      </c>
+      <c r="Q18">
+        <v>20</v>
+      </c>
+      <c r="R18">
+        <v>3.2</v>
+      </c>
+      <c r="S18">
+        <v>20</v>
+      </c>
+      <c r="T18">
+        <v>100</v>
+      </c>
+      <c r="U18">
+        <v>2.8</v>
+      </c>
+      <c r="V18">
+        <v>2.1</v>
+      </c>
+      <c r="W18">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="X18">
+        <v>0.5</v>
+      </c>
+      <c r="Y18">
+        <v>0.5</v>
+      </c>
+      <c r="Z18">
+        <v>0.79</v>
+      </c>
+      <c r="AA18">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19">
+        <v>30</v>
+      </c>
+      <c r="D19">
+        <v>11.56</v>
+      </c>
+      <c r="E19">
+        <v>40</v>
+      </c>
+      <c r="F19">
+        <v>0.9</v>
+      </c>
+      <c r="G19">
+        <v>4.5</v>
+      </c>
+      <c r="H19">
+        <v>760</v>
+      </c>
+      <c r="I19">
+        <v>900</v>
+      </c>
+      <c r="J19">
+        <v>100</v>
+      </c>
+      <c r="K19">
+        <v>25</v>
+      </c>
+      <c r="L19">
+        <v>650</v>
+      </c>
+      <c r="M19">
+        <v>95</v>
+      </c>
+      <c r="N19">
+        <v>11</v>
+      </c>
+      <c r="O19">
+        <v>21</v>
+      </c>
+      <c r="P19">
+        <v>20</v>
+      </c>
+      <c r="Q19">
+        <v>20</v>
+      </c>
+      <c r="R19">
+        <v>0.65</v>
+      </c>
+      <c r="S19">
+        <v>20</v>
+      </c>
+      <c r="T19">
+        <v>64</v>
+      </c>
+      <c r="U19">
+        <v>7</v>
+      </c>
+      <c r="V19">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="W19">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="X19">
+        <v>1</v>
+      </c>
+      <c r="Y19">
+        <v>1</v>
+      </c>
+      <c r="Z19">
+        <v>0.85</v>
+      </c>
+      <c r="AA19">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>5</v>
+      </c>
+      <c r="B20" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20">
+        <v>30</v>
+      </c>
+      <c r="D20">
+        <f>3.4*3.4</f>
+        <v>11.559999999999999</v>
+      </c>
+      <c r="E20">
         <v>80</v>
       </c>
-      <c r="T16" s="6">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="U16" s="6">
-        <v>2.8</v>
-      </c>
-      <c r="V16" s="3">
-        <v>1.4</v>
-      </c>
-      <c r="W16" s="6">
-        <v>1</v>
-      </c>
-      <c r="X16" s="6">
-        <v>1</v>
-      </c>
-      <c r="Y16" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="Z16" s="6">
-        <v>10</v>
+      <c r="F20">
+        <v>5</v>
+      </c>
+      <c r="G20">
+        <v>4.5</v>
+      </c>
+      <c r="H20">
+        <v>2100</v>
+      </c>
+      <c r="I20">
+        <v>1200</v>
+      </c>
+      <c r="J20">
+        <v>300</v>
+      </c>
+      <c r="K20">
+        <v>40</v>
+      </c>
+      <c r="L20">
+        <v>1900</v>
+      </c>
+      <c r="M20">
+        <v>280</v>
+      </c>
+      <c r="N20">
+        <v>12</v>
+      </c>
+      <c r="O20">
+        <v>27</v>
+      </c>
+      <c r="P20">
+        <v>20</v>
+      </c>
+      <c r="Q20">
+        <v>40</v>
+      </c>
+      <c r="R20">
+        <v>4</v>
+      </c>
+      <c r="S20">
+        <v>40</v>
+      </c>
+      <c r="T20">
+        <v>52</v>
+      </c>
+      <c r="U20">
+        <v>7.4</v>
+      </c>
+      <c r="V20">
+        <v>5.9</v>
+      </c>
+      <c r="W20">
+        <v>1.3</v>
+      </c>
+      <c r="X20">
+        <v>0.5</v>
+      </c>
+      <c r="Y20">
+        <v>0.5</v>
+      </c>
+      <c r="Z20">
+        <v>0.85</v>
+      </c>
+      <c r="AA20">
+        <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>113</v>
-      </c>
-      <c r="B17" t="s">
-        <v>47</v>
-      </c>
-      <c r="C17">
-        <v>45</v>
-      </c>
-      <c r="D17">
-        <v>30</v>
-      </c>
-      <c r="E17">
-        <v>11.4</v>
-      </c>
-      <c r="F17">
-        <v>4.5</v>
-      </c>
-      <c r="G17" s="2">
-        <v>4600</v>
-      </c>
-      <c r="H17" s="2">
-        <v>5500</v>
-      </c>
-      <c r="I17" s="2">
-        <v>250</v>
-      </c>
-      <c r="J17" s="2">
-        <v>15</v>
-      </c>
-      <c r="K17" s="2">
-        <v>4200</v>
-      </c>
-      <c r="L17" s="2">
-        <v>1800</v>
-      </c>
-      <c r="M17" s="2">
-        <v>68</v>
-      </c>
-      <c r="N17" s="2">
-        <v>45</v>
-      </c>
-      <c r="O17" s="2">
-        <v>10</v>
-      </c>
-      <c r="P17" s="2">
-        <v>15</v>
-      </c>
-      <c r="Q17" s="6">
-        <v>2.4</v>
-      </c>
-      <c r="R17" s="2">
-        <v>15</v>
-      </c>
-      <c r="S17" s="2">
-        <v>67</v>
-      </c>
-      <c r="T17" s="6">
-        <v>1.8</v>
-      </c>
-      <c r="U17" s="6">
-        <v>1</v>
-      </c>
-      <c r="V17" s="6">
-        <v>1.2</v>
-      </c>
-      <c r="W17" s="6">
-        <v>0.9</v>
-      </c>
-      <c r="X17" s="6">
-        <v>0.9</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="Z17" s="6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:26" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" t="s">
-        <v>47</v>
-      </c>
-      <c r="C18">
-        <v>45</v>
-      </c>
-      <c r="D18">
-        <v>40</v>
-      </c>
-      <c r="E18">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="F18">
-        <v>10</v>
-      </c>
-      <c r="G18" s="2">
-        <v>2900</v>
-      </c>
-      <c r="H18" s="2">
-        <v>2500</v>
-      </c>
-      <c r="I18" s="2">
-        <v>250</v>
-      </c>
-      <c r="J18" s="2">
-        <v>30</v>
-      </c>
-      <c r="K18" s="2">
-        <v>2800</v>
-      </c>
-      <c r="L18" s="2">
-        <v>400</v>
-      </c>
-      <c r="M18" s="2">
-        <v>30</v>
-      </c>
-      <c r="N18" s="2">
-        <v>41</v>
-      </c>
-      <c r="O18" s="2">
-        <v>20</v>
-      </c>
-      <c r="P18" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q18" s="6">
-        <v>2.5</v>
-      </c>
-      <c r="R18" s="2">
-        <v>20</v>
-      </c>
-      <c r="S18" s="2">
-        <v>203</v>
-      </c>
-      <c r="T18" s="6">
-        <v>3.5</v>
-      </c>
-      <c r="U18" s="6">
-        <v>2.6</v>
-      </c>
-      <c r="V18" s="3">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="W18" s="3">
-        <v>0.25</v>
-      </c>
-      <c r="X18" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="Z18" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:26" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>109</v>
-      </c>
-      <c r="B19" t="s">
-        <v>47</v>
-      </c>
-      <c r="C19">
-        <v>45</v>
-      </c>
-      <c r="D19">
-        <v>40</v>
-      </c>
-      <c r="E19">
-        <v>5.5</v>
-      </c>
-      <c r="F19">
-        <v>10</v>
-      </c>
-      <c r="G19" s="2">
-        <v>2200</v>
-      </c>
-      <c r="H19" s="2">
-        <v>2400</v>
-      </c>
-      <c r="I19" s="2">
-        <v>300</v>
-      </c>
-      <c r="J19" s="2">
-        <v>15</v>
-      </c>
-      <c r="K19" s="2">
-        <v>2000</v>
-      </c>
-      <c r="L19" s="2">
-        <v>900</v>
-      </c>
-      <c r="M19" s="2">
-        <v>28</v>
-      </c>
-      <c r="N19" s="2">
-        <v>42</v>
-      </c>
-      <c r="O19" s="2">
-        <v>10</v>
-      </c>
-      <c r="P19" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q19" s="6">
-        <v>3.6</v>
-      </c>
-      <c r="R19" s="2">
-        <v>20</v>
-      </c>
-      <c r="S19" s="2">
-        <v>170</v>
-      </c>
-      <c r="T19" s="6">
-        <v>2.4</v>
-      </c>
-      <c r="U19" s="6">
-        <v>1.8</v>
-      </c>
-      <c r="V19" s="3">
-        <v>1.2</v>
-      </c>
-      <c r="W19" s="6">
-        <v>1</v>
-      </c>
-      <c r="X19" s="6">
-        <v>1</v>
-      </c>
-      <c r="Y19" s="3">
-        <v>0.84</v>
-      </c>
-      <c r="Z19" s="2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="20" spans="1:26" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>110</v>
-      </c>
-      <c r="B20" t="s">
-        <v>47</v>
-      </c>
-      <c r="C20">
-        <v>45</v>
-      </c>
-      <c r="D20">
-        <v>40</v>
-      </c>
-      <c r="E20">
-        <v>4.8</v>
-      </c>
-      <c r="F20">
-        <v>10</v>
-      </c>
-      <c r="G20" s="2">
-        <v>2000</v>
-      </c>
-      <c r="H20" s="2">
-        <v>2000</v>
-      </c>
-      <c r="I20" s="2">
-        <v>300</v>
-      </c>
-      <c r="J20" s="2">
-        <v>15</v>
-      </c>
-      <c r="K20" s="2">
-        <v>1800</v>
-      </c>
-      <c r="L20" s="2">
-        <v>750</v>
-      </c>
-      <c r="M20" s="2">
-        <v>90</v>
-      </c>
-      <c r="N20" s="2">
-        <v>52</v>
-      </c>
-      <c r="O20" s="2">
-        <v>50</v>
-      </c>
-      <c r="P20" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q20" s="6">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="R20" s="2">
-        <v>20</v>
-      </c>
-      <c r="S20" s="2">
-        <v>150</v>
-      </c>
-      <c r="T20" s="6">
-        <v>3.3</v>
-      </c>
-      <c r="U20" s="6">
-        <v>2.5</v>
-      </c>
-      <c r="V20" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="W20" s="6">
-        <v>1</v>
-      </c>
-      <c r="X20" s="6">
-        <v>1</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>0.88</v>
-      </c>
-      <c r="Z20" s="2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="21" spans="1:26" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B21" t="s">
         <v>46</v>
       </c>
       <c r="C21">
+        <v>30</v>
+      </c>
+      <c r="D21">
         <v>11.56</v>
       </c>
-      <c r="D21">
+      <c r="E21">
+        <v>60</v>
+      </c>
+      <c r="F21">
+        <v>5</v>
+      </c>
+      <c r="G21">
+        <v>4.5</v>
+      </c>
+      <c r="H21">
+        <v>2300</v>
+      </c>
+      <c r="I21">
+        <v>1500</v>
+      </c>
+      <c r="J21">
+        <v>400</v>
+      </c>
+      <c r="K21">
         <v>40</v>
       </c>
-      <c r="E21">
-        <v>4.7</v>
-      </c>
-      <c r="F21">
-        <v>10</v>
-      </c>
-      <c r="G21">
-        <v>2000</v>
-      </c>
-      <c r="H21">
-        <v>2500</v>
-      </c>
-      <c r="I21">
-        <v>360</v>
-      </c>
-      <c r="J21">
-        <v>25</v>
-      </c>
-      <c r="K21">
-        <v>1800</v>
-      </c>
       <c r="L21">
-        <v>500</v>
+        <v>1900</v>
       </c>
       <c r="M21">
+        <v>330</v>
+      </c>
+      <c r="N21">
+        <v>16</v>
+      </c>
+      <c r="O21">
         <v>17</v>
       </c>
-      <c r="N21">
-        <v>44</v>
-      </c>
-      <c r="O21">
-        <v>20</v>
-      </c>
       <c r="P21">
         <v>20</v>
       </c>
       <c r="Q21">
-        <v>3.2</v>
+        <v>30</v>
       </c>
       <c r="R21">
-        <v>20</v>
+        <v>4.8</v>
       </c>
       <c r="S21">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="T21">
-        <v>2.8</v>
+        <v>66</v>
       </c>
       <c r="U21">
-        <v>2.1</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="V21">
-        <v>1.1000000000000001</v>
+        <v>3.9</v>
       </c>
       <c r="W21">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="X21">
         <v>0.5</v>
       </c>
       <c r="Y21">
-        <v>0.79</v>
+        <v>0.5</v>
       </c>
       <c r="Z21">
+        <v>0.83</v>
+      </c>
+      <c r="AA21">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:26" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B22" t="s">
         <v>46</v>
       </c>
       <c r="C22">
+        <v>30</v>
+      </c>
+      <c r="D22">
         <v>11.56</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <v>40</v>
       </c>
-      <c r="E22">
+      <c r="F22">
+        <v>3.2</v>
+      </c>
+      <c r="G22">
+        <v>4.5</v>
+      </c>
+      <c r="H22" s="2">
+        <v>2500</v>
+      </c>
+      <c r="I22" s="2">
+        <v>1500</v>
+      </c>
+      <c r="J22" s="2">
+        <v>200</v>
+      </c>
+      <c r="K22" s="2">
+        <v>24</v>
+      </c>
+      <c r="L22" s="2">
+        <v>1375</v>
+      </c>
+      <c r="M22" s="2">
+        <v>1130</v>
+      </c>
+      <c r="N22" s="2">
+        <v>50</v>
+      </c>
+      <c r="O22" s="2">
+        <v>17</v>
+      </c>
+      <c r="P22" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q22" s="2">
+        <v>20</v>
+      </c>
+      <c r="R22" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="S22" s="2">
+        <v>20</v>
+      </c>
+      <c r="T22" s="2">
+        <v>65</v>
+      </c>
+      <c r="U22" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="V22" s="3">
+        <v>4.5</v>
+      </c>
+      <c r="W22" s="3">
         <v>0.9</v>
       </c>
-      <c r="F22">
-        <v>4.5</v>
-      </c>
-      <c r="G22">
-        <v>760</v>
-      </c>
-      <c r="H22">
-        <v>900</v>
-      </c>
-      <c r="I22">
-        <v>100</v>
-      </c>
-      <c r="J22">
-        <v>25</v>
-      </c>
-      <c r="K22">
-        <v>650</v>
-      </c>
-      <c r="L22">
-        <v>95</v>
-      </c>
-      <c r="M22">
-        <v>11</v>
-      </c>
-      <c r="N22">
-        <v>21</v>
-      </c>
-      <c r="O22">
-        <v>20</v>
-      </c>
-      <c r="P22">
-        <v>20</v>
-      </c>
-      <c r="Q22">
-        <v>0.65</v>
-      </c>
-      <c r="R22">
-        <v>20</v>
-      </c>
-      <c r="S22">
-        <v>64</v>
-      </c>
-      <c r="T22">
-        <v>7</v>
-      </c>
-      <c r="U22">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="V22">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="W22">
-        <v>1</v>
-      </c>
-      <c r="X22">
-        <v>1</v>
-      </c>
-      <c r="Y22">
-        <v>0.85</v>
-      </c>
-      <c r="Z22">
-        <v>20</v>
+      <c r="X22" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="AA22" s="3">
+        <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:26" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="B23" t="s">
         <v>46</v>
       </c>
       <c r="C23">
-        <f>3.4*3.4</f>
-        <v>11.559999999999999</v>
+        <v>30</v>
       </c>
       <c r="D23">
-        <v>80</v>
+        <v>11.56</v>
       </c>
       <c r="E23">
+        <v>30</v>
+      </c>
+      <c r="F23">
+        <v>3.7</v>
+      </c>
+      <c r="G23">
+        <v>4.5</v>
+      </c>
+      <c r="H23" s="2">
+        <v>1200</v>
+      </c>
+      <c r="I23" s="2">
+        <v>1200</v>
+      </c>
+      <c r="J23" s="2">
+        <v>150</v>
+      </c>
+      <c r="K23" s="2">
+        <v>12</v>
+      </c>
+      <c r="L23" s="2">
+        <v>1175</v>
+      </c>
+      <c r="M23" s="2">
+        <v>450</v>
+      </c>
+      <c r="N23" s="2">
+        <v>30</v>
+      </c>
+      <c r="O23" s="2">
+        <v>10</v>
+      </c>
+      <c r="P23" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q23">
+        <v>15</v>
+      </c>
+      <c r="R23">
+        <v>1.4</v>
+      </c>
+      <c r="S23">
+        <v>15</v>
+      </c>
+      <c r="T23">
+        <v>53</v>
+      </c>
+      <c r="U23">
+        <v>3.8</v>
+      </c>
+      <c r="V23">
+        <v>2.7</v>
+      </c>
+      <c r="W23">
+        <v>0.9</v>
+      </c>
+      <c r="X23" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="Y23" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="Z23">
+        <v>0.76</v>
+      </c>
+      <c r="AA23">
         <v>5</v>
       </c>
-      <c r="F23">
+    </row>
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24">
+        <v>30</v>
+      </c>
+      <c r="D24">
+        <v>11.56</v>
+      </c>
+      <c r="E24">
+        <v>40</v>
+      </c>
+      <c r="F24">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="G24">
         <v>4.5</v>
       </c>
-      <c r="G23">
-        <v>2100</v>
-      </c>
-      <c r="H23">
-        <v>1200</v>
-      </c>
-      <c r="I23">
-        <v>300</v>
-      </c>
-      <c r="J23">
+      <c r="H24">
+        <v>2700</v>
+      </c>
+      <c r="I24">
+        <v>1400</v>
+      </c>
+      <c r="J24">
+        <v>70</v>
+      </c>
+      <c r="K24">
+        <v>30</v>
+      </c>
+      <c r="L24">
+        <v>2450</v>
+      </c>
+      <c r="M24">
+        <v>350</v>
+      </c>
+      <c r="N24">
+        <v>20</v>
+      </c>
+      <c r="O24">
+        <v>10</v>
+      </c>
+      <c r="P24">
+        <v>20.8</v>
+      </c>
+      <c r="Q24">
+        <v>20</v>
+      </c>
+      <c r="R24">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="S24">
+        <v>20</v>
+      </c>
+      <c r="T24">
+        <v>76</v>
+      </c>
+      <c r="U24">
+        <v>3.88</v>
+      </c>
+      <c r="V24">
+        <v>2.71</v>
+      </c>
+      <c r="W24">
+        <v>1.3</v>
+      </c>
+      <c r="X24">
+        <v>0.8</v>
+      </c>
+      <c r="Y24">
+        <v>0.8</v>
+      </c>
+      <c r="Z24">
+        <v>0.74</v>
+      </c>
+      <c r="AA24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25">
+        <v>30</v>
+      </c>
+      <c r="D25">
+        <v>11.56</v>
+      </c>
+      <c r="E25">
         <v>40</v>
       </c>
-      <c r="K23">
-        <v>1900</v>
-      </c>
-      <c r="L23">
-        <v>280</v>
-      </c>
-      <c r="M23">
-        <v>12</v>
-      </c>
-      <c r="N23">
-        <v>27</v>
-      </c>
-      <c r="O23">
-        <v>20</v>
-      </c>
-      <c r="P23">
-        <v>40</v>
-      </c>
-      <c r="Q23">
-        <v>4</v>
-      </c>
-      <c r="R23">
-        <v>40</v>
-      </c>
-      <c r="S23">
-        <v>52</v>
-      </c>
-      <c r="T23">
-        <v>7.4</v>
-      </c>
-      <c r="U23">
-        <v>5.9</v>
-      </c>
-      <c r="V23">
-        <v>1.3</v>
-      </c>
-      <c r="W23">
+      <c r="F25">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="G25">
+        <v>4.5</v>
+      </c>
+      <c r="H25">
+        <v>3600</v>
+      </c>
+      <c r="I25">
+        <v>1600</v>
+      </c>
+      <c r="J25">
+        <v>350</v>
+      </c>
+      <c r="K25">
+        <v>24</v>
+      </c>
+      <c r="L25">
+        <v>3250</v>
+      </c>
+      <c r="M25">
+        <v>400</v>
+      </c>
+      <c r="N25">
+        <v>50</v>
+      </c>
+      <c r="O25">
+        <v>23</v>
+      </c>
+      <c r="P25">
+        <v>10</v>
+      </c>
+      <c r="Q25">
+        <v>20</v>
+      </c>
+      <c r="R25">
+        <v>4.2</v>
+      </c>
+      <c r="S25">
+        <v>20</v>
+      </c>
+      <c r="T25">
+        <v>70</v>
+      </c>
+      <c r="U25">
+        <v>3.85</v>
+      </c>
+      <c r="V25">
+        <v>2.85</v>
+      </c>
+      <c r="W25">
+        <v>1.4</v>
+      </c>
+      <c r="X25">
         <v>0.5</v>
       </c>
-      <c r="X23">
+      <c r="Y25">
         <v>0.5</v>
       </c>
-      <c r="Y23">
-        <v>0.85</v>
-      </c>
-      <c r="Z23">
-        <v>20</v>
+      <c r="Z25">
+        <v>0.74</v>
+      </c>
+      <c r="AA25">
+        <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:26" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" t="s">
-        <v>47</v>
-      </c>
-      <c r="C24">
-        <v>45</v>
-      </c>
-      <c r="D24">
-        <v>40</v>
-      </c>
-      <c r="E24">
-        <v>2.1</v>
-      </c>
-      <c r="F24">
-        <v>10</v>
-      </c>
-      <c r="G24" s="2">
-        <v>750</v>
-      </c>
-      <c r="H24" s="2">
-        <v>900</v>
-      </c>
-      <c r="I24" s="2">
-        <v>100</v>
-      </c>
-      <c r="J24" s="2">
-        <v>25</v>
-      </c>
-      <c r="K24" s="2">
-        <v>650</v>
-      </c>
-      <c r="L24" s="2">
-        <v>190</v>
-      </c>
-      <c r="M24" s="2">
-        <v>12</v>
-      </c>
-      <c r="N24" s="2">
-        <v>22</v>
-      </c>
-      <c r="O24" s="2">
-        <v>10</v>
-      </c>
-      <c r="P24" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q24" s="6">
-        <v>1.4</v>
-      </c>
-      <c r="R24" s="2">
-        <v>20</v>
-      </c>
-      <c r="S24" s="2">
-        <v>100</v>
-      </c>
-      <c r="T24" s="6">
-        <v>6.8</v>
-      </c>
-      <c r="U24" s="6">
-        <v>4.7</v>
-      </c>
-      <c r="V24" s="6">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="W24" s="6">
-        <v>1</v>
-      </c>
-      <c r="X24" s="6">
-        <v>1</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>0.92</v>
-      </c>
-      <c r="Z24" s="2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="25" spans="1:26" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>14</v>
-      </c>
-      <c r="B25" t="s">
-        <v>47</v>
-      </c>
-      <c r="C25">
-        <v>45</v>
-      </c>
-      <c r="D25">
-        <v>40</v>
-      </c>
-      <c r="E25">
-        <v>7.6</v>
-      </c>
-      <c r="F25">
-        <v>10</v>
-      </c>
-      <c r="G25" s="2">
-        <v>2400</v>
-      </c>
-      <c r="H25" s="2">
-        <v>1800</v>
-      </c>
-      <c r="I25" s="2">
-        <v>300</v>
-      </c>
-      <c r="J25" s="2">
-        <v>30</v>
-      </c>
-      <c r="K25" s="2">
-        <v>2200</v>
-      </c>
-      <c r="L25" s="2">
-        <v>380</v>
-      </c>
-      <c r="M25" s="2">
-        <v>15</v>
-      </c>
-      <c r="N25" s="2">
-        <v>23</v>
-      </c>
-      <c r="O25" s="2">
-        <v>42</v>
-      </c>
-      <c r="P25" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q25" s="6">
-        <v>3.2</v>
-      </c>
-      <c r="R25" s="2">
-        <v>20</v>
-      </c>
-      <c r="S25" s="2">
-        <v>96</v>
-      </c>
-      <c r="T25" s="6">
-        <v>6.8</v>
-      </c>
-      <c r="U25" s="6">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="V25" s="6">
-        <v>1.4</v>
-      </c>
-      <c r="W25" s="6">
-        <v>1</v>
-      </c>
-      <c r="X25" s="6">
-        <v>1</v>
-      </c>
-      <c r="Y25" s="3">
-        <v>0.88</v>
-      </c>
-      <c r="Z25" s="2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="26" spans="1:26" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B26" t="s">
         <v>46</v>
       </c>
       <c r="C26">
+        <v>30</v>
+      </c>
+      <c r="D26">
         <v>11.56</v>
       </c>
-      <c r="D26">
+      <c r="E26">
         <v>60</v>
       </c>
-      <c r="E26">
-        <v>5</v>
-      </c>
       <c r="F26">
+        <v>7</v>
+      </c>
+      <c r="G26">
         <v>4.5</v>
       </c>
-      <c r="G26">
-        <v>2300</v>
-      </c>
       <c r="H26">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="I26">
-        <v>400</v>
+        <v>2000</v>
       </c>
       <c r="J26">
-        <v>40</v>
+        <v>300</v>
       </c>
       <c r="K26">
-        <v>1900</v>
+        <v>24</v>
       </c>
       <c r="L26">
-        <v>330</v>
+        <v>2500</v>
       </c>
       <c r="M26">
-        <v>16</v>
+        <v>700</v>
       </c>
       <c r="N26">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="O26">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P26">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="Q26">
-        <v>4.8</v>
+        <v>30</v>
       </c>
       <c r="R26">
-        <v>30</v>
+        <v>4.7</v>
       </c>
       <c r="S26">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="T26">
-        <v>4.9000000000000004</v>
+        <v>57</v>
       </c>
       <c r="U26">
-        <v>3.9</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="V26">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="W26">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="X26">
         <v>0.5</v>
       </c>
       <c r="Y26">
-        <v>0.83</v>
+        <v>0.5</v>
       </c>
       <c r="Z26">
-        <v>20</v>
+        <v>0.74</v>
+      </c>
+      <c r="AA26">
+        <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:26" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27">
+        <v>30</v>
+      </c>
+      <c r="D27">
+        <v>11.56</v>
+      </c>
+      <c r="E27">
+        <v>60</v>
+      </c>
+      <c r="F27">
+        <v>6.2</v>
+      </c>
+      <c r="G27">
+        <v>4.5</v>
+      </c>
+      <c r="H27">
+        <v>2200</v>
+      </c>
+      <c r="I27">
+        <v>1600</v>
+      </c>
+      <c r="J27">
+        <v>300</v>
+      </c>
+      <c r="K27">
+        <v>24</v>
+      </c>
+      <c r="L27">
+        <v>2000</v>
+      </c>
+      <c r="M27">
+        <v>560</v>
+      </c>
+      <c r="N27">
+        <v>32</v>
+      </c>
+      <c r="O27">
+        <v>20</v>
+      </c>
+      <c r="P27">
+        <v>10</v>
+      </c>
+      <c r="Q27">
+        <v>30</v>
+      </c>
+      <c r="R27">
+        <v>4.5</v>
+      </c>
+      <c r="S27">
+        <v>30</v>
+      </c>
+      <c r="T27">
+        <v>54</v>
+      </c>
+      <c r="U27">
+        <v>4.8</v>
+      </c>
+      <c r="V27">
+        <v>3.4</v>
+      </c>
+      <c r="W27">
+        <v>0.85</v>
+      </c>
+      <c r="X27">
+        <v>0.5</v>
+      </c>
+      <c r="Y27">
+        <v>0.5</v>
+      </c>
+      <c r="Z27">
+        <v>0.75</v>
+      </c>
+      <c r="AA27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28">
+        <v>30</v>
+      </c>
+      <c r="D28">
+        <v>11.56</v>
+      </c>
+      <c r="E28">
+        <v>40</v>
+      </c>
+      <c r="F28">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="G28">
+        <v>4.5</v>
+      </c>
+      <c r="H28">
+        <v>4100</v>
+      </c>
+      <c r="I28">
+        <v>2000</v>
+      </c>
+      <c r="J28">
+        <v>350</v>
+      </c>
+      <c r="K28">
+        <v>24</v>
+      </c>
+      <c r="L28">
+        <v>3700</v>
+      </c>
+      <c r="M28">
+        <v>600</v>
+      </c>
+      <c r="N28">
+        <v>90</v>
+      </c>
+      <c r="O28">
+        <v>23</v>
+      </c>
+      <c r="P28">
+        <v>10</v>
+      </c>
+      <c r="Q28">
+        <v>20</v>
+      </c>
+      <c r="R28">
         <v>4</v>
       </c>
-      <c r="B27" t="s">
+      <c r="S28">
+        <v>20</v>
+      </c>
+      <c r="T28">
+        <v>98</v>
+      </c>
+      <c r="U28">
+        <v>2.4</v>
+      </c>
+      <c r="V28">
+        <v>1.8</v>
+      </c>
+      <c r="W28">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="X28">
+        <v>0.5</v>
+      </c>
+      <c r="Y28">
+        <v>0.5</v>
+      </c>
+      <c r="Z28">
+        <v>0.73</v>
+      </c>
+      <c r="AA28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>20</v>
+      </c>
+      <c r="B29" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29">
+        <v>30</v>
+      </c>
+      <c r="D29">
+        <v>11.56</v>
+      </c>
+      <c r="E29">
+        <v>40</v>
+      </c>
+      <c r="F29">
+        <v>2.9</v>
+      </c>
+      <c r="G29">
+        <v>4.5</v>
+      </c>
+      <c r="H29">
+        <v>950</v>
+      </c>
+      <c r="I29">
+        <v>500</v>
+      </c>
+      <c r="J29">
+        <v>70</v>
+      </c>
+      <c r="K29">
+        <v>25</v>
+      </c>
+      <c r="L29" s="2">
+        <v>875</v>
+      </c>
+      <c r="M29" s="2">
+        <v>150</v>
+      </c>
+      <c r="N29" s="2">
+        <v>16</v>
+      </c>
+      <c r="O29" s="2">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="P29" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q29" s="2">
+        <v>20</v>
+      </c>
+      <c r="R29" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="S29">
+        <v>20</v>
+      </c>
+      <c r="T29" s="2">
         <v>45</v>
       </c>
-      <c r="C27" s="2">
-        <v>1</v>
-      </c>
-      <c r="D27" s="2">
-        <v>0</v>
-      </c>
-      <c r="E27" s="5">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="F27" s="5">
-        <v>4.5</v>
-      </c>
-      <c r="G27" s="5">
-        <v>1</v>
-      </c>
-      <c r="H27" s="5">
-        <v>1</v>
-      </c>
-      <c r="I27" s="5">
-        <v>1</v>
-      </c>
-      <c r="J27" s="5">
+      <c r="U29">
+        <v>9.6</v>
+      </c>
+      <c r="V29">
+        <v>6.7</v>
+      </c>
+      <c r="W29" s="4">
+        <v>3.2</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0.82</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>46</v>
+      </c>
+      <c r="C30">
+        <v>30</v>
+      </c>
+      <c r="D30">
+        <v>11.56</v>
+      </c>
+      <c r="E30">
+        <v>30</v>
+      </c>
+      <c r="F30">
+        <v>3.6</v>
+      </c>
+      <c r="G30">
+        <v>10</v>
+      </c>
+      <c r="H30" s="2">
+        <v>1450</v>
+      </c>
+      <c r="I30" s="2">
+        <v>1100</v>
+      </c>
+      <c r="J30" s="2">
+        <v>200</v>
+      </c>
+      <c r="K30" s="2">
         <v>25</v>
       </c>
-      <c r="K27" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="L27" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="M27" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="N27" s="5">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="O27" s="5">
-        <v>1</v>
-      </c>
-      <c r="P27" s="5">
-        <v>20</v>
-      </c>
-      <c r="Q27" s="5">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="R27" s="5">
-        <v>20</v>
-      </c>
-      <c r="S27" s="5">
-        <v>20</v>
-      </c>
-      <c r="T27" s="6">
-        <v>1E-3</v>
-      </c>
-      <c r="U27" s="6">
-        <v>1E-3</v>
-      </c>
-      <c r="V27" s="5">
-        <v>1</v>
-      </c>
-      <c r="W27" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="X27" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="Y27" s="5">
-        <v>0.01</v>
-      </c>
-      <c r="Z27" s="5">
+      <c r="L30" s="2">
+        <v>1300</v>
+      </c>
+      <c r="M30" s="2">
+        <v>250</v>
+      </c>
+      <c r="N30" s="2">
+        <v>30</v>
+      </c>
+      <c r="O30" s="2">
+        <v>18</v>
+      </c>
+      <c r="P30" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q30" s="2">
+        <v>15</v>
+      </c>
+      <c r="R30" s="6">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="S30" s="2">
+        <v>15</v>
+      </c>
+      <c r="T30" s="2">
+        <v>77</v>
+      </c>
+      <c r="U30" s="6">
+        <v>6</v>
+      </c>
+      <c r="V30" s="6">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="W30" s="6">
+        <v>1.7</v>
+      </c>
+      <c r="X30" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="Y30" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="Z30" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="AA30" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:26" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>111</v>
-      </c>
-      <c r="B28" t="s">
-        <v>47</v>
-      </c>
-      <c r="C28">
-        <v>45</v>
-      </c>
-      <c r="D28">
-        <v>40</v>
-      </c>
-      <c r="E28">
-        <v>7</v>
-      </c>
-      <c r="F28">
-        <v>10</v>
-      </c>
-      <c r="G28" s="2">
-        <v>1900</v>
-      </c>
-      <c r="H28" s="2">
-        <v>2000</v>
-      </c>
-      <c r="I28" s="2">
-        <v>300</v>
-      </c>
-      <c r="J28" s="2">
-        <v>15</v>
-      </c>
-      <c r="K28" s="2">
-        <v>1600</v>
-      </c>
-      <c r="L28" s="2">
-        <v>780</v>
-      </c>
-      <c r="M28" s="2">
-        <v>80</v>
-      </c>
-      <c r="N28" s="2">
-        <v>23</v>
-      </c>
-      <c r="O28" s="2">
-        <v>50</v>
-      </c>
-      <c r="P28" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q28" s="6">
-        <v>4</v>
-      </c>
-      <c r="R28" s="2">
-        <v>20</v>
-      </c>
-      <c r="S28" s="2">
-        <v>140</v>
-      </c>
-      <c r="T28" s="6">
-        <v>3.1</v>
-      </c>
-      <c r="U28" s="6">
-        <v>2.7</v>
-      </c>
-      <c r="V28" s="3">
-        <v>2.8</v>
-      </c>
-      <c r="W28" s="6">
-        <v>1</v>
-      </c>
-      <c r="X28" s="6">
-        <v>1</v>
-      </c>
-      <c r="Y28" s="3">
-        <v>0.89</v>
-      </c>
-      <c r="Z28" s="2">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="29" spans="1:26" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>112</v>
-      </c>
-      <c r="B29" t="s">
-        <v>47</v>
-      </c>
-      <c r="C29">
-        <v>45</v>
-      </c>
-      <c r="D29">
-        <v>40</v>
-      </c>
-      <c r="E29">
-        <v>5</v>
-      </c>
-      <c r="F29">
-        <v>10</v>
-      </c>
-      <c r="G29" s="2">
-        <v>1400</v>
-      </c>
-      <c r="H29" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I29" s="2">
-        <v>200</v>
-      </c>
-      <c r="J29" s="2">
-        <v>15</v>
-      </c>
-      <c r="K29" s="2">
-        <v>1100</v>
-      </c>
-      <c r="L29" s="2">
-        <v>580</v>
-      </c>
-      <c r="M29" s="2">
-        <v>60</v>
-      </c>
-      <c r="N29" s="2">
-        <v>19</v>
-      </c>
-      <c r="O29" s="2">
-        <v>50</v>
-      </c>
-      <c r="P29" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q29" s="6">
-        <v>3</v>
-      </c>
-      <c r="R29" s="2">
-        <v>20</v>
-      </c>
-      <c r="S29" s="2">
-        <v>100</v>
-      </c>
-      <c r="T29" s="6">
-        <v>4</v>
-      </c>
-      <c r="U29" s="6">
-        <v>3.5</v>
-      </c>
-      <c r="V29" s="3">
-        <v>2.1</v>
-      </c>
-      <c r="W29" s="3">
-        <v>1</v>
-      </c>
-      <c r="X29" s="3">
-        <v>1</v>
-      </c>
-      <c r="Y29" s="3">
-        <v>0.88</v>
-      </c>
-      <c r="Z29" s="2">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="30" spans="1:26" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>13</v>
-      </c>
-      <c r="B30" t="s">
-        <v>47</v>
-      </c>
-      <c r="C30">
-        <v>45</v>
-      </c>
-      <c r="D30">
-        <v>40</v>
-      </c>
-      <c r="E30">
-        <v>6.3</v>
-      </c>
-      <c r="F30">
-        <v>4.5</v>
-      </c>
-      <c r="G30" s="2">
-        <v>2100</v>
-      </c>
-      <c r="H30" s="2">
-        <v>1400</v>
-      </c>
-      <c r="I30" s="2">
-        <v>150</v>
-      </c>
-      <c r="J30" s="2">
-        <v>24</v>
-      </c>
-      <c r="K30" s="2">
-        <v>2000</v>
-      </c>
-      <c r="L30" s="2">
-        <v>350</v>
-      </c>
-      <c r="M30" s="2">
-        <v>14</v>
-      </c>
-      <c r="N30" s="2">
-        <v>13</v>
-      </c>
-      <c r="O30" s="2">
-        <v>10</v>
-      </c>
-      <c r="P30" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q30" s="6">
-        <v>2.1</v>
-      </c>
-      <c r="R30" s="2">
-        <v>20</v>
-      </c>
-      <c r="S30" s="2">
-        <v>50</v>
-      </c>
-      <c r="T30" s="3">
-        <v>5</v>
-      </c>
-      <c r="U30" s="3">
-        <v>3.5</v>
-      </c>
-      <c r="V30" s="3">
-        <v>1.45</v>
-      </c>
-      <c r="W30" s="3">
-        <v>1</v>
-      </c>
-      <c r="X30" s="3">
-        <v>1</v>
-      </c>
-      <c r="Y30" s="3">
-        <v>0.74</v>
-      </c>
-      <c r="Z30" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:26" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="B31" t="s">
         <v>46</v>
       </c>
       <c r="C31">
+        <v>30</v>
+      </c>
+      <c r="D31">
         <v>11.56</v>
       </c>
-      <c r="D31">
-        <v>40</v>
-      </c>
       <c r="E31">
-        <v>3.2</v>
+        <v>30</v>
       </c>
       <c r="F31">
+        <v>4</v>
+      </c>
+      <c r="G31">
         <v>4.5</v>
       </c>
-      <c r="G31" s="2">
-        <v>2500</v>
-      </c>
-      <c r="H31" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I31" s="2">
+      <c r="H31">
+        <v>1600</v>
+      </c>
+      <c r="I31">
+        <v>1280</v>
+      </c>
+      <c r="J31">
         <v>200</v>
       </c>
-      <c r="J31" s="2">
-        <v>24</v>
-      </c>
       <c r="K31" s="2">
-        <v>1375</v>
-      </c>
-      <c r="L31" s="2">
-        <v>1130</v>
-      </c>
-      <c r="M31" s="2">
-        <v>50</v>
-      </c>
-      <c r="N31" s="2">
-        <v>17</v>
+        <v>25</v>
+      </c>
+      <c r="L31">
+        <v>1400</v>
+      </c>
+      <c r="M31">
+        <v>250</v>
+      </c>
+      <c r="N31">
+        <v>36</v>
       </c>
       <c r="O31" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="P31" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="Q31" s="2">
-        <v>2.5</v>
+        <v>15</v>
       </c>
       <c r="R31" s="2">
-        <v>20</v>
+        <v>1.8</v>
       </c>
       <c r="S31" s="2">
+        <v>15</v>
+      </c>
+      <c r="T31" s="2">
         <v>65</v>
       </c>
-      <c r="T31" s="3">
-        <v>6.2</v>
-      </c>
-      <c r="U31" s="3">
-        <v>4.5</v>
-      </c>
-      <c r="V31" s="3">
-        <v>0.9</v>
-      </c>
-      <c r="W31" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="X31" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="Y31" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="Z31" s="3">
-        <v>4</v>
+      <c r="U31">
+        <v>6.8</v>
+      </c>
+      <c r="V31">
+        <v>4.25</v>
+      </c>
+      <c r="W31">
+        <v>1.65</v>
+      </c>
+      <c r="X31">
+        <v>0.8</v>
+      </c>
+      <c r="Y31">
+        <v>0.8</v>
+      </c>
+      <c r="Z31">
+        <v>0.76</v>
+      </c>
+      <c r="AA31">
+        <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:26" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B32" t="s">
         <v>46</v>
       </c>
       <c r="C32">
+        <v>30</v>
+      </c>
+      <c r="D32">
         <v>11.56</v>
       </c>
-      <c r="D32">
-        <v>30</v>
-      </c>
       <c r="E32">
-        <v>4.2</v>
+        <v>30</v>
       </c>
       <c r="F32">
+        <v>2.8</v>
+      </c>
+      <c r="G32">
         <v>4.5</v>
       </c>
-      <c r="G32" s="2">
-        <v>1700</v>
-      </c>
       <c r="H32" s="2">
-        <v>1600</v>
+        <v>1060</v>
       </c>
       <c r="I32" s="2">
-        <v>250</v>
+        <v>900</v>
       </c>
       <c r="J32" s="2">
-        <v>15</v>
+        <v>140</v>
       </c>
       <c r="K32" s="2">
-        <v>1550</v>
+        <v>10</v>
       </c>
       <c r="L32" s="2">
-        <v>550</v>
+        <v>960</v>
       </c>
       <c r="M32" s="2">
-        <v>60</v>
+        <v>460</v>
       </c>
       <c r="N32" s="2">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="O32" s="2">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="P32" s="2">
         <v>15</v>
       </c>
       <c r="Q32" s="2">
-        <v>2.6</v>
-      </c>
-      <c r="R32" s="2">
-        <v>15</v>
+        <v>15</v>
+      </c>
+      <c r="R32" s="6">
+        <v>1.2</v>
       </c>
       <c r="S32" s="2">
-        <v>67</v>
-      </c>
-      <c r="T32" s="3">
-        <v>4.8</v>
-      </c>
-      <c r="U32" s="3">
-        <v>2.7</v>
-      </c>
-      <c r="V32" s="2">
-        <v>1.4</v>
-      </c>
-      <c r="W32" s="3">
+        <v>15</v>
+      </c>
+      <c r="T32" s="2">
+        <v>46</v>
+      </c>
+      <c r="U32" s="6">
+        <v>7.87</v>
+      </c>
+      <c r="V32" s="6">
+        <v>5.63</v>
+      </c>
+      <c r="W32" s="6">
         <v>0.8</v>
       </c>
-      <c r="X32" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="Z32" s="2">
-        <v>10</v>
+      <c r="X32" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Y32" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Z32" s="6">
+        <v>0.85</v>
+      </c>
+      <c r="AA32" s="6">
+        <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:26" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B33" t="s">
         <v>46</v>
       </c>
       <c r="C33">
+        <v>30</v>
+      </c>
+      <c r="D33">
         <v>11.56</v>
       </c>
-      <c r="D33">
-        <v>30</v>
-      </c>
       <c r="E33">
+        <v>30</v>
+      </c>
+      <c r="F33">
+        <v>2.1</v>
+      </c>
+      <c r="G33">
+        <v>4.5</v>
+      </c>
+      <c r="H33" s="2">
+        <v>735</v>
+      </c>
+      <c r="I33" s="2">
+        <v>680</v>
+      </c>
+      <c r="J33" s="2">
+        <v>100</v>
+      </c>
+      <c r="K33" s="2">
+        <v>12</v>
+      </c>
+      <c r="L33" s="2">
+        <v>640</v>
+      </c>
+      <c r="M33" s="2">
+        <v>310</v>
+      </c>
+      <c r="N33" s="2">
+        <v>21</v>
+      </c>
+      <c r="O33" s="2">
+        <v>10</v>
+      </c>
+      <c r="P33" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q33" s="2">
+        <v>15</v>
+      </c>
+      <c r="R33" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="S33" s="2">
+        <v>15</v>
+      </c>
+      <c r="T33" s="2">
+        <v>37</v>
+      </c>
+      <c r="U33" s="6">
+        <v>11</v>
+      </c>
+      <c r="V33" s="6">
+        <v>8.4</v>
+      </c>
+      <c r="W33" s="6">
+        <v>1.4</v>
+      </c>
+      <c r="X33" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Y33" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Z33" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="AA33" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
         <v>4</v>
       </c>
-      <c r="F33">
+      <c r="B34" t="s">
+        <v>45</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34" s="2">
+        <v>1</v>
+      </c>
+      <c r="E34" s="2">
+        <v>0</v>
+      </c>
+      <c r="F34" s="5">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="G34" s="5">
         <v>4.5</v>
       </c>
-      <c r="G33">
-        <v>1600</v>
-      </c>
-      <c r="H33">
-        <v>1280</v>
-      </c>
-      <c r="I33">
+      <c r="H34" s="5">
+        <v>1</v>
+      </c>
+      <c r="I34" s="5">
+        <v>1</v>
+      </c>
+      <c r="J34" s="5">
+        <v>1</v>
+      </c>
+      <c r="K34" s="5">
+        <v>25</v>
+      </c>
+      <c r="L34" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="M34" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="N34" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="O34" s="5">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="P34" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q34" s="5">
+        <v>20</v>
+      </c>
+      <c r="R34" s="5">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="S34" s="5">
+        <v>20</v>
+      </c>
+      <c r="T34" s="5">
+        <v>20</v>
+      </c>
+      <c r="U34" s="6">
+        <v>1E-3</v>
+      </c>
+      <c r="V34" s="6">
+        <v>1E-3</v>
+      </c>
+      <c r="W34" s="5">
+        <v>1</v>
+      </c>
+      <c r="X34" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="Y34" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="Z34" s="5">
+        <v>0.01</v>
+      </c>
+      <c r="AA34" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" t="s">
+        <v>49</v>
+      </c>
+      <c r="C35">
+        <v>32</v>
+      </c>
+      <c r="D35">
+        <v>11.56</v>
+      </c>
+      <c r="E35">
+        <v>30</v>
+      </c>
+      <c r="F35">
+        <v>5.5</v>
+      </c>
+      <c r="G35">
+        <v>5</v>
+      </c>
+      <c r="H35" s="2">
+        <v>1500</v>
+      </c>
+      <c r="I35" s="2">
+        <v>1500</v>
+      </c>
+      <c r="J35" s="2">
         <v>200</v>
       </c>
-      <c r="J33" s="2">
+      <c r="K35" s="2">
+        <v>10</v>
+      </c>
+      <c r="L35" s="2">
+        <v>1450</v>
+      </c>
+      <c r="M35" s="2">
+        <v>700</v>
+      </c>
+      <c r="N35" s="2">
+        <v>48</v>
+      </c>
+      <c r="O35" s="2">
+        <v>6</v>
+      </c>
+      <c r="P35" s="2">
+        <v>15</v>
+      </c>
+      <c r="Q35" s="2">
+        <v>15</v>
+      </c>
+      <c r="R35" s="6">
+        <v>1.7</v>
+      </c>
+      <c r="S35" s="2">
+        <v>15</v>
+      </c>
+      <c r="T35" s="2">
+        <v>61</v>
+      </c>
+      <c r="U35" s="6">
+        <v>2.9</v>
+      </c>
+      <c r="V35" s="6">
+        <v>2</v>
+      </c>
+      <c r="W35" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="X35" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y35" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z35" s="3">
+        <v>0.85</v>
+      </c>
+      <c r="AA35" s="6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" t="s">
+        <v>49</v>
+      </c>
+      <c r="C36">
+        <v>32</v>
+      </c>
+      <c r="D36">
+        <v>11.56</v>
+      </c>
+      <c r="E36">
+        <v>30</v>
+      </c>
+      <c r="F36">
+        <v>3.8</v>
+      </c>
+      <c r="G36">
+        <v>5</v>
+      </c>
+      <c r="H36" s="2">
+        <v>1050</v>
+      </c>
+      <c r="I36" s="2">
+        <v>1000</v>
+      </c>
+      <c r="J36" s="2">
+        <v>150</v>
+      </c>
+      <c r="K36" s="2">
+        <v>10</v>
+      </c>
+      <c r="L36" s="2">
+        <v>1000</v>
+      </c>
+      <c r="M36" s="2">
+        <v>460</v>
+      </c>
+      <c r="N36" s="2">
+        <v>39</v>
+      </c>
+      <c r="O36" s="2">
+        <v>3</v>
+      </c>
+      <c r="P36" s="2">
+        <v>15</v>
+      </c>
+      <c r="Q36" s="2">
+        <v>15</v>
+      </c>
+      <c r="R36" s="6">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="S36" s="2">
+        <v>15</v>
+      </c>
+      <c r="T36" s="2">
+        <v>57</v>
+      </c>
+      <c r="U36" s="6">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="V36" s="6">
+        <v>2.7</v>
+      </c>
+      <c r="W36" s="6">
+        <v>1.2</v>
+      </c>
+      <c r="X36" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z36" s="3">
+        <v>0.85</v>
+      </c>
+      <c r="AA36" s="6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>113</v>
+      </c>
+      <c r="B37" t="s">
+        <v>47</v>
+      </c>
+      <c r="C37">
+        <v>15</v>
+      </c>
+      <c r="D37">
+        <v>45</v>
+      </c>
+      <c r="E37">
+        <v>30</v>
+      </c>
+      <c r="F37">
+        <v>11.4</v>
+      </c>
+      <c r="G37">
+        <v>4.5</v>
+      </c>
+      <c r="H37" s="2">
+        <v>4600</v>
+      </c>
+      <c r="I37" s="2">
+        <v>5500</v>
+      </c>
+      <c r="J37" s="2">
+        <v>250</v>
+      </c>
+      <c r="K37" s="2">
+        <v>15</v>
+      </c>
+      <c r="L37" s="2">
+        <v>4200</v>
+      </c>
+      <c r="M37" s="2">
+        <v>1800</v>
+      </c>
+      <c r="N37" s="2">
+        <v>68</v>
+      </c>
+      <c r="O37" s="2">
+        <v>45</v>
+      </c>
+      <c r="P37" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q37" s="2">
+        <v>15</v>
+      </c>
+      <c r="R37" s="6">
+        <v>2.4</v>
+      </c>
+      <c r="S37" s="2">
+        <v>15</v>
+      </c>
+      <c r="T37" s="2">
+        <v>67</v>
+      </c>
+      <c r="U37" s="6">
+        <v>1.8</v>
+      </c>
+      <c r="V37" s="6">
+        <v>1</v>
+      </c>
+      <c r="W37" s="6">
+        <v>1.2</v>
+      </c>
+      <c r="X37" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="Y37" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="Z37" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="AA37" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>32</v>
+      </c>
+      <c r="B38" t="s">
+        <v>47</v>
+      </c>
+      <c r="C38">
+        <v>15</v>
+      </c>
+      <c r="D38">
+        <v>45</v>
+      </c>
+      <c r="E38">
+        <v>30</v>
+      </c>
+      <c r="F38">
+        <v>19</v>
+      </c>
+      <c r="G38">
+        <v>4.5</v>
+      </c>
+      <c r="H38" s="2">
+        <v>8500</v>
+      </c>
+      <c r="I38" s="2">
+        <v>6000</v>
+      </c>
+      <c r="J38" s="2">
+        <v>1000</v>
+      </c>
+      <c r="K38" s="2">
+        <v>24</v>
+      </c>
+      <c r="L38" s="2">
+        <v>7500</v>
+      </c>
+      <c r="M38" s="2">
+        <v>1400</v>
+      </c>
+      <c r="N38" s="2">
+        <v>75</v>
+      </c>
+      <c r="O38" s="2">
+        <v>20</v>
+      </c>
+      <c r="P38" s="2">
+        <v>87</v>
+      </c>
+      <c r="Q38" s="2">
+        <v>15</v>
+      </c>
+      <c r="R38" s="2">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="S38" s="2">
+        <v>15</v>
+      </c>
+      <c r="T38" s="2">
+        <v>120</v>
+      </c>
+      <c r="U38" s="3">
+        <v>2</v>
+      </c>
+      <c r="V38" s="3">
+        <v>1.7</v>
+      </c>
+      <c r="W38" s="3">
+        <v>1.9</v>
+      </c>
+      <c r="X38" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="Y38" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="Z38" s="3">
+        <v>0.81</v>
+      </c>
+      <c r="AA38" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>36</v>
+      </c>
+      <c r="B39" t="s">
+        <v>47</v>
+      </c>
+      <c r="C39">
+        <v>15</v>
+      </c>
+      <c r="D39">
+        <v>45</v>
+      </c>
+      <c r="E39">
+        <v>60</v>
+      </c>
+      <c r="F39">
+        <v>10</v>
+      </c>
+      <c r="G39">
+        <v>10</v>
+      </c>
+      <c r="H39" s="2">
+        <v>4000</v>
+      </c>
+      <c r="I39" s="2">
+        <v>3000</v>
+      </c>
+      <c r="J39" s="2">
+        <v>700</v>
+      </c>
+      <c r="K39" s="2">
         <v>25</v>
       </c>
-      <c r="K33">
-        <v>1400</v>
-      </c>
-      <c r="L33">
-        <v>250</v>
-      </c>
-      <c r="M33">
-        <v>36</v>
-      </c>
-      <c r="N33" s="2">
-        <v>14</v>
-      </c>
-      <c r="O33" s="2">
-        <v>10</v>
-      </c>
-      <c r="P33" s="2">
-        <v>15</v>
-      </c>
-      <c r="Q33" s="2">
-        <v>1.8</v>
-      </c>
-      <c r="R33" s="2">
-        <v>15</v>
-      </c>
-      <c r="S33" s="2">
-        <v>65</v>
-      </c>
-      <c r="T33">
-        <v>6.8</v>
-      </c>
-      <c r="U33">
-        <v>4.25</v>
-      </c>
-      <c r="V33">
-        <v>1.65</v>
-      </c>
-      <c r="W33">
-        <v>0.8</v>
-      </c>
-      <c r="X33">
-        <v>0.8</v>
-      </c>
-      <c r="Y33">
-        <v>0.76</v>
-      </c>
-      <c r="Z33">
-        <v>5</v>
+      <c r="L39" s="2">
+        <v>3300</v>
+      </c>
+      <c r="M39" s="2">
+        <v>1000</v>
+      </c>
+      <c r="N39" s="2">
+        <v>50</v>
+      </c>
+      <c r="O39" s="2">
+        <v>73</v>
+      </c>
+      <c r="P39" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q39" s="2">
+        <v>30</v>
+      </c>
+      <c r="R39" s="6">
+        <v>8.5</v>
+      </c>
+      <c r="S39" s="2">
+        <v>30</v>
+      </c>
+      <c r="T39" s="2">
+        <v>100</v>
+      </c>
+      <c r="U39" s="6">
+        <v>3.1</v>
+      </c>
+      <c r="V39" s="6">
+        <v>2.4</v>
+      </c>
+      <c r="W39" s="6">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="X39" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="Y39" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="Z39" s="3">
+        <v>0.69</v>
+      </c>
+      <c r="AA39" s="6">
+        <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:26" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>23</v>
-      </c>
-      <c r="B34" t="s">
-        <v>46</v>
-      </c>
-      <c r="C34">
-        <v>11.56</v>
-      </c>
-      <c r="D34">
-        <v>40</v>
-      </c>
-      <c r="E34">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="F34">
-        <v>4.5</v>
-      </c>
-      <c r="G34">
-        <v>2700</v>
-      </c>
-      <c r="H34">
-        <v>1400</v>
-      </c>
-      <c r="I34">
-        <v>70</v>
-      </c>
-      <c r="J34">
-        <v>30</v>
-      </c>
-      <c r="K34">
-        <v>2450</v>
-      </c>
-      <c r="L34">
-        <v>350</v>
-      </c>
-      <c r="M34">
-        <v>20</v>
-      </c>
-      <c r="N34">
-        <v>10</v>
-      </c>
-      <c r="O34">
-        <v>20.8</v>
-      </c>
-      <c r="P34">
-        <v>20</v>
-      </c>
-      <c r="Q34">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="R34">
-        <v>20</v>
-      </c>
-      <c r="S34">
-        <v>76</v>
-      </c>
-      <c r="T34">
-        <v>3.88</v>
-      </c>
-      <c r="U34">
-        <v>2.71</v>
-      </c>
-      <c r="V34">
-        <v>1.3</v>
-      </c>
-      <c r="W34">
-        <v>0.8</v>
-      </c>
-      <c r="X34">
-        <v>0.8</v>
-      </c>
-      <c r="Y34">
-        <v>0.74</v>
-      </c>
-      <c r="Z34">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35" spans="1:26" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>22</v>
-      </c>
-      <c r="B35" t="s">
-        <v>46</v>
-      </c>
-      <c r="C35">
-        <v>11.56</v>
-      </c>
-      <c r="D35">
-        <v>40</v>
-      </c>
-      <c r="E35">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="F35">
-        <v>4.5</v>
-      </c>
-      <c r="G35">
-        <v>3600</v>
-      </c>
-      <c r="H35">
-        <v>1600</v>
-      </c>
-      <c r="I35">
-        <v>350</v>
-      </c>
-      <c r="J35">
-        <v>24</v>
-      </c>
-      <c r="K35">
-        <v>3250</v>
-      </c>
-      <c r="L35">
-        <v>400</v>
-      </c>
-      <c r="M35">
-        <v>50</v>
-      </c>
-      <c r="N35">
-        <v>23</v>
-      </c>
-      <c r="O35">
-        <v>10</v>
-      </c>
-      <c r="P35">
-        <v>20</v>
-      </c>
-      <c r="Q35">
-        <v>4.2</v>
-      </c>
-      <c r="R35">
-        <v>20</v>
-      </c>
-      <c r="S35">
-        <v>70</v>
-      </c>
-      <c r="T35">
-        <v>3.85</v>
-      </c>
-      <c r="U35">
-        <v>2.85</v>
-      </c>
-      <c r="V35">
-        <v>1.4</v>
-      </c>
-      <c r="W35">
-        <v>0.5</v>
-      </c>
-      <c r="X35">
-        <v>0.5</v>
-      </c>
-      <c r="Y35">
-        <v>0.74</v>
-      </c>
-      <c r="Z35">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:26" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>24</v>
-      </c>
-      <c r="B36" t="s">
-        <v>46</v>
-      </c>
-      <c r="C36">
-        <v>11.56</v>
-      </c>
-      <c r="D36">
-        <v>30</v>
-      </c>
-      <c r="E36">
-        <v>3.7</v>
-      </c>
-      <c r="F36">
-        <v>4.5</v>
-      </c>
-      <c r="G36" s="2">
-        <v>1200</v>
-      </c>
-      <c r="H36" s="2">
-        <v>1200</v>
-      </c>
-      <c r="I36" s="2">
-        <v>150</v>
-      </c>
-      <c r="J36" s="2">
-        <v>12</v>
-      </c>
-      <c r="K36" s="2">
-        <v>1175</v>
-      </c>
-      <c r="L36" s="2">
-        <v>450</v>
-      </c>
-      <c r="M36" s="2">
-        <v>30</v>
-      </c>
-      <c r="N36" s="2">
-        <v>10</v>
-      </c>
-      <c r="O36" s="2">
-        <v>10</v>
-      </c>
-      <c r="P36">
-        <v>15</v>
-      </c>
-      <c r="Q36">
-        <v>1.4</v>
-      </c>
-      <c r="R36">
-        <v>15</v>
-      </c>
-      <c r="S36">
-        <v>53</v>
-      </c>
-      <c r="T36">
-        <v>3.8</v>
-      </c>
-      <c r="U36">
-        <v>2.7</v>
-      </c>
-      <c r="V36">
-        <v>0.9</v>
-      </c>
-      <c r="W36" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="X36" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="Y36">
-        <v>0.76</v>
-      </c>
-      <c r="Z36">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:26" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>8</v>
-      </c>
-      <c r="B37" t="s">
-        <v>46</v>
-      </c>
-      <c r="C37">
-        <v>11.56</v>
-      </c>
-      <c r="D37">
-        <v>60</v>
-      </c>
-      <c r="E37">
-        <v>7</v>
-      </c>
-      <c r="F37">
-        <v>4.5</v>
-      </c>
-      <c r="G37">
-        <v>3000</v>
-      </c>
-      <c r="H37">
-        <v>2000</v>
-      </c>
-      <c r="I37">
-        <v>300</v>
-      </c>
-      <c r="J37">
-        <v>24</v>
-      </c>
-      <c r="K37">
-        <v>2500</v>
-      </c>
-      <c r="L37">
-        <v>700</v>
-      </c>
-      <c r="M37">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
         <v>35</v>
       </c>
-      <c r="N37">
-        <v>25</v>
-      </c>
-      <c r="O37">
-        <v>10</v>
-      </c>
-      <c r="P37">
-        <v>30</v>
-      </c>
-      <c r="Q37">
-        <v>4.7</v>
-      </c>
-      <c r="R37">
-        <v>30</v>
-      </c>
-      <c r="S37">
-        <v>57</v>
-      </c>
-      <c r="T37">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="U37">
-        <v>2.9</v>
-      </c>
-      <c r="V37">
-        <v>0.85</v>
-      </c>
-      <c r="W37">
-        <v>0.5</v>
-      </c>
-      <c r="X37">
-        <v>0.5</v>
-      </c>
-      <c r="Y37">
-        <v>0.74</v>
-      </c>
-      <c r="Z37">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="38" spans="1:26" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>9</v>
-      </c>
-      <c r="B38" t="s">
-        <v>46</v>
-      </c>
-      <c r="C38">
-        <v>11.56</v>
-      </c>
-      <c r="D38">
-        <v>60</v>
-      </c>
-      <c r="E38">
-        <v>6.2</v>
-      </c>
-      <c r="F38">
-        <v>4.5</v>
-      </c>
-      <c r="G38">
-        <v>2200</v>
-      </c>
-      <c r="H38">
-        <v>1600</v>
-      </c>
-      <c r="I38">
-        <v>300</v>
-      </c>
-      <c r="J38">
-        <v>24</v>
-      </c>
-      <c r="K38">
-        <v>2000</v>
-      </c>
-      <c r="L38">
-        <v>560</v>
-      </c>
-      <c r="M38">
-        <v>32</v>
-      </c>
-      <c r="N38">
-        <v>20</v>
-      </c>
-      <c r="O38">
-        <v>10</v>
-      </c>
-      <c r="P38">
-        <v>30</v>
-      </c>
-      <c r="Q38">
-        <v>4.5</v>
-      </c>
-      <c r="R38">
-        <v>30</v>
-      </c>
-      <c r="S38">
-        <v>54</v>
-      </c>
-      <c r="T38">
-        <v>4.8</v>
-      </c>
-      <c r="U38">
-        <v>3.4</v>
-      </c>
-      <c r="V38">
-        <v>0.85</v>
-      </c>
-      <c r="W38">
-        <v>0.5</v>
-      </c>
-      <c r="X38">
-        <v>0.5</v>
-      </c>
-      <c r="Y38">
-        <v>0.75</v>
-      </c>
-      <c r="Z38">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:26" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>12</v>
-      </c>
-      <c r="B39" t="s">
-        <v>46</v>
-      </c>
-      <c r="C39">
-        <v>11.56</v>
-      </c>
-      <c r="D39">
-        <v>40</v>
-      </c>
-      <c r="E39">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="F39">
-        <v>4.5</v>
-      </c>
-      <c r="G39">
-        <v>4100</v>
-      </c>
-      <c r="H39">
-        <v>2000</v>
-      </c>
-      <c r="I39">
-        <v>350</v>
-      </c>
-      <c r="J39">
-        <v>24</v>
-      </c>
-      <c r="K39">
-        <v>3700</v>
-      </c>
-      <c r="L39">
-        <v>600</v>
-      </c>
-      <c r="M39">
-        <v>90</v>
-      </c>
-      <c r="N39">
-        <v>23</v>
-      </c>
-      <c r="O39">
-        <v>10</v>
-      </c>
-      <c r="P39">
-        <v>20</v>
-      </c>
-      <c r="Q39">
-        <v>4</v>
-      </c>
-      <c r="R39">
-        <v>20</v>
-      </c>
-      <c r="S39">
-        <v>98</v>
-      </c>
-      <c r="T39">
-        <v>2.4</v>
-      </c>
-      <c r="U39">
-        <v>1.8</v>
-      </c>
-      <c r="V39">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="W39">
-        <v>0.5</v>
-      </c>
-      <c r="X39">
-        <v>0.5</v>
-      </c>
-      <c r="Y39">
-        <v>0.73</v>
-      </c>
-      <c r="Z39">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:26" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>20</v>
-      </c>
       <c r="B40" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C40">
-        <v>11.56</v>
+        <v>15</v>
       </c>
       <c r="D40">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="E40">
-        <v>2.9</v>
+        <v>30</v>
       </c>
       <c r="F40">
         <v>4.5</v>
       </c>
       <c r="G40">
-        <v>950</v>
-      </c>
-      <c r="H40">
-        <v>500</v>
-      </c>
-      <c r="I40">
-        <v>70</v>
-      </c>
-      <c r="J40">
-        <v>25</v>
+        <v>10</v>
+      </c>
+      <c r="H40" s="2">
+        <v>2200</v>
+      </c>
+      <c r="I40" s="2">
+        <v>1300</v>
+      </c>
+      <c r="J40" s="2">
+        <v>300</v>
       </c>
       <c r="K40" s="2">
-        <v>875</v>
+        <v>15</v>
       </c>
       <c r="L40" s="2">
-        <v>150</v>
+        <v>1900</v>
       </c>
       <c r="M40" s="2">
+        <v>400</v>
+      </c>
+      <c r="N40" s="2">
+        <v>50</v>
+      </c>
+      <c r="O40" s="2">
+        <v>21.5</v>
+      </c>
+      <c r="P40" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q40" s="2">
+        <v>15</v>
+      </c>
+      <c r="R40" s="6">
+        <v>3.6</v>
+      </c>
+      <c r="S40" s="2">
+        <v>15</v>
+      </c>
+      <c r="T40" s="2">
+        <v>165</v>
+      </c>
+      <c r="U40" s="10">
+        <v>2.8</v>
+      </c>
+      <c r="V40" s="10">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="W40" s="6">
+        <v>1.8</v>
+      </c>
+      <c r="X40" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="Y40" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="Z40" s="3">
+        <v>0.68</v>
+      </c>
+      <c r="AA40" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
         <v>16</v>
       </c>
-      <c r="N40" s="2">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="O40" s="2">
-        <v>10</v>
-      </c>
-      <c r="P40" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q40" s="6">
-        <v>0.9</v>
-      </c>
-      <c r="R40">
-        <v>20</v>
-      </c>
-      <c r="S40" s="2">
+      <c r="B41" t="s">
+        <v>47</v>
+      </c>
+      <c r="C41">
+        <v>15</v>
+      </c>
+      <c r="D41">
         <v>45</v>
       </c>
-      <c r="T40">
-        <v>9.6</v>
-      </c>
-      <c r="U40">
-        <v>6.7</v>
-      </c>
-      <c r="V40" s="4">
-        <v>3.2</v>
-      </c>
-      <c r="W40" s="3">
+      <c r="E41">
+        <v>40</v>
+      </c>
+      <c r="F41">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="G41">
+        <v>10</v>
+      </c>
+      <c r="H41" s="2">
+        <v>2900</v>
+      </c>
+      <c r="I41" s="2">
+        <v>2500</v>
+      </c>
+      <c r="J41" s="2">
+        <v>250</v>
+      </c>
+      <c r="K41" s="2">
+        <v>30</v>
+      </c>
+      <c r="L41" s="2">
+        <v>2800</v>
+      </c>
+      <c r="M41" s="2">
+        <v>400</v>
+      </c>
+      <c r="N41" s="2">
+        <v>30</v>
+      </c>
+      <c r="O41" s="2">
+        <v>41</v>
+      </c>
+      <c r="P41" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q41" s="2">
+        <v>20</v>
+      </c>
+      <c r="R41" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="S41" s="2">
+        <v>20</v>
+      </c>
+      <c r="T41" s="2">
+        <v>203</v>
+      </c>
+      <c r="U41" s="6">
+        <v>3.5</v>
+      </c>
+      <c r="V41" s="6">
+        <v>2.6</v>
+      </c>
+      <c r="W41" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="X41" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="Y41" s="6">
         <v>0.5</v>
       </c>
-      <c r="X40" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="Y40" s="3">
-        <v>0.82</v>
-      </c>
-      <c r="Z40" s="3">
-        <v>10</v>
+      <c r="Z41" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="AA41" s="6">
+        <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:26" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>26</v>
-      </c>
-      <c r="B41" t="s">
-        <v>46</v>
-      </c>
-      <c r="C41">
-        <v>11.56</v>
-      </c>
-      <c r="D41">
-        <v>30</v>
-      </c>
-      <c r="E41">
-        <v>9.6</v>
-      </c>
-      <c r="F41">
-        <v>4.5</v>
-      </c>
-      <c r="G41" s="2">
-        <v>3000</v>
-      </c>
-      <c r="H41" s="2">
-        <v>3000</v>
-      </c>
-      <c r="I41" s="2">
-        <v>500</v>
-      </c>
-      <c r="J41" s="2">
-        <v>12</v>
-      </c>
-      <c r="K41" s="2">
-        <v>2975</v>
-      </c>
-      <c r="L41" s="2">
-        <v>1200</v>
-      </c>
-      <c r="M41" s="2">
-        <v>200</v>
-      </c>
-      <c r="N41" s="2">
-        <v>25</v>
-      </c>
-      <c r="O41" s="2">
-        <v>10</v>
-      </c>
-      <c r="P41">
-        <v>15</v>
-      </c>
-      <c r="Q41">
-        <v>3.9</v>
-      </c>
-      <c r="R41">
-        <v>15</v>
-      </c>
-      <c r="S41">
-        <v>95</v>
-      </c>
-      <c r="T41">
-        <v>1.5</v>
-      </c>
-      <c r="U41">
-        <v>0.95</v>
-      </c>
-      <c r="V41">
-        <v>0.42</v>
-      </c>
-      <c r="W41" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="X41" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="Y41">
-        <v>0.73</v>
-      </c>
-      <c r="Z41">
-        <v>5</v>
+    <row r="42" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>109</v>
+      </c>
+      <c r="B42" t="s">
+        <v>47</v>
+      </c>
+      <c r="C42">
+        <v>15</v>
+      </c>
+      <c r="D42">
+        <v>45</v>
+      </c>
+      <c r="E42">
+        <v>40</v>
+      </c>
+      <c r="F42">
+        <v>5.5</v>
+      </c>
+      <c r="G42">
+        <v>10</v>
+      </c>
+      <c r="H42" s="2">
+        <v>2200</v>
+      </c>
+      <c r="I42" s="2">
+        <v>2400</v>
+      </c>
+      <c r="J42" s="2">
+        <v>300</v>
+      </c>
+      <c r="K42" s="2">
+        <v>15</v>
+      </c>
+      <c r="L42" s="2">
+        <v>2000</v>
+      </c>
+      <c r="M42" s="2">
+        <v>900</v>
+      </c>
+      <c r="N42" s="2">
+        <v>28</v>
+      </c>
+      <c r="O42" s="2">
+        <v>42</v>
+      </c>
+      <c r="P42" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q42" s="2">
+        <v>20</v>
+      </c>
+      <c r="R42" s="6">
+        <v>3.6</v>
+      </c>
+      <c r="S42" s="2">
+        <v>20</v>
+      </c>
+      <c r="T42" s="2">
+        <v>170</v>
+      </c>
+      <c r="U42" s="6">
+        <v>2.4</v>
+      </c>
+      <c r="V42" s="6">
+        <v>1.8</v>
+      </c>
+      <c r="W42" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="X42" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y42" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z42" s="3">
+        <v>0.84</v>
+      </c>
+      <c r="AA42" s="2">
+        <v>50</v>
       </c>
     </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>27</v>
-      </c>
-      <c r="B42" t="s">
-        <v>46</v>
-      </c>
-      <c r="C42">
-        <v>11.56</v>
-      </c>
-      <c r="D42">
-        <v>30</v>
-      </c>
-      <c r="E42">
-        <v>11.3</v>
-      </c>
-      <c r="F42">
-        <v>4.5</v>
-      </c>
-      <c r="G42" s="2">
-        <v>4000</v>
-      </c>
-      <c r="H42" s="2">
-        <v>3000</v>
-      </c>
-      <c r="I42" s="2">
-        <v>500</v>
-      </c>
-      <c r="J42" s="2">
-        <v>12</v>
-      </c>
-      <c r="K42" s="2">
-        <v>3500</v>
-      </c>
-      <c r="L42" s="2">
-        <v>1400</v>
-      </c>
-      <c r="M42" s="2">
-        <v>100</v>
-      </c>
-      <c r="N42" s="2">
-        <v>34</v>
-      </c>
-      <c r="O42" s="2">
-        <v>10</v>
-      </c>
-      <c r="P42">
-        <v>15</v>
-      </c>
-      <c r="Q42">
-        <v>3</v>
-      </c>
-      <c r="R42">
-        <v>15</v>
-      </c>
-      <c r="S42">
-        <v>117</v>
-      </c>
-      <c r="T42">
-        <v>1.25</v>
-      </c>
-      <c r="U42">
-        <v>0.88</v>
-      </c>
-      <c r="V42">
-        <v>0.75</v>
-      </c>
-      <c r="W42" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="X42" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="Y42">
-        <v>0.73</v>
-      </c>
-      <c r="Z42">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:26" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="B43" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C43">
-        <v>11.56</v>
+        <v>15</v>
       </c>
       <c r="D43">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E43">
-        <v>11.2</v>
+        <v>40</v>
       </c>
       <c r="F43">
-        <v>4.5</v>
-      </c>
-      <c r="G43" s="2">
-        <v>4000</v>
+        <v>4.8</v>
+      </c>
+      <c r="G43">
+        <v>10</v>
       </c>
       <c r="H43" s="2">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="I43" s="2">
-        <v>550</v>
+        <v>2000</v>
       </c>
       <c r="J43" s="2">
-        <v>15</v>
+        <v>300</v>
       </c>
       <c r="K43" s="2">
-        <v>3700</v>
+        <v>15</v>
       </c>
       <c r="L43" s="2">
         <v>1800</v>
       </c>
       <c r="M43" s="2">
-        <v>160</v>
+        <v>750</v>
       </c>
       <c r="N43" s="2">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="O43" s="2">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="P43" s="2">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="Q43" s="2">
-        <v>5.8</v>
-      </c>
-      <c r="R43" s="2">
-        <v>15</v>
+        <v>20</v>
+      </c>
+      <c r="R43" s="6">
+        <v>4.0999999999999996</v>
       </c>
       <c r="S43" s="2">
-        <v>84</v>
-      </c>
-      <c r="T43" s="3">
-        <v>1.75</v>
-      </c>
-      <c r="U43" s="3">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="V43" s="3">
-        <v>0.6</v>
+        <v>20</v>
+      </c>
+      <c r="T43" s="2">
+        <v>150</v>
+      </c>
+      <c r="U43" s="6">
+        <v>3.3</v>
+      </c>
+      <c r="V43" s="6">
+        <v>2.5</v>
       </c>
       <c r="W43" s="3">
         <v>0.8</v>
       </c>
-      <c r="X43" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="Y43" s="3">
-        <v>0.45</v>
+      <c r="X43" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y43" s="6">
+        <v>1</v>
       </c>
       <c r="Z43" s="3">
-        <v>10</v>
+        <v>0.88</v>
+      </c>
+      <c r="AA43" s="2">
+        <v>50</v>
       </c>
     </row>
-    <row r="44" spans="1:26" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B44" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C44">
-        <v>11.56</v>
+        <v>15</v>
       </c>
       <c r="D44">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="E44">
+        <v>40</v>
+      </c>
+      <c r="F44">
         <v>2.1</v>
       </c>
-      <c r="F44">
-        <v>4.5</v>
-      </c>
-      <c r="G44" s="2">
-        <v>735</v>
+      <c r="G44">
+        <v>10</v>
       </c>
       <c r="H44" s="2">
-        <v>680</v>
+        <v>750</v>
       </c>
       <c r="I44" s="2">
+        <v>900</v>
+      </c>
+      <c r="J44" s="2">
         <v>100</v>
       </c>
-      <c r="J44" s="2">
+      <c r="K44" s="2">
+        <v>25</v>
+      </c>
+      <c r="L44" s="2">
+        <v>650</v>
+      </c>
+      <c r="M44" s="2">
+        <v>190</v>
+      </c>
+      <c r="N44" s="2">
         <v>12</v>
       </c>
-      <c r="K44" s="2">
-        <v>640</v>
-      </c>
-      <c r="L44" s="2">
-        <v>310</v>
-      </c>
-      <c r="M44" s="2">
-        <v>21</v>
-      </c>
-      <c r="N44" s="2">
-        <v>10</v>
-      </c>
       <c r="O44" s="2">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="P44" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Q44" s="2">
-        <v>0.7</v>
-      </c>
-      <c r="R44" s="2">
-        <v>15</v>
+        <v>20</v>
+      </c>
+      <c r="R44" s="6">
+        <v>1.4</v>
       </c>
       <c r="S44" s="2">
-        <v>37</v>
-      </c>
-      <c r="T44" s="6">
-        <v>11</v>
+        <v>20</v>
+      </c>
+      <c r="T44" s="2">
+        <v>100</v>
       </c>
       <c r="U44" s="6">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="V44" s="6">
+        <v>4.7</v>
+      </c>
+      <c r="W44" s="6">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="X44" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y44" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z44" s="3">
+        <v>0.92</v>
+      </c>
+      <c r="AA44" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="45" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>14</v>
+      </c>
+      <c r="B45" t="s">
+        <v>47</v>
+      </c>
+      <c r="C45">
+        <v>15</v>
+      </c>
+      <c r="D45">
+        <v>45</v>
+      </c>
+      <c r="E45">
+        <v>40</v>
+      </c>
+      <c r="F45">
+        <v>7.6</v>
+      </c>
+      <c r="G45">
+        <v>10</v>
+      </c>
+      <c r="H45" s="2">
+        <v>2400</v>
+      </c>
+      <c r="I45" s="2">
+        <v>1800</v>
+      </c>
+      <c r="J45" s="2">
+        <v>300</v>
+      </c>
+      <c r="K45" s="2">
+        <v>30</v>
+      </c>
+      <c r="L45" s="2">
+        <v>2200</v>
+      </c>
+      <c r="M45" s="2">
+        <v>380</v>
+      </c>
+      <c r="N45" s="2">
+        <v>15</v>
+      </c>
+      <c r="O45" s="2">
+        <v>23</v>
+      </c>
+      <c r="P45" s="2">
+        <v>42</v>
+      </c>
+      <c r="Q45" s="2">
+        <v>20</v>
+      </c>
+      <c r="R45" s="6">
+        <v>3.2</v>
+      </c>
+      <c r="S45" s="2">
+        <v>20</v>
+      </c>
+      <c r="T45" s="2">
+        <v>96</v>
+      </c>
+      <c r="U45" s="6">
+        <v>6.8</v>
+      </c>
+      <c r="V45" s="6">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="W45" s="6">
         <v>1.4</v>
       </c>
-      <c r="W44" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="X44" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="Y44" s="6">
-        <v>0.8</v>
-      </c>
-      <c r="Z44" s="6">
-        <v>10</v>
+      <c r="X45" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y45" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z45" s="3">
+        <v>0.88</v>
+      </c>
+      <c r="AA45" s="2">
+        <v>50</v>
       </c>
     </row>
-    <row r="45" spans="1:26" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>34</v>
-      </c>
-      <c r="B45" t="s">
-        <v>46</v>
-      </c>
-      <c r="C45">
-        <v>11.56</v>
-      </c>
-      <c r="D45">
-        <v>30</v>
-      </c>
-      <c r="E45">
+    <row r="46" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>111</v>
+      </c>
+      <c r="B46" t="s">
+        <v>47</v>
+      </c>
+      <c r="C46">
+        <v>15</v>
+      </c>
+      <c r="D46">
+        <v>45</v>
+      </c>
+      <c r="E46">
+        <v>40</v>
+      </c>
+      <c r="F46">
+        <v>7</v>
+      </c>
+      <c r="G46">
+        <v>10</v>
+      </c>
+      <c r="H46" s="2">
+        <v>1900</v>
+      </c>
+      <c r="I46" s="2">
+        <v>2000</v>
+      </c>
+      <c r="J46" s="2">
+        <v>300</v>
+      </c>
+      <c r="K46" s="2">
+        <v>15</v>
+      </c>
+      <c r="L46" s="2">
+        <v>1600</v>
+      </c>
+      <c r="M46" s="2">
+        <v>780</v>
+      </c>
+      <c r="N46" s="2">
+        <v>80</v>
+      </c>
+      <c r="O46" s="2">
+        <v>23</v>
+      </c>
+      <c r="P46" s="2">
+        <v>50</v>
+      </c>
+      <c r="Q46" s="2">
+        <v>20</v>
+      </c>
+      <c r="R46" s="6">
+        <v>4</v>
+      </c>
+      <c r="S46" s="2">
+        <v>20</v>
+      </c>
+      <c r="T46" s="2">
+        <v>140</v>
+      </c>
+      <c r="U46" s="6">
+        <v>3.1</v>
+      </c>
+      <c r="V46" s="6">
+        <v>2.7</v>
+      </c>
+      <c r="W46" s="3">
         <v>2.8</v>
       </c>
-      <c r="F45">
-        <v>4.5</v>
-      </c>
-      <c r="G45" s="2">
-        <v>1060</v>
-      </c>
-      <c r="H45" s="2">
-        <v>900</v>
-      </c>
-      <c r="I45" s="2">
-        <v>140</v>
-      </c>
-      <c r="J45" s="2">
-        <v>10</v>
-      </c>
-      <c r="K45" s="2">
-        <v>960</v>
-      </c>
-      <c r="L45" s="2">
-        <v>460</v>
-      </c>
-      <c r="M45" s="2">
+      <c r="X46" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y46" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z46" s="3">
+        <v>0.89</v>
+      </c>
+      <c r="AA46" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="47" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>112</v>
+      </c>
+      <c r="B47" t="s">
+        <v>47</v>
+      </c>
+      <c r="C47">
+        <v>15</v>
+      </c>
+      <c r="D47">
+        <v>45</v>
+      </c>
+      <c r="E47">
         <v>40</v>
-      </c>
-      <c r="N45" s="2">
-        <v>30</v>
-      </c>
-      <c r="O45" s="2">
-        <v>15</v>
-      </c>
-      <c r="P45" s="2">
-        <v>15</v>
-      </c>
-      <c r="Q45" s="6">
-        <v>1.2</v>
-      </c>
-      <c r="R45" s="2">
-        <v>15</v>
-      </c>
-      <c r="S45" s="2">
-        <v>46</v>
-      </c>
-      <c r="T45" s="6">
-        <v>7.87</v>
-      </c>
-      <c r="U45" s="6">
-        <v>5.63</v>
-      </c>
-      <c r="V45" s="6">
-        <v>0.8</v>
-      </c>
-      <c r="W45" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="X45" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="Y45" s="6">
-        <v>0.85</v>
-      </c>
-      <c r="Z45" s="6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="46" spans="1:26" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>38</v>
-      </c>
-      <c r="B46" t="s">
-        <v>49</v>
-      </c>
-      <c r="C46">
-        <v>11.56</v>
-      </c>
-      <c r="D46">
-        <v>30</v>
-      </c>
-      <c r="E46">
-        <v>5.5</v>
-      </c>
-      <c r="F46">
-        <v>5</v>
-      </c>
-      <c r="G46" s="2">
-        <v>1500</v>
-      </c>
-      <c r="H46" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I46" s="2">
-        <v>200</v>
-      </c>
-      <c r="J46" s="2">
-        <v>10</v>
-      </c>
-      <c r="K46" s="2">
-        <v>1450</v>
-      </c>
-      <c r="L46" s="2">
-        <v>700</v>
-      </c>
-      <c r="M46" s="2">
-        <v>48</v>
-      </c>
-      <c r="N46" s="2">
-        <v>6</v>
-      </c>
-      <c r="O46" s="2">
-        <v>15</v>
-      </c>
-      <c r="P46" s="2">
-        <v>15</v>
-      </c>
-      <c r="Q46" s="6">
-        <v>1.7</v>
-      </c>
-      <c r="R46" s="2">
-        <v>15</v>
-      </c>
-      <c r="S46" s="2">
-        <v>61</v>
-      </c>
-      <c r="T46" s="6">
-        <v>2.9</v>
-      </c>
-      <c r="U46" s="6">
-        <v>2</v>
-      </c>
-      <c r="V46" s="6">
-        <v>0.9</v>
-      </c>
-      <c r="W46" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="X46" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="Y46" s="3">
-        <v>0.85</v>
-      </c>
-      <c r="Z46" s="6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="47" spans="1:26" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>37</v>
-      </c>
-      <c r="B47" t="s">
-        <v>49</v>
-      </c>
-      <c r="C47">
-        <v>11.56</v>
-      </c>
-      <c r="D47">
-        <v>30</v>
-      </c>
-      <c r="E47">
-        <v>3.8</v>
       </c>
       <c r="F47">
         <v>5</v>
       </c>
-      <c r="G47" s="2">
-        <v>1050</v>
+      <c r="G47">
+        <v>10</v>
       </c>
       <c r="H47" s="2">
-        <v>1000</v>
+        <v>1400</v>
       </c>
       <c r="I47" s="2">
-        <v>150</v>
+        <v>1500</v>
       </c>
       <c r="J47" s="2">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="K47" s="2">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="L47" s="2">
-        <v>460</v>
+        <v>1100</v>
       </c>
       <c r="M47" s="2">
-        <v>39</v>
+        <v>580</v>
       </c>
       <c r="N47" s="2">
+        <v>60</v>
+      </c>
+      <c r="O47" s="2">
+        <v>19</v>
+      </c>
+      <c r="P47" s="2">
+        <v>50</v>
+      </c>
+      <c r="Q47" s="2">
+        <v>20</v>
+      </c>
+      <c r="R47" s="6">
         <v>3</v>
       </c>
-      <c r="O47" s="2">
-        <v>15</v>
-      </c>
-      <c r="P47" s="2">
-        <v>15</v>
-      </c>
-      <c r="Q47" s="6">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="R47" s="2">
-        <v>15</v>
-      </c>
       <c r="S47" s="2">
-        <v>57</v>
-      </c>
-      <c r="T47" s="6">
-        <v>4.4000000000000004</v>
+        <v>20</v>
+      </c>
+      <c r="T47" s="2">
+        <v>100</v>
       </c>
       <c r="U47" s="6">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="V47" s="6">
-        <v>1.2</v>
-      </c>
-      <c r="W47" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="X47" s="6">
-        <v>0.5</v>
+        <v>3.5</v>
+      </c>
+      <c r="W47" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="X47" s="3">
+        <v>1</v>
       </c>
       <c r="Y47" s="3">
-        <v>0.85</v>
-      </c>
-      <c r="Z47" s="6">
-        <v>15</v>
+        <v>1</v>
+      </c>
+      <c r="Z47" s="3">
+        <v>0.88</v>
+      </c>
+      <c r="AA47" s="2">
+        <v>35</v>
       </c>
     </row>
-    <row r="48" spans="1:26" hidden="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>114</v>
+        <v>13</v>
       </c>
       <c r="B48" t="s">
         <v>47</v>
       </c>
       <c r="C48">
+        <v>15</v>
+      </c>
+      <c r="D48">
         <v>45</v>
       </c>
-      <c r="D48">
+      <c r="E48">
         <v>40</v>
       </c>
-      <c r="E48">
+      <c r="F48">
+        <v>6.3</v>
+      </c>
+      <c r="G48">
+        <v>4.5</v>
+      </c>
+      <c r="H48" s="2">
+        <v>2100</v>
+      </c>
+      <c r="I48" s="2">
+        <v>1400</v>
+      </c>
+      <c r="J48" s="2">
+        <v>150</v>
+      </c>
+      <c r="K48" s="2">
+        <v>24</v>
+      </c>
+      <c r="L48" s="2">
+        <v>2000</v>
+      </c>
+      <c r="M48" s="2">
+        <v>350</v>
+      </c>
+      <c r="N48" s="2">
+        <v>14</v>
+      </c>
+      <c r="O48" s="2">
         <v>13</v>
       </c>
-      <c r="F48">
-        <v>10</v>
-      </c>
-      <c r="G48" s="2">
-        <v>3600</v>
-      </c>
-      <c r="H48" s="2">
-        <v>3800</v>
-      </c>
-      <c r="I48" s="2">
-        <v>1000</v>
-      </c>
-      <c r="J48" s="2">
-        <v>15</v>
-      </c>
-      <c r="K48" s="2">
-        <v>2900</v>
-      </c>
-      <c r="L48" s="2">
-        <v>380</v>
-      </c>
-      <c r="M48" s="2">
-        <v>270</v>
-      </c>
-      <c r="N48" s="2">
-        <v>41</v>
-      </c>
-      <c r="O48" s="2">
-        <v>40</v>
-      </c>
       <c r="P48" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q48" s="6">
-        <v>15</v>
-      </c>
-      <c r="R48" s="2">
-        <v>20</v>
-      </c>
-      <c r="S48" s="11">
-        <v>100</v>
-      </c>
-      <c r="T48" s="6">
-        <v>20</v>
-      </c>
-      <c r="U48" s="6">
-        <v>2.5</v>
+        <v>10</v>
+      </c>
+      <c r="Q48" s="2">
+        <v>20</v>
+      </c>
+      <c r="R48" s="6">
+        <v>2.1</v>
+      </c>
+      <c r="S48" s="2">
+        <v>20</v>
+      </c>
+      <c r="T48" s="2">
+        <v>50</v>
+      </c>
+      <c r="U48" s="3">
+        <v>5</v>
       </c>
       <c r="V48" s="3">
-        <v>2.1</v>
-      </c>
-      <c r="W48" s="6">
-        <v>1</v>
-      </c>
-      <c r="X48" s="6">
+        <v>3.5</v>
+      </c>
+      <c r="W48" s="3">
+        <v>1.45</v>
+      </c>
+      <c r="X48" s="3">
         <v>1</v>
       </c>
       <c r="Y48" s="3">
-        <v>0.83</v>
-      </c>
-      <c r="Z48" s="2">
-        <v>40</v>
+        <v>1</v>
+      </c>
+      <c r="Z48" s="3">
+        <v>0.74</v>
+      </c>
+      <c r="AA48" s="2">
+        <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:26" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>115</v>
+        <v>18</v>
       </c>
       <c r="B49" t="s">
         <v>47</v>
       </c>
       <c r="C49">
+        <v>15</v>
+      </c>
+      <c r="D49">
         <v>45</v>
       </c>
-      <c r="D49">
+      <c r="E49">
+        <v>30</v>
+      </c>
+      <c r="F49">
+        <v>4.5</v>
+      </c>
+      <c r="G49">
+        <v>4.5</v>
+      </c>
+      <c r="H49" s="2">
+        <v>1600</v>
+      </c>
+      <c r="I49" s="2">
+        <v>1500</v>
+      </c>
+      <c r="J49" s="2">
+        <v>200</v>
+      </c>
+      <c r="K49" s="2">
+        <v>15</v>
+      </c>
+      <c r="L49" s="2">
+        <v>1500</v>
+      </c>
+      <c r="M49" s="2">
+        <v>520</v>
+      </c>
+      <c r="N49" s="2">
+        <v>38</v>
+      </c>
+      <c r="O49" s="2">
+        <v>13</v>
+      </c>
+      <c r="P49" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q49" s="2">
+        <v>15</v>
+      </c>
+      <c r="R49" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="S49" s="2">
+        <v>15</v>
+      </c>
+      <c r="T49" s="2">
+        <v>80</v>
+      </c>
+      <c r="U49" s="6">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="V49" s="6">
+        <v>2.8</v>
+      </c>
+      <c r="W49" s="3">
+        <v>1.4</v>
+      </c>
+      <c r="X49" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y49" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z49" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="AA49" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>114</v>
+      </c>
+      <c r="B50" t="s">
+        <v>47</v>
+      </c>
+      <c r="C50">
+        <v>15</v>
+      </c>
+      <c r="D50">
+        <v>45</v>
+      </c>
+      <c r="E50">
         <v>40</v>
       </c>
-      <c r="E49">
+      <c r="F50">
+        <v>13</v>
+      </c>
+      <c r="G50">
+        <v>10</v>
+      </c>
+      <c r="H50" s="2">
+        <v>3600</v>
+      </c>
+      <c r="I50" s="2">
+        <v>3800</v>
+      </c>
+      <c r="J50" s="2">
+        <v>1000</v>
+      </c>
+      <c r="K50" s="2">
+        <v>15</v>
+      </c>
+      <c r="L50" s="2">
+        <v>2900</v>
+      </c>
+      <c r="M50" s="2">
+        <v>380</v>
+      </c>
+      <c r="N50" s="2">
+        <v>270</v>
+      </c>
+      <c r="O50" s="2">
+        <v>41</v>
+      </c>
+      <c r="P50" s="2">
+        <v>40</v>
+      </c>
+      <c r="Q50" s="2">
+        <v>20</v>
+      </c>
+      <c r="R50" s="6">
+        <v>15</v>
+      </c>
+      <c r="S50" s="2">
+        <v>20</v>
+      </c>
+      <c r="T50" s="11">
+        <v>100</v>
+      </c>
+      <c r="U50" s="6">
+        <v>20</v>
+      </c>
+      <c r="V50" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="W50" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="X50" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y50" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z50" s="3">
+        <v>0.83</v>
+      </c>
+      <c r="AA50" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="51" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>115</v>
+      </c>
+      <c r="B51" t="s">
+        <v>47</v>
+      </c>
+      <c r="C51">
+        <v>15</v>
+      </c>
+      <c r="D51">
+        <v>45</v>
+      </c>
+      <c r="E51">
+        <v>40</v>
+      </c>
+      <c r="F51">
         <v>16</v>
       </c>
-      <c r="F49">
-        <v>10</v>
-      </c>
-      <c r="G49" s="2">
+      <c r="G51">
+        <v>10</v>
+      </c>
+      <c r="H51" s="2">
         <v>5000</v>
       </c>
-      <c r="H49" s="2">
+      <c r="I51" s="2">
         <v>4000</v>
       </c>
-      <c r="I49" s="2">
+      <c r="J51" s="2">
         <v>1100</v>
       </c>
-      <c r="J49" s="2">
-        <v>15</v>
-      </c>
-      <c r="K49" s="2">
+      <c r="K51" s="2">
+        <v>15</v>
+      </c>
+      <c r="L51" s="2">
         <v>3300</v>
       </c>
-      <c r="L49" s="2">
+      <c r="M51" s="2">
         <v>460</v>
       </c>
-      <c r="M49" s="2">
+      <c r="N51" s="2">
         <v>300</v>
       </c>
-      <c r="N49" s="2">
+      <c r="O51" s="2">
         <v>48</v>
       </c>
-      <c r="O49" s="2">
+      <c r="P51" s="2">
         <v>40</v>
       </c>
-      <c r="P49" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q49" s="6">
+      <c r="Q51" s="2">
+        <v>20</v>
+      </c>
+      <c r="R51" s="6">
         <v>16</v>
       </c>
-      <c r="R49" s="2">
-        <v>20</v>
-      </c>
-      <c r="S49" s="11">
+      <c r="S51" s="2">
+        <v>20</v>
+      </c>
+      <c r="T51" s="11">
         <v>100</v>
       </c>
-      <c r="T49" s="6">
+      <c r="U51" s="6">
         <v>7</v>
       </c>
-      <c r="U49" s="6">
+      <c r="V51" s="6">
         <v>1.86</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W51" s="3">
         <v>1.7</v>
       </c>
-      <c r="W49" s="6">
-        <v>1</v>
-      </c>
-      <c r="X49" s="6">
-        <v>1</v>
-      </c>
-      <c r="Y49" s="3">
+      <c r="X51" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z51" s="3">
         <v>0.83</v>
       </c>
-      <c r="Z49" s="2">
+      <c r="AA51" s="2">
         <v>50</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:Z49" xr:uid="{E69B3F4A-D7AE-43B6-8CEC-20724C077B7B}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="SIRA62DDP"/>
-        <filter val="SISS54DN"/>
-      </filters>
-    </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:Z49">
-      <sortCondition ref="D4:D49"/>
+  <autoFilter ref="A4:AA51" xr:uid="{E69B3F4A-D7AE-43B6-8CEC-20724C077B7B}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:AA51">
+      <sortCondition ref="B4:B51"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/mosfet_data.xlsx
+++ b/data/mosfet_data.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://renesasgroup-my.sharepoint.com/personal/gary_kidwell_wz_renesas_com/Documents/python/charger/mathmodels/pdis_2or3lvl_bb/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="663" documentId="13_ncr:1_{B6E73BC3-DAD1-4207-9F29-342E0D899D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFAAD25C-EA45-4727-9926-51328176FE62}"/>
+  <xr:revisionPtr revIDLastSave="791" documentId="13_ncr:1_{B6E73BC3-DAD1-4207-9F29-342E0D899D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{724EC80C-90C0-EC47-A234-2C17DD402888}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="39120" yWindow="7280" windowWidth="37000" windowHeight="15700" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="column_data_old" sheetId="1" r:id="rId1"/>
     <sheet name="transpose" sheetId="5" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">transpose!$A$4:$AA$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">transpose!$A$4:$AA$55</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="124">
   <si>
     <t>description</t>
   </si>
@@ -403,6 +403,18 @@
   </si>
   <si>
     <t>degC/W</t>
+  </si>
+  <si>
+    <t>AONR36366</t>
+  </si>
+  <si>
+    <t>AON6380</t>
+  </si>
+  <si>
+    <t>AONS36333</t>
+  </si>
+  <si>
+    <t>SIRA06DDP</t>
   </si>
 </sst>
 </file>
@@ -493,6 +505,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -793,24 +809,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AQ26"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="41.85546875" customWidth="1"/>
-    <col min="11" max="11" width="16.85546875" customWidth="1"/>
-    <col min="12" max="13" width="15.7109375" customWidth="1"/>
-    <col min="15" max="15" width="16.140625" customWidth="1"/>
-    <col min="16" max="16" width="15.5703125" customWidth="1"/>
-    <col min="17" max="19" width="14.28515625" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" customWidth="1"/>
-    <col min="25" max="26" width="11.85546875" customWidth="1"/>
-    <col min="33" max="33" width="17.140625" customWidth="1"/>
-    <col min="40" max="40" width="15.140625" customWidth="1"/>
-    <col min="41" max="41" width="15.7109375" customWidth="1"/>
-    <col min="42" max="42" width="13.28515625" customWidth="1"/>
-    <col min="43" max="43" width="13.42578125" customWidth="1"/>
+    <col min="1" max="1" width="41.83203125" customWidth="1"/>
+    <col min="11" max="11" width="16.83203125" customWidth="1"/>
+    <col min="12" max="13" width="15.6640625" customWidth="1"/>
+    <col min="15" max="15" width="16.1640625" customWidth="1"/>
+    <col min="16" max="16" width="15.5" customWidth="1"/>
+    <col min="17" max="19" width="14.33203125" customWidth="1"/>
+    <col min="22" max="22" width="14.83203125" customWidth="1"/>
+    <col min="25" max="26" width="11.83203125" customWidth="1"/>
+    <col min="33" max="33" width="17.1640625" customWidth="1"/>
+    <col min="40" max="40" width="15.1640625" customWidth="1"/>
+    <col min="41" max="41" width="15.6640625" customWidth="1"/>
+    <col min="42" max="42" width="13.33203125" customWidth="1"/>
+    <col min="43" max="43" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -941,7 +957,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>43</v>
       </c>
@@ -1072,7 +1088,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>52</v>
       </c>
@@ -1205,7 +1221,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>55</v>
       </c>
@@ -1336,7 +1352,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>58</v>
       </c>
@@ -1467,7 +1483,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>61</v>
       </c>
@@ -1598,7 +1614,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>63</v>
       </c>
@@ -1729,7 +1745,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>66</v>
       </c>
@@ -1860,7 +1876,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>68</v>
       </c>
@@ -1991,7 +2007,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>70</v>
       </c>
@@ -2122,7 +2138,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>72</v>
       </c>
@@ -2253,7 +2269,7 @@
         <v>2250</v>
       </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>74</v>
       </c>
@@ -2384,7 +2400,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>76</v>
       </c>
@@ -2515,7 +2531,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>78</v>
       </c>
@@ -2646,7 +2662,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>80</v>
       </c>
@@ -2777,7 +2793,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>83</v>
       </c>
@@ -2908,7 +2924,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>85</v>
       </c>
@@ -3039,7 +3055,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="18" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>87</v>
       </c>
@@ -3170,7 +3186,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>89</v>
       </c>
@@ -3301,7 +3317,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="20" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>92</v>
       </c>
@@ -3432,7 +3448,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="21" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>95</v>
       </c>
@@ -3563,7 +3579,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="22" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>97</v>
       </c>
@@ -3694,7 +3710,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="23" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
         <v>100</v>
       </c>
@@ -3825,7 +3841,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="24" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
         <v>103</v>
       </c>
@@ -3956,7 +3972,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="25" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
         <v>105</v>
       </c>
@@ -4087,7 +4103,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="26" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:43" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
         <v>107</v>
       </c>
@@ -4231,29 +4247,30 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E69B3F4A-D7AE-43B6-8CEC-20724C077B7B}">
-  <dimension ref="A1:AA51"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:AA55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" customWidth="1"/>
-    <col min="5" max="6" width="15.5703125" customWidth="1"/>
-    <col min="7" max="7" width="16.5703125" customWidth="1"/>
-    <col min="11" max="11" width="15.85546875" customWidth="1"/>
-    <col min="12" max="12" width="10.140625" customWidth="1"/>
-    <col min="13" max="13" width="10.42578125" customWidth="1"/>
-    <col min="14" max="14" width="9.85546875" customWidth="1"/>
-    <col min="16" max="16" width="13.85546875" customWidth="1"/>
-    <col min="17" max="17" width="12.28515625" customWidth="1"/>
-    <col min="19" max="19" width="12.42578125" customWidth="1"/>
-    <col min="22" max="22" width="11.140625" customWidth="1"/>
-    <col min="24" max="24" width="11.140625" customWidth="1"/>
-    <col min="25" max="25" width="11.5703125" customWidth="1"/>
-    <col min="26" max="26" width="15.7109375" customWidth="1"/>
+    <col min="2" max="3" width="12.6640625" customWidth="1"/>
+    <col min="4" max="4" width="11.33203125" customWidth="1"/>
+    <col min="5" max="6" width="15.5" customWidth="1"/>
+    <col min="7" max="7" width="16.5" customWidth="1"/>
+    <col min="11" max="11" width="15.83203125" customWidth="1"/>
+    <col min="12" max="12" width="10.1640625" customWidth="1"/>
+    <col min="13" max="13" width="10.5" customWidth="1"/>
+    <col min="14" max="14" width="9.83203125" customWidth="1"/>
+    <col min="16" max="16" width="13.83203125" customWidth="1"/>
+    <col min="17" max="17" width="12.33203125" customWidth="1"/>
+    <col min="19" max="19" width="12.5" customWidth="1"/>
+    <col min="22" max="22" width="11.1640625" customWidth="1"/>
+    <col min="24" max="24" width="11.1640625" customWidth="1"/>
+    <col min="25" max="25" width="11.5" customWidth="1"/>
+    <col min="26" max="26" width="15.6640625" customWidth="1"/>
     <col min="27" max="27" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -4336,7 +4353,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -4419,7 +4436,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -4502,7 +4519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="51" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" ht="56" x14ac:dyDescent="0.15">
       <c r="A4" s="8" t="s">
         <v>0</v>
       </c>
@@ -4585,51 +4602,51 @@
         <v>107</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C5">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D5">
-        <v>11.56</v>
+        <v>45</v>
       </c>
       <c r="E5">
         <v>30</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="G5">
         <v>10</v>
       </c>
       <c r="H5" s="2">
-        <v>1700</v>
+        <v>1250</v>
       </c>
       <c r="I5" s="2">
-        <v>1050</v>
+        <v>1100</v>
       </c>
       <c r="J5" s="2">
         <v>200</v>
       </c>
       <c r="K5" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L5" s="2">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="M5" s="2">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="N5" s="2">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="O5" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P5" s="2">
         <v>20</v>
@@ -4638,81 +4655,81 @@
         <v>15</v>
       </c>
       <c r="R5" s="6">
-        <v>2.2000000000000002</v>
+        <v>3</v>
       </c>
       <c r="S5" s="2">
         <v>15</v>
       </c>
       <c r="T5" s="2">
-        <v>108</v>
-      </c>
-      <c r="U5" s="3">
-        <v>3.7</v>
-      </c>
-      <c r="V5" s="3">
-        <v>3.05</v>
-      </c>
-      <c r="W5" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="X5" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="Y5" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="Z5" s="3">
+        <v>57</v>
+      </c>
+      <c r="U5" s="6">
+        <v>5.2</v>
+      </c>
+      <c r="V5" s="6">
+        <v>3.5</v>
+      </c>
+      <c r="W5" s="6">
+        <v>1.2</v>
+      </c>
+      <c r="X5" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="Y5" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Z5" s="6">
         <v>0.7</v>
       </c>
-      <c r="AA5" s="3">
+      <c r="AA5" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C6">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D6">
-        <v>11.56</v>
+        <v>45</v>
       </c>
       <c r="E6">
         <v>30</v>
       </c>
       <c r="F6">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="G6">
         <v>10</v>
       </c>
       <c r="H6" s="2">
-        <v>1340</v>
+        <v>2550</v>
       </c>
       <c r="I6" s="2">
-        <v>900</v>
+        <v>2000</v>
       </c>
       <c r="J6" s="2">
-        <v>140</v>
+        <v>400</v>
       </c>
       <c r="K6" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="L6" s="2">
-        <v>1210</v>
+        <v>2250</v>
       </c>
       <c r="M6" s="2">
-        <v>240</v>
+        <v>650</v>
       </c>
       <c r="N6" s="2">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="O6" s="2">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="P6" s="2">
         <v>20</v>
@@ -4721,63 +4738,63 @@
         <v>15</v>
       </c>
       <c r="R6" s="6">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="S6" s="2">
         <v>15</v>
       </c>
       <c r="T6" s="2">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="U6" s="6">
-        <v>4.7</v>
+        <v>2.6</v>
       </c>
       <c r="V6" s="6">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="W6" s="6">
-        <v>1.9</v>
-      </c>
-      <c r="X6" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="Y6" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="Z6" s="3">
+        <v>1.4</v>
+      </c>
+      <c r="X6" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="Z6" s="6">
         <v>0.7</v>
       </c>
-      <c r="AA6" s="3">
+      <c r="AA6" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
-        <v>116</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C7">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D7">
-        <v>11.56</v>
+        <v>45</v>
       </c>
       <c r="E7">
         <v>30</v>
       </c>
       <c r="F7">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="G7">
         <v>10</v>
       </c>
       <c r="H7" s="2">
-        <v>2300</v>
+        <v>2200</v>
       </c>
       <c r="I7" s="2">
-        <v>1750</v>
+        <v>1300</v>
       </c>
       <c r="J7" s="2">
         <v>300</v>
@@ -4786,16 +4803,16 @@
         <v>15</v>
       </c>
       <c r="L7" s="2">
-        <v>2050</v>
+        <v>1900</v>
       </c>
       <c r="M7" s="2">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="N7" s="2">
         <v>50</v>
       </c>
       <c r="O7" s="2">
-        <v>32</v>
+        <v>21.5</v>
       </c>
       <c r="P7" s="2">
         <v>20</v>
@@ -4804,22 +4821,22 @@
         <v>15</v>
       </c>
       <c r="R7" s="6">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="S7" s="2">
         <v>15</v>
       </c>
       <c r="T7" s="2">
-        <v>135</v>
-      </c>
-      <c r="U7" s="6">
-        <v>2.4</v>
-      </c>
-      <c r="V7" s="6">
-        <v>2</v>
+        <v>165</v>
+      </c>
+      <c r="U7" s="10">
+        <v>2.8</v>
+      </c>
+      <c r="V7" s="10">
+        <v>2.2999999999999998</v>
       </c>
       <c r="W7" s="6">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="X7" s="6">
         <v>0.8</v>
@@ -4827,271 +4844,271 @@
       <c r="Y7" s="6">
         <v>0.8</v>
       </c>
-      <c r="Z7" s="6">
-        <v>0.7</v>
+      <c r="Z7" s="3">
+        <v>0.68</v>
       </c>
       <c r="AA7" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
-        <v>117</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C8">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D8">
         <v>11.56</v>
       </c>
       <c r="E8">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F8">
-        <v>5.5</v>
+        <v>0.9</v>
       </c>
       <c r="G8">
-        <v>10</v>
-      </c>
-      <c r="H8" s="2">
-        <v>2300</v>
-      </c>
-      <c r="I8" s="2">
-        <v>1600</v>
-      </c>
-      <c r="J8" s="2">
-        <v>275</v>
-      </c>
-      <c r="K8" s="2">
-        <v>15</v>
-      </c>
-      <c r="L8" s="2">
-        <v>1950</v>
-      </c>
-      <c r="M8" s="2">
-        <v>475</v>
-      </c>
-      <c r="N8" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="H8">
+        <v>760</v>
+      </c>
+      <c r="I8">
+        <v>900</v>
+      </c>
+      <c r="J8">
+        <v>100</v>
+      </c>
+      <c r="K8">
+        <v>25</v>
+      </c>
+      <c r="L8">
+        <v>650</v>
+      </c>
+      <c r="M8">
+        <v>95</v>
+      </c>
+      <c r="N8">
+        <v>11</v>
+      </c>
+      <c r="O8">
+        <v>21</v>
+      </c>
+      <c r="P8">
+        <v>20</v>
+      </c>
+      <c r="Q8">
+        <v>20</v>
+      </c>
+      <c r="R8">
+        <v>0.65</v>
+      </c>
+      <c r="S8">
+        <v>20</v>
+      </c>
+      <c r="T8">
+        <v>64</v>
+      </c>
+      <c r="U8">
+        <v>7</v>
+      </c>
+      <c r="V8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="W8">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="X8">
+        <v>1</v>
+      </c>
+      <c r="Y8">
+        <v>1</v>
+      </c>
+      <c r="Z8">
+        <v>0.85</v>
+      </c>
+      <c r="AA8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" t="s">
         <v>50</v>
       </c>
-      <c r="O8" s="2">
-        <v>24</v>
-      </c>
-      <c r="P8" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q8" s="2">
-        <v>15</v>
-      </c>
-      <c r="R8" s="2">
+      <c r="C9">
+        <v>32</v>
+      </c>
+      <c r="D9">
+        <v>11.56</v>
+      </c>
+      <c r="E9">
+        <v>30</v>
+      </c>
+      <c r="F9">
+        <v>4</v>
+      </c>
+      <c r="G9">
+        <v>10</v>
+      </c>
+      <c r="H9" s="2">
+        <v>1700</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1050</v>
+      </c>
+      <c r="J9" s="2">
+        <v>200</v>
+      </c>
+      <c r="K9" s="2">
+        <v>20</v>
+      </c>
+      <c r="L9" s="2">
+        <v>1500</v>
+      </c>
+      <c r="M9" s="2">
+        <v>300</v>
+      </c>
+      <c r="N9" s="2">
+        <v>50</v>
+      </c>
+      <c r="O9" s="2">
+        <v>21</v>
+      </c>
+      <c r="P9" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>15</v>
+      </c>
+      <c r="R9" s="6">
         <v>2.2000000000000002</v>
       </c>
-      <c r="S8" s="2">
-        <v>15</v>
-      </c>
-      <c r="T8" s="2">
-        <v>150</v>
-      </c>
-      <c r="U8" s="6">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="V8" s="6">
+      <c r="S9" s="2">
+        <v>15</v>
+      </c>
+      <c r="T9" s="2">
+        <v>108</v>
+      </c>
+      <c r="U9" s="3">
+        <v>3.7</v>
+      </c>
+      <c r="V9" s="3">
+        <v>3.05</v>
+      </c>
+      <c r="W9" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="X9" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="Y9" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="Z9" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="AA9" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10">
+        <v>32</v>
+      </c>
+      <c r="D10">
+        <v>11.56</v>
+      </c>
+      <c r="E10">
+        <v>30</v>
+      </c>
+      <c r="F10">
+        <v>3.2</v>
+      </c>
+      <c r="G10">
+        <v>10</v>
+      </c>
+      <c r="H10" s="2">
+        <v>1340</v>
+      </c>
+      <c r="I10" s="2">
+        <v>900</v>
+      </c>
+      <c r="J10" s="2">
+        <v>140</v>
+      </c>
+      <c r="K10" s="2">
+        <v>20</v>
+      </c>
+      <c r="L10" s="2">
+        <v>1210</v>
+      </c>
+      <c r="M10" s="2">
+        <v>240</v>
+      </c>
+      <c r="N10" s="2">
+        <v>30</v>
+      </c>
+      <c r="O10" s="2">
+        <v>15</v>
+      </c>
+      <c r="P10" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>15</v>
+      </c>
+      <c r="R10" s="6">
+        <v>1</v>
+      </c>
+      <c r="S10" s="2">
+        <v>15</v>
+      </c>
+      <c r="T10" s="2">
+        <v>125</v>
+      </c>
+      <c r="U10" s="6">
+        <v>4.7</v>
+      </c>
+      <c r="V10" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="W10" s="6">
         <v>1.9</v>
       </c>
-      <c r="W8" s="6">
-        <v>1.2</v>
-      </c>
-      <c r="X8" s="6">
+      <c r="X10" s="3">
         <v>0.8</v>
       </c>
-      <c r="Y8" s="6">
+      <c r="Y10" s="3">
         <v>0.8</v>
       </c>
-      <c r="Z8" s="6">
+      <c r="Z10" s="3">
         <v>0.7</v>
       </c>
-      <c r="AA8" s="6">
+      <c r="AA10" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C9">
-        <v>25</v>
-      </c>
-      <c r="D9">
-        <v>45</v>
-      </c>
-      <c r="E9">
-        <v>30</v>
-      </c>
-      <c r="F9">
-        <v>5.5</v>
-      </c>
-      <c r="G9">
-        <v>10</v>
-      </c>
-      <c r="H9" s="2">
-        <v>2550</v>
-      </c>
-      <c r="I9" s="2">
-        <v>2000</v>
-      </c>
-      <c r="J9" s="2">
-        <v>400</v>
-      </c>
-      <c r="K9" s="2">
-        <v>15</v>
-      </c>
-      <c r="L9" s="2">
-        <v>2250</v>
-      </c>
-      <c r="M9" s="2">
-        <v>650</v>
-      </c>
-      <c r="N9" s="2">
-        <v>100</v>
-      </c>
-      <c r="O9" s="2">
-        <v>30</v>
-      </c>
-      <c r="P9" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q9" s="2">
-        <v>15</v>
-      </c>
-      <c r="R9" s="6">
-        <v>4.5</v>
-      </c>
-      <c r="S9" s="2">
-        <v>15</v>
-      </c>
-      <c r="T9" s="2">
-        <v>110</v>
-      </c>
-      <c r="U9" s="6">
-        <v>2.6</v>
-      </c>
-      <c r="V9" s="6">
-        <v>1.5</v>
-      </c>
-      <c r="W9" s="6">
-        <v>1.4</v>
-      </c>
-      <c r="X9" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="Y9" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="Z9" s="6">
-        <v>0.7</v>
-      </c>
-      <c r="AA9" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C10">
-        <v>25</v>
-      </c>
-      <c r="D10">
-        <v>45</v>
-      </c>
-      <c r="E10">
-        <v>30</v>
-      </c>
-      <c r="F10">
-        <v>2.5</v>
-      </c>
-      <c r="G10">
-        <v>10</v>
-      </c>
-      <c r="H10" s="2">
-        <v>1250</v>
-      </c>
-      <c r="I10" s="2">
-        <v>1100</v>
-      </c>
-      <c r="J10" s="2">
-        <v>200</v>
-      </c>
-      <c r="K10" s="2">
-        <v>15</v>
-      </c>
-      <c r="L10" s="2">
-        <v>1200</v>
-      </c>
-      <c r="M10" s="2">
-        <v>400</v>
-      </c>
-      <c r="N10" s="2">
-        <v>62</v>
-      </c>
-      <c r="O10" s="2">
-        <v>20</v>
-      </c>
-      <c r="P10" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q10" s="2">
-        <v>15</v>
-      </c>
-      <c r="R10" s="6">
-        <v>3</v>
-      </c>
-      <c r="S10" s="2">
-        <v>15</v>
-      </c>
-      <c r="T10" s="2">
-        <v>57</v>
-      </c>
-      <c r="U10" s="6">
-        <v>5.2</v>
-      </c>
-      <c r="V10" s="6">
-        <v>3.5</v>
-      </c>
-      <c r="W10" s="6">
-        <v>1.2</v>
-      </c>
-      <c r="X10" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="Y10" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="Z10" s="6">
-        <v>0.7</v>
-      </c>
-      <c r="AA10" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>116</v>
       </c>
       <c r="B11" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C11">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D11">
         <v>11.56</v>
@@ -5100,81 +5117,81 @@
         <v>30</v>
       </c>
       <c r="F11">
-        <v>11.3</v>
+        <v>5.2</v>
       </c>
       <c r="G11">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="H11" s="2">
-        <v>4000</v>
+        <v>2300</v>
       </c>
       <c r="I11" s="2">
-        <v>3000</v>
+        <v>1750</v>
       </c>
       <c r="J11" s="2">
+        <v>300</v>
+      </c>
+      <c r="K11" s="2">
+        <v>15</v>
+      </c>
+      <c r="L11" s="2">
+        <v>2050</v>
+      </c>
+      <c r="M11" s="2">
         <v>500</v>
       </c>
-      <c r="K11" s="2">
-        <v>12</v>
-      </c>
-      <c r="L11" s="2">
-        <v>3500</v>
-      </c>
-      <c r="M11" s="2">
-        <v>1400</v>
-      </c>
       <c r="N11" s="2">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="O11" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P11" s="2">
-        <v>10</v>
-      </c>
-      <c r="Q11">
-        <v>15</v>
-      </c>
-      <c r="R11">
-        <v>3</v>
-      </c>
-      <c r="S11">
-        <v>15</v>
-      </c>
-      <c r="T11">
+        <v>20</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>15</v>
+      </c>
+      <c r="R11" s="6">
+        <v>2.1</v>
+      </c>
+      <c r="S11" s="2">
+        <v>15</v>
+      </c>
+      <c r="T11" s="2">
+        <v>135</v>
+      </c>
+      <c r="U11" s="6">
+        <v>2.4</v>
+      </c>
+      <c r="V11" s="6">
+        <v>2</v>
+      </c>
+      <c r="W11" s="6">
+        <v>1.2</v>
+      </c>
+      <c r="X11" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="Y11" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="Z11" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="AA11" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A12" t="s">
         <v>117</v>
       </c>
-      <c r="U11">
-        <v>1.25</v>
-      </c>
-      <c r="V11">
-        <v>0.88</v>
-      </c>
-      <c r="W11">
-        <v>0.75</v>
-      </c>
-      <c r="X11" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="Y11" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="Z11">
-        <v>0.73</v>
-      </c>
-      <c r="AA11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>26</v>
-      </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C12">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D12">
         <v>11.56</v>
@@ -5183,75 +5200,75 @@
         <v>30</v>
       </c>
       <c r="F12">
-        <v>9.6</v>
+        <v>5.5</v>
       </c>
       <c r="G12">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="H12" s="2">
-        <v>3000</v>
+        <v>2300</v>
       </c>
       <c r="I12" s="2">
-        <v>3000</v>
+        <v>1600</v>
       </c>
       <c r="J12" s="2">
-        <v>500</v>
+        <v>275</v>
       </c>
       <c r="K12" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L12" s="2">
-        <v>2975</v>
+        <v>1950</v>
       </c>
       <c r="M12" s="2">
-        <v>1200</v>
+        <v>475</v>
       </c>
       <c r="N12" s="2">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="O12" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P12" s="2">
-        <v>10</v>
-      </c>
-      <c r="Q12">
-        <v>15</v>
-      </c>
-      <c r="R12">
-        <v>3.9</v>
-      </c>
-      <c r="S12">
-        <v>15</v>
-      </c>
-      <c r="T12">
-        <v>95</v>
-      </c>
-      <c r="U12">
-        <v>1.5</v>
-      </c>
-      <c r="V12">
-        <v>0.95</v>
-      </c>
-      <c r="W12">
-        <v>0.42</v>
-      </c>
-      <c r="X12" s="3">
+        <v>20</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>15</v>
+      </c>
+      <c r="R12" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="S12" s="2">
+        <v>15</v>
+      </c>
+      <c r="T12" s="2">
+        <v>150</v>
+      </c>
+      <c r="U12" s="6">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="V12" s="6">
+        <v>1.9</v>
+      </c>
+      <c r="W12" s="6">
+        <v>1.2</v>
+      </c>
+      <c r="X12" s="6">
         <v>0.8</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Y12" s="6">
         <v>0.8</v>
       </c>
-      <c r="Z12">
-        <v>0.73</v>
-      </c>
-      <c r="AA12">
-        <v>5</v>
+      <c r="Z12" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="AA12" s="6">
+        <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B13" t="s">
         <v>46</v>
@@ -5266,34 +5283,34 @@
         <v>30</v>
       </c>
       <c r="F13">
-        <v>11.2</v>
+        <v>2.1</v>
       </c>
       <c r="G13">
         <v>4.5</v>
       </c>
       <c r="H13" s="2">
-        <v>4000</v>
+        <v>735</v>
       </c>
       <c r="I13" s="2">
-        <v>4000</v>
+        <v>680</v>
       </c>
       <c r="J13" s="2">
-        <v>550</v>
+        <v>100</v>
       </c>
       <c r="K13" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L13" s="2">
-        <v>3700</v>
+        <v>640</v>
       </c>
       <c r="M13" s="2">
-        <v>1800</v>
+        <v>310</v>
       </c>
       <c r="N13" s="2">
-        <v>160</v>
+        <v>21</v>
       </c>
       <c r="O13" s="2">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="P13" s="2">
         <v>10</v>
@@ -5302,39 +5319,39 @@
         <v>15</v>
       </c>
       <c r="R13" s="2">
-        <v>5.8</v>
+        <v>0.7</v>
       </c>
       <c r="S13" s="2">
         <v>15</v>
       </c>
       <c r="T13" s="2">
-        <v>84</v>
-      </c>
-      <c r="U13" s="3">
-        <v>1.75</v>
-      </c>
-      <c r="V13" s="3">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="W13" s="3">
-        <v>0.6</v>
-      </c>
-      <c r="X13" s="3">
+        <v>37</v>
+      </c>
+      <c r="U13" s="6">
+        <v>11</v>
+      </c>
+      <c r="V13" s="6">
+        <v>8.4</v>
+      </c>
+      <c r="W13" s="6">
+        <v>1.4</v>
+      </c>
+      <c r="X13" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Y13" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Z13" s="6">
         <v>0.8</v>
       </c>
-      <c r="Y13" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="Z13" s="3">
-        <v>0.45</v>
-      </c>
-      <c r="AA13" s="3">
+      <c r="AA13" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B14" t="s">
         <v>46</v>
@@ -5346,61 +5363,61 @@
         <v>11.56</v>
       </c>
       <c r="E14">
-        <v>30</v>
-      </c>
-      <c r="F14">
-        <v>8.5</v>
-      </c>
-      <c r="G14">
-        <v>10</v>
+        <v>40</v>
+      </c>
+      <c r="F14" s="7">
+        <v>2.75</v>
+      </c>
+      <c r="G14" s="7">
+        <v>4.5</v>
       </c>
       <c r="H14" s="2">
-        <v>3200</v>
+        <v>1550</v>
       </c>
       <c r="I14" s="2">
-        <v>2500</v>
+        <v>1000</v>
       </c>
       <c r="J14" s="2">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="K14" s="2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="L14" s="2">
-        <v>2800</v>
+        <v>1450</v>
       </c>
       <c r="M14" s="2">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="N14" s="2">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="O14" s="2">
-        <v>36.5</v>
+        <v>21</v>
       </c>
       <c r="P14" s="2">
         <v>20</v>
       </c>
       <c r="Q14" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R14" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S14" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T14" s="2">
-        <v>125</v>
+        <v>70</v>
       </c>
       <c r="U14" s="6">
-        <v>2.4500000000000002</v>
+        <v>7.4</v>
       </c>
       <c r="V14" s="6">
-        <v>1.55</v>
+        <v>5</v>
       </c>
       <c r="W14" s="6">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="X14" s="6">
         <v>0.5</v>
@@ -5409,15 +5426,15 @@
         <v>0.5</v>
       </c>
       <c r="Z14" s="6">
-        <v>0.68</v>
-      </c>
-      <c r="AA14" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="AA14" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="B15" t="s">
         <v>46</v>
@@ -5426,3072 +5443,3415 @@
         <v>30</v>
       </c>
       <c r="D15">
+        <v>11.56</v>
+      </c>
+      <c r="E15">
+        <v>30</v>
+      </c>
+      <c r="F15">
+        <v>2.8</v>
+      </c>
+      <c r="G15">
+        <v>4.5</v>
+      </c>
+      <c r="H15" s="2">
+        <v>1060</v>
+      </c>
+      <c r="I15" s="2">
+        <v>900</v>
+      </c>
+      <c r="J15" s="2">
+        <v>140</v>
+      </c>
+      <c r="K15" s="2">
+        <v>10</v>
+      </c>
+      <c r="L15" s="2">
+        <v>960</v>
+      </c>
+      <c r="M15" s="2">
+        <v>460</v>
+      </c>
+      <c r="N15" s="2">
+        <v>40</v>
+      </c>
+      <c r="O15" s="2">
+        <v>30</v>
+      </c>
+      <c r="P15" s="2">
+        <v>15</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>15</v>
+      </c>
+      <c r="R15" s="6">
+        <v>1.2</v>
+      </c>
+      <c r="S15" s="2">
+        <v>15</v>
+      </c>
+      <c r="T15" s="2">
+        <v>46</v>
+      </c>
+      <c r="U15" s="6">
+        <v>7.87</v>
+      </c>
+      <c r="V15" s="6">
+        <v>5.63</v>
+      </c>
+      <c r="W15" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="X15" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Y15" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Z15" s="6">
+        <v>0.85</v>
+      </c>
+      <c r="AA15" s="6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16">
+        <v>15</v>
+      </c>
+      <c r="D16">
+        <v>45</v>
+      </c>
+      <c r="E16">
+        <v>40</v>
+      </c>
+      <c r="F16">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="G16">
+        <v>10</v>
+      </c>
+      <c r="H16" s="2">
+        <v>2900</v>
+      </c>
+      <c r="I16" s="2">
+        <v>2500</v>
+      </c>
+      <c r="J16" s="2">
+        <v>250</v>
+      </c>
+      <c r="K16" s="2">
+        <v>30</v>
+      </c>
+      <c r="L16" s="2">
+        <v>2800</v>
+      </c>
+      <c r="M16" s="2">
+        <v>400</v>
+      </c>
+      <c r="N16" s="2">
+        <v>30</v>
+      </c>
+      <c r="O16" s="2">
+        <v>41</v>
+      </c>
+      <c r="P16" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>20</v>
+      </c>
+      <c r="R16" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="S16" s="2">
+        <v>20</v>
+      </c>
+      <c r="T16" s="2">
+        <v>203</v>
+      </c>
+      <c r="U16" s="6">
+        <v>3.5</v>
+      </c>
+      <c r="V16" s="6">
+        <v>2.6</v>
+      </c>
+      <c r="W16" s="3">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="X16" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="Y16" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Z16" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="AA16" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17">
+        <v>15</v>
+      </c>
+      <c r="D17">
+        <v>45</v>
+      </c>
+      <c r="E17">
+        <v>60</v>
+      </c>
+      <c r="F17">
+        <v>10</v>
+      </c>
+      <c r="G17">
+        <v>10</v>
+      </c>
+      <c r="H17" s="2">
+        <v>4000</v>
+      </c>
+      <c r="I17" s="2">
+        <v>3000</v>
+      </c>
+      <c r="J17" s="2">
+        <v>700</v>
+      </c>
+      <c r="K17" s="2">
+        <v>25</v>
+      </c>
+      <c r="L17" s="2">
+        <v>3300</v>
+      </c>
+      <c r="M17" s="2">
+        <v>1000</v>
+      </c>
+      <c r="N17" s="2">
+        <v>50</v>
+      </c>
+      <c r="O17" s="2">
+        <v>73</v>
+      </c>
+      <c r="P17" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>30</v>
+      </c>
+      <c r="R17" s="6">
+        <v>8.5</v>
+      </c>
+      <c r="S17" s="2">
+        <v>30</v>
+      </c>
+      <c r="T17" s="2">
+        <v>100</v>
+      </c>
+      <c r="U17" s="6">
+        <v>3.1</v>
+      </c>
+      <c r="V17" s="6">
+        <v>2.4</v>
+      </c>
+      <c r="W17" s="6">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="X17" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="Y17" s="6">
+        <v>0.75</v>
+      </c>
+      <c r="Z17" s="3">
+        <v>0.69</v>
+      </c>
+      <c r="AA17" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="A18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C18">
+        <v>15</v>
+      </c>
+      <c r="D18">
+        <v>45</v>
+      </c>
+      <c r="E18">
+        <v>30</v>
+      </c>
+      <c r="F18">
+        <v>19</v>
+      </c>
+      <c r="G18">
+        <v>4.5</v>
+      </c>
+      <c r="H18" s="2">
+        <v>8500</v>
+      </c>
+      <c r="I18" s="2">
+        <v>6000</v>
+      </c>
+      <c r="J18" s="2">
+        <v>1000</v>
+      </c>
+      <c r="K18" s="2">
+        <v>24</v>
+      </c>
+      <c r="L18" s="2">
+        <v>7500</v>
+      </c>
+      <c r="M18" s="2">
+        <v>1400</v>
+      </c>
+      <c r="N18" s="2">
+        <v>75</v>
+      </c>
+      <c r="O18" s="2">
+        <v>20</v>
+      </c>
+      <c r="P18" s="2">
+        <v>87</v>
+      </c>
+      <c r="Q18" s="2">
+        <v>15</v>
+      </c>
+      <c r="R18" s="2">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="S18" s="2">
+        <v>15</v>
+      </c>
+      <c r="T18" s="2">
+        <v>120</v>
+      </c>
+      <c r="U18" s="3">
+        <v>2</v>
+      </c>
+      <c r="V18" s="3">
+        <v>1.7</v>
+      </c>
+      <c r="W18" s="3">
+        <v>1.9</v>
+      </c>
+      <c r="X18" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>0.81</v>
+      </c>
+      <c r="AA18" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="A19" t="s">
+        <v>109</v>
+      </c>
+      <c r="B19" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19">
+        <v>15</v>
+      </c>
+      <c r="D19">
+        <v>45</v>
+      </c>
+      <c r="E19">
+        <v>40</v>
+      </c>
+      <c r="F19">
+        <v>5.5</v>
+      </c>
+      <c r="G19">
+        <v>10</v>
+      </c>
+      <c r="H19" s="2">
+        <v>2200</v>
+      </c>
+      <c r="I19" s="2">
+        <v>2400</v>
+      </c>
+      <c r="J19" s="2">
+        <v>300</v>
+      </c>
+      <c r="K19" s="2">
+        <v>15</v>
+      </c>
+      <c r="L19" s="2">
+        <v>2000</v>
+      </c>
+      <c r="M19" s="2">
+        <v>900</v>
+      </c>
+      <c r="N19" s="2">
+        <v>28</v>
+      </c>
+      <c r="O19" s="2">
+        <v>42</v>
+      </c>
+      <c r="P19" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q19" s="2">
+        <v>20</v>
+      </c>
+      <c r="R19" s="6">
+        <v>3.6</v>
+      </c>
+      <c r="S19" s="2">
+        <v>20</v>
+      </c>
+      <c r="T19" s="2">
+        <v>170</v>
+      </c>
+      <c r="U19" s="6">
+        <v>2.4</v>
+      </c>
+      <c r="V19" s="6">
+        <v>1.8</v>
+      </c>
+      <c r="W19" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="X19" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y19" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z19" s="3">
+        <v>0.84</v>
+      </c>
+      <c r="AA19" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="A20" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20">
+        <v>15</v>
+      </c>
+      <c r="D20">
+        <v>45</v>
+      </c>
+      <c r="E20">
+        <v>40</v>
+      </c>
+      <c r="F20">
+        <v>4.8</v>
+      </c>
+      <c r="G20">
+        <v>10</v>
+      </c>
+      <c r="H20" s="2">
+        <v>2000</v>
+      </c>
+      <c r="I20" s="2">
+        <v>2000</v>
+      </c>
+      <c r="J20" s="2">
+        <v>300</v>
+      </c>
+      <c r="K20" s="2">
+        <v>15</v>
+      </c>
+      <c r="L20" s="2">
+        <v>1800</v>
+      </c>
+      <c r="M20" s="2">
+        <v>750</v>
+      </c>
+      <c r="N20" s="2">
+        <v>90</v>
+      </c>
+      <c r="O20" s="2">
+        <v>52</v>
+      </c>
+      <c r="P20" s="2">
+        <v>50</v>
+      </c>
+      <c r="Q20" s="2">
+        <v>20</v>
+      </c>
+      <c r="R20" s="6">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="S20" s="2">
+        <v>20</v>
+      </c>
+      <c r="T20" s="2">
+        <v>150</v>
+      </c>
+      <c r="U20" s="6">
+        <v>3.3</v>
+      </c>
+      <c r="V20" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="W20" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="X20" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y20" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z20" s="3">
+        <v>0.88</v>
+      </c>
+      <c r="AA20" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21">
+        <v>15</v>
+      </c>
+      <c r="D21">
+        <v>45</v>
+      </c>
+      <c r="E21">
+        <v>40</v>
+      </c>
+      <c r="F21">
+        <v>2.1</v>
+      </c>
+      <c r="G21">
+        <v>10</v>
+      </c>
+      <c r="H21" s="2">
+        <v>750</v>
+      </c>
+      <c r="I21" s="2">
+        <v>900</v>
+      </c>
+      <c r="J21" s="2">
+        <v>100</v>
+      </c>
+      <c r="K21" s="2">
+        <v>25</v>
+      </c>
+      <c r="L21" s="2">
+        <v>650</v>
+      </c>
+      <c r="M21" s="2">
+        <v>190</v>
+      </c>
+      <c r="N21" s="2">
+        <v>12</v>
+      </c>
+      <c r="O21" s="2">
+        <v>22</v>
+      </c>
+      <c r="P21" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q21" s="2">
+        <v>20</v>
+      </c>
+      <c r="R21" s="6">
+        <v>1.4</v>
+      </c>
+      <c r="S21" s="2">
+        <v>20</v>
+      </c>
+      <c r="T21" s="2">
+        <v>100</v>
+      </c>
+      <c r="U21" s="6">
+        <v>6.8</v>
+      </c>
+      <c r="V21" s="6">
+        <v>4.7</v>
+      </c>
+      <c r="W21" s="6">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="X21" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y21" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z21" s="3">
+        <v>0.92</v>
+      </c>
+      <c r="AA21" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22">
+        <v>15</v>
+      </c>
+      <c r="D22">
+        <v>45</v>
+      </c>
+      <c r="E22">
+        <v>40</v>
+      </c>
+      <c r="F22">
+        <v>7.6</v>
+      </c>
+      <c r="G22">
+        <v>10</v>
+      </c>
+      <c r="H22" s="2">
+        <v>2400</v>
+      </c>
+      <c r="I22" s="2">
+        <v>1800</v>
+      </c>
+      <c r="J22" s="2">
+        <v>300</v>
+      </c>
+      <c r="K22" s="2">
+        <v>30</v>
+      </c>
+      <c r="L22" s="2">
+        <v>2200</v>
+      </c>
+      <c r="M22" s="2">
+        <v>380</v>
+      </c>
+      <c r="N22" s="2">
+        <v>15</v>
+      </c>
+      <c r="O22" s="2">
+        <v>23</v>
+      </c>
+      <c r="P22" s="2">
+        <v>42</v>
+      </c>
+      <c r="Q22" s="2">
+        <v>20</v>
+      </c>
+      <c r="R22" s="6">
+        <v>3.2</v>
+      </c>
+      <c r="S22" s="2">
+        <v>20</v>
+      </c>
+      <c r="T22" s="2">
+        <v>96</v>
+      </c>
+      <c r="U22" s="6">
+        <v>6.8</v>
+      </c>
+      <c r="V22" s="6">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="W22" s="6">
+        <v>1.4</v>
+      </c>
+      <c r="X22" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y22" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>0.88</v>
+      </c>
+      <c r="AA22" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A23" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23">
+        <v>30</v>
+      </c>
+      <c r="D23">
+        <v>11.56</v>
+      </c>
+      <c r="E23">
+        <v>40</v>
+      </c>
+      <c r="F23">
+        <v>2.9</v>
+      </c>
+      <c r="G23">
+        <v>4.5</v>
+      </c>
+      <c r="H23">
+        <v>950</v>
+      </c>
+      <c r="I23">
+        <v>500</v>
+      </c>
+      <c r="J23">
+        <v>70</v>
+      </c>
+      <c r="K23">
+        <v>25</v>
+      </c>
+      <c r="L23" s="2">
+        <v>875</v>
+      </c>
+      <c r="M23" s="2">
+        <v>150</v>
+      </c>
+      <c r="N23" s="2">
+        <v>16</v>
+      </c>
+      <c r="O23" s="2">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="P23" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q23" s="2">
+        <v>20</v>
+      </c>
+      <c r="R23" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="S23">
+        <v>20</v>
+      </c>
+      <c r="T23" s="2">
+        <v>45</v>
+      </c>
+      <c r="U23">
+        <v>9.6</v>
+      </c>
+      <c r="V23">
+        <v>6.7</v>
+      </c>
+      <c r="W23" s="4">
+        <v>3.2</v>
+      </c>
+      <c r="X23" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="Y23" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="Z23" s="3">
+        <v>0.82</v>
+      </c>
+      <c r="AA23" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A24" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24">
+        <v>30</v>
+      </c>
+      <c r="D24">
+        <v>11.56</v>
+      </c>
+      <c r="E24">
+        <v>40</v>
+      </c>
+      <c r="F24">
+        <v>3.2</v>
+      </c>
+      <c r="G24">
+        <v>4.5</v>
+      </c>
+      <c r="H24" s="2">
+        <v>2500</v>
+      </c>
+      <c r="I24" s="2">
+        <v>1500</v>
+      </c>
+      <c r="J24" s="2">
+        <v>200</v>
+      </c>
+      <c r="K24" s="2">
+        <v>24</v>
+      </c>
+      <c r="L24" s="2">
+        <v>1375</v>
+      </c>
+      <c r="M24" s="2">
+        <v>1130</v>
+      </c>
+      <c r="N24" s="2">
+        <v>50</v>
+      </c>
+      <c r="O24" s="2">
+        <v>17</v>
+      </c>
+      <c r="P24" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q24" s="2">
+        <v>20</v>
+      </c>
+      <c r="R24" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="S24" s="2">
+        <v>20</v>
+      </c>
+      <c r="T24" s="2">
+        <v>65</v>
+      </c>
+      <c r="U24" s="3">
+        <v>6.2</v>
+      </c>
+      <c r="V24" s="3">
+        <v>4.5</v>
+      </c>
+      <c r="W24" s="3">
+        <v>0.9</v>
+      </c>
+      <c r="X24" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A25" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25">
+        <v>30</v>
+      </c>
+      <c r="D25">
+        <v>11.56</v>
+      </c>
+      <c r="E25">
+        <v>30</v>
+      </c>
+      <c r="F25">
+        <v>3.6</v>
+      </c>
+      <c r="G25">
+        <v>10</v>
+      </c>
+      <c r="H25" s="2">
+        <v>1450</v>
+      </c>
+      <c r="I25" s="2">
+        <v>1100</v>
+      </c>
+      <c r="J25" s="2">
+        <v>200</v>
+      </c>
+      <c r="K25" s="2">
+        <v>25</v>
+      </c>
+      <c r="L25" s="2">
+        <v>1300</v>
+      </c>
+      <c r="M25" s="2">
+        <v>250</v>
+      </c>
+      <c r="N25" s="2">
+        <v>30</v>
+      </c>
+      <c r="O25" s="2">
+        <v>18</v>
+      </c>
+      <c r="P25" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q25" s="2">
+        <v>15</v>
+      </c>
+      <c r="R25" s="6">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="S25" s="2">
+        <v>15</v>
+      </c>
+      <c r="T25" s="2">
+        <v>77</v>
+      </c>
+      <c r="U25" s="6">
+        <v>6</v>
+      </c>
+      <c r="V25" s="6">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="W25" s="6">
+        <v>1.7</v>
+      </c>
+      <c r="X25" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="Y25" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="Z25" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="AA25" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="A26" t="s">
+        <v>111</v>
+      </c>
+      <c r="B26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26">
+        <v>15</v>
+      </c>
+      <c r="D26">
+        <v>45</v>
+      </c>
+      <c r="E26">
+        <v>40</v>
+      </c>
+      <c r="F26">
+        <v>7</v>
+      </c>
+      <c r="G26">
+        <v>10</v>
+      </c>
+      <c r="H26" s="2">
+        <v>1900</v>
+      </c>
+      <c r="I26" s="2">
+        <v>2000</v>
+      </c>
+      <c r="J26" s="2">
+        <v>300</v>
+      </c>
+      <c r="K26" s="2">
+        <v>15</v>
+      </c>
+      <c r="L26" s="2">
+        <v>1600</v>
+      </c>
+      <c r="M26" s="2">
+        <v>780</v>
+      </c>
+      <c r="N26" s="2">
+        <v>80</v>
+      </c>
+      <c r="O26" s="2">
+        <v>23</v>
+      </c>
+      <c r="P26" s="2">
+        <v>50</v>
+      </c>
+      <c r="Q26" s="2">
+        <v>20</v>
+      </c>
+      <c r="R26" s="6">
+        <v>4</v>
+      </c>
+      <c r="S26" s="2">
+        <v>20</v>
+      </c>
+      <c r="T26" s="2">
+        <v>140</v>
+      </c>
+      <c r="U26" s="6">
+        <v>3.1</v>
+      </c>
+      <c r="V26" s="6">
+        <v>2.7</v>
+      </c>
+      <c r="W26" s="3">
+        <v>2.8</v>
+      </c>
+      <c r="X26" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y26" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z26" s="3">
+        <v>0.89</v>
+      </c>
+      <c r="AA26" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="A27" t="s">
+        <v>112</v>
+      </c>
+      <c r="B27" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27">
+        <v>15</v>
+      </c>
+      <c r="D27">
+        <v>45</v>
+      </c>
+      <c r="E27">
+        <v>40</v>
+      </c>
+      <c r="F27">
+        <v>5</v>
+      </c>
+      <c r="G27">
+        <v>10</v>
+      </c>
+      <c r="H27" s="2">
+        <v>1400</v>
+      </c>
+      <c r="I27" s="2">
+        <v>1500</v>
+      </c>
+      <c r="J27" s="2">
+        <v>200</v>
+      </c>
+      <c r="K27" s="2">
+        <v>15</v>
+      </c>
+      <c r="L27" s="2">
+        <v>1100</v>
+      </c>
+      <c r="M27" s="2">
+        <v>580</v>
+      </c>
+      <c r="N27" s="2">
+        <v>60</v>
+      </c>
+      <c r="O27" s="2">
+        <v>19</v>
+      </c>
+      <c r="P27" s="2">
+        <v>50</v>
+      </c>
+      <c r="Q27" s="2">
+        <v>20</v>
+      </c>
+      <c r="R27" s="6">
+        <v>3</v>
+      </c>
+      <c r="S27" s="2">
+        <v>20</v>
+      </c>
+      <c r="T27" s="2">
+        <v>100</v>
+      </c>
+      <c r="U27" s="6">
+        <v>4</v>
+      </c>
+      <c r="V27" s="6">
+        <v>3.5</v>
+      </c>
+      <c r="W27" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="X27" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y27" s="3">
+        <v>1</v>
+      </c>
+      <c r="Z27" s="3">
+        <v>0.88</v>
+      </c>
+      <c r="AA27" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A28" t="s">
+        <v>24</v>
+      </c>
+      <c r="B28" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28">
+        <v>30</v>
+      </c>
+      <c r="D28">
+        <v>11.56</v>
+      </c>
+      <c r="E28">
+        <v>30</v>
+      </c>
+      <c r="F28">
+        <v>3.7</v>
+      </c>
+      <c r="G28">
+        <v>4.5</v>
+      </c>
+      <c r="H28" s="2">
+        <v>1200</v>
+      </c>
+      <c r="I28" s="2">
+        <v>1200</v>
+      </c>
+      <c r="J28" s="2">
+        <v>150</v>
+      </c>
+      <c r="K28" s="2">
+        <v>12</v>
+      </c>
+      <c r="L28" s="2">
+        <v>1175</v>
+      </c>
+      <c r="M28" s="2">
+        <v>450</v>
+      </c>
+      <c r="N28" s="2">
+        <v>30</v>
+      </c>
+      <c r="O28" s="2">
+        <v>10</v>
+      </c>
+      <c r="P28" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q28">
+        <v>15</v>
+      </c>
+      <c r="R28">
+        <v>1.4</v>
+      </c>
+      <c r="S28">
+        <v>15</v>
+      </c>
+      <c r="T28">
+        <v>53</v>
+      </c>
+      <c r="U28">
+        <v>3.8</v>
+      </c>
+      <c r="V28">
+        <v>2.7</v>
+      </c>
+      <c r="W28">
+        <v>0.9</v>
+      </c>
+      <c r="X28" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="Z28">
+        <v>0.76</v>
+      </c>
+      <c r="AA28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="A29" t="s">
+        <v>115</v>
+      </c>
+      <c r="B29" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29">
+        <v>15</v>
+      </c>
+      <c r="D29">
+        <v>45</v>
+      </c>
+      <c r="E29">
+        <v>40</v>
+      </c>
+      <c r="F29">
+        <v>16</v>
+      </c>
+      <c r="G29">
+        <v>10</v>
+      </c>
+      <c r="H29" s="2">
+        <v>5000</v>
+      </c>
+      <c r="I29" s="2">
+        <v>4000</v>
+      </c>
+      <c r="J29" s="2">
+        <v>1100</v>
+      </c>
+      <c r="K29" s="2">
+        <v>15</v>
+      </c>
+      <c r="L29" s="2">
+        <v>3300</v>
+      </c>
+      <c r="M29" s="2">
+        <v>460</v>
+      </c>
+      <c r="N29" s="2">
+        <v>300</v>
+      </c>
+      <c r="O29" s="2">
+        <v>48</v>
+      </c>
+      <c r="P29" s="2">
+        <v>40</v>
+      </c>
+      <c r="Q29" s="2">
+        <v>20</v>
+      </c>
+      <c r="R29" s="6">
+        <v>16</v>
+      </c>
+      <c r="S29" s="2">
+        <v>20</v>
+      </c>
+      <c r="T29" s="11">
+        <v>100</v>
+      </c>
+      <c r="U29" s="6">
+        <v>7</v>
+      </c>
+      <c r="V29" s="6">
+        <v>1.86</v>
+      </c>
+      <c r="W29" s="3">
+        <v>1.7</v>
+      </c>
+      <c r="X29" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y29" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0.83</v>
+      </c>
+      <c r="AA29" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="A30" t="s">
+        <v>114</v>
+      </c>
+      <c r="B30" t="s">
+        <v>47</v>
+      </c>
+      <c r="C30">
+        <v>15</v>
+      </c>
+      <c r="D30">
+        <v>45</v>
+      </c>
+      <c r="E30">
+        <v>40</v>
+      </c>
+      <c r="F30">
+        <v>13</v>
+      </c>
+      <c r="G30">
+        <v>10</v>
+      </c>
+      <c r="H30" s="2">
+        <v>3600</v>
+      </c>
+      <c r="I30" s="2">
+        <v>3800</v>
+      </c>
+      <c r="J30" s="2">
+        <v>1000</v>
+      </c>
+      <c r="K30" s="2">
+        <v>15</v>
+      </c>
+      <c r="L30" s="2">
+        <v>2900</v>
+      </c>
+      <c r="M30" s="2">
+        <v>380</v>
+      </c>
+      <c r="N30" s="2">
+        <v>270</v>
+      </c>
+      <c r="O30" s="2">
+        <v>41</v>
+      </c>
+      <c r="P30" s="2">
+        <v>40</v>
+      </c>
+      <c r="Q30" s="2">
+        <v>20</v>
+      </c>
+      <c r="R30" s="6">
+        <v>15</v>
+      </c>
+      <c r="S30" s="2">
+        <v>20</v>
+      </c>
+      <c r="T30" s="11">
+        <v>100</v>
+      </c>
+      <c r="U30" s="6">
+        <v>20</v>
+      </c>
+      <c r="V30" s="6">
+        <v>2.5</v>
+      </c>
+      <c r="W30" s="3">
+        <v>2.1</v>
+      </c>
+      <c r="X30" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y30" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z30" s="3">
+        <v>0.83</v>
+      </c>
+      <c r="AA30" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31" s="2">
+        <v>1</v>
+      </c>
+      <c r="E31" s="2">
+        <v>0</v>
+      </c>
+      <c r="F31" s="5">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="G31" s="5">
+        <v>4.5</v>
+      </c>
+      <c r="H31" s="5">
+        <v>1</v>
+      </c>
+      <c r="I31" s="5">
+        <v>1</v>
+      </c>
+      <c r="J31" s="5">
+        <v>1</v>
+      </c>
+      <c r="K31" s="5">
+        <v>25</v>
+      </c>
+      <c r="L31" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="M31" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="N31" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="O31" s="5">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="P31" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q31" s="5">
+        <v>20</v>
+      </c>
+      <c r="R31" s="5">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="S31" s="5">
+        <v>20</v>
+      </c>
+      <c r="T31" s="5">
+        <v>20</v>
+      </c>
+      <c r="U31" s="6">
+        <v>1E-3</v>
+      </c>
+      <c r="V31" s="6">
+        <v>1E-3</v>
+      </c>
+      <c r="W31" s="5">
+        <v>1</v>
+      </c>
+      <c r="X31" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="Y31" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="Z31" s="5">
+        <v>0.01</v>
+      </c>
+      <c r="AA31" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="A32" t="s">
+        <v>18</v>
+      </c>
+      <c r="B32" t="s">
+        <v>47</v>
+      </c>
+      <c r="C32">
+        <v>15</v>
+      </c>
+      <c r="D32">
+        <v>45</v>
+      </c>
+      <c r="E32">
+        <v>30</v>
+      </c>
+      <c r="F32">
+        <v>4.5</v>
+      </c>
+      <c r="G32">
+        <v>4.5</v>
+      </c>
+      <c r="H32" s="2">
+        <v>1600</v>
+      </c>
+      <c r="I32" s="2">
+        <v>1500</v>
+      </c>
+      <c r="J32" s="2">
+        <v>200</v>
+      </c>
+      <c r="K32" s="2">
+        <v>15</v>
+      </c>
+      <c r="L32" s="2">
+        <v>1500</v>
+      </c>
+      <c r="M32" s="2">
+        <v>520</v>
+      </c>
+      <c r="N32" s="2">
+        <v>38</v>
+      </c>
+      <c r="O32" s="2">
+        <v>13</v>
+      </c>
+      <c r="P32" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q32" s="2">
+        <v>15</v>
+      </c>
+      <c r="R32" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="S32" s="2">
+        <v>15</v>
+      </c>
+      <c r="T32" s="2">
+        <v>80</v>
+      </c>
+      <c r="U32" s="6">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="V32" s="6">
+        <v>2.8</v>
+      </c>
+      <c r="W32" s="3">
+        <v>1.4</v>
+      </c>
+      <c r="X32" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y32" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z32" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="AA32" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="A33" t="s">
+        <v>113</v>
+      </c>
+      <c r="B33" t="s">
+        <v>47</v>
+      </c>
+      <c r="C33">
+        <v>15</v>
+      </c>
+      <c r="D33">
+        <v>45</v>
+      </c>
+      <c r="E33">
+        <v>30</v>
+      </c>
+      <c r="F33">
+        <v>11.4</v>
+      </c>
+      <c r="G33">
+        <v>4.5</v>
+      </c>
+      <c r="H33" s="2">
+        <v>4600</v>
+      </c>
+      <c r="I33" s="2">
+        <v>5500</v>
+      </c>
+      <c r="J33" s="2">
+        <v>250</v>
+      </c>
+      <c r="K33" s="2">
+        <v>15</v>
+      </c>
+      <c r="L33" s="2">
+        <v>4200</v>
+      </c>
+      <c r="M33" s="2">
+        <v>1800</v>
+      </c>
+      <c r="N33" s="2">
+        <v>68</v>
+      </c>
+      <c r="O33" s="2">
+        <v>45</v>
+      </c>
+      <c r="P33" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q33" s="2">
+        <v>15</v>
+      </c>
+      <c r="R33" s="6">
+        <v>2.4</v>
+      </c>
+      <c r="S33" s="2">
+        <v>15</v>
+      </c>
+      <c r="T33" s="2">
+        <v>67</v>
+      </c>
+      <c r="U33" s="6">
+        <v>1.8</v>
+      </c>
+      <c r="V33" s="6">
+        <v>1</v>
+      </c>
+      <c r="W33" s="6">
+        <v>1.2</v>
+      </c>
+      <c r="X33" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="Y33" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="Z33" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="AA33" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="A34" t="s">
+        <v>13</v>
+      </c>
+      <c r="B34" t="s">
+        <v>47</v>
+      </c>
+      <c r="C34">
+        <v>15</v>
+      </c>
+      <c r="D34">
+        <v>45</v>
+      </c>
+      <c r="E34">
+        <v>40</v>
+      </c>
+      <c r="F34">
+        <v>6.3</v>
+      </c>
+      <c r="G34">
+        <v>4.5</v>
+      </c>
+      <c r="H34" s="2">
+        <v>2100</v>
+      </c>
+      <c r="I34" s="2">
+        <v>1400</v>
+      </c>
+      <c r="J34" s="2">
+        <v>150</v>
+      </c>
+      <c r="K34" s="2">
+        <v>24</v>
+      </c>
+      <c r="L34" s="2">
+        <v>2000</v>
+      </c>
+      <c r="M34" s="2">
+        <v>350</v>
+      </c>
+      <c r="N34" s="2">
+        <v>14</v>
+      </c>
+      <c r="O34" s="2">
+        <v>13</v>
+      </c>
+      <c r="P34" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q34" s="2">
+        <v>20</v>
+      </c>
+      <c r="R34" s="6">
+        <v>2.1</v>
+      </c>
+      <c r="S34" s="2">
+        <v>20</v>
+      </c>
+      <c r="T34" s="2">
+        <v>50</v>
+      </c>
+      <c r="U34" s="3">
+        <v>5</v>
+      </c>
+      <c r="V34" s="3">
+        <v>3.5</v>
+      </c>
+      <c r="W34" s="3">
+        <v>1.45</v>
+      </c>
+      <c r="X34" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>1</v>
+      </c>
+      <c r="Z34" s="3">
+        <v>0.74</v>
+      </c>
+      <c r="AA34" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:27" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A35" t="s">
+        <v>31</v>
+      </c>
+      <c r="B35" t="s">
+        <v>46</v>
+      </c>
+      <c r="C35">
+        <v>30</v>
+      </c>
+      <c r="D35">
+        <v>11.56</v>
+      </c>
+      <c r="E35">
+        <v>30</v>
+      </c>
+      <c r="F35">
+        <v>4</v>
+      </c>
+      <c r="G35">
+        <v>4.5</v>
+      </c>
+      <c r="H35">
+        <v>1600</v>
+      </c>
+      <c r="I35">
+        <v>1280</v>
+      </c>
+      <c r="J35">
+        <v>200</v>
+      </c>
+      <c r="K35" s="2">
+        <v>25</v>
+      </c>
+      <c r="L35">
+        <v>1400</v>
+      </c>
+      <c r="M35">
+        <v>250</v>
+      </c>
+      <c r="N35">
+        <v>36</v>
+      </c>
+      <c r="O35" s="2">
+        <v>14</v>
+      </c>
+      <c r="P35" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q35" s="2">
+        <v>15</v>
+      </c>
+      <c r="R35" s="2">
+        <v>1.8</v>
+      </c>
+      <c r="S35" s="2">
+        <v>15</v>
+      </c>
+      <c r="T35" s="2">
+        <v>65</v>
+      </c>
+      <c r="U35">
+        <v>6.8</v>
+      </c>
+      <c r="V35">
+        <v>4.25</v>
+      </c>
+      <c r="W35">
+        <v>1.65</v>
+      </c>
+      <c r="X35">
+        <v>0.8</v>
+      </c>
+      <c r="Y35">
+        <v>0.8</v>
+      </c>
+      <c r="Z35">
+        <v>0.76</v>
+      </c>
+      <c r="AA35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:27" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A36" t="s">
+        <v>25</v>
+      </c>
+      <c r="B36" t="s">
+        <v>46</v>
+      </c>
+      <c r="C36">
+        <v>30</v>
+      </c>
+      <c r="D36">
+        <v>11.56</v>
+      </c>
+      <c r="E36">
+        <v>30</v>
+      </c>
+      <c r="F36">
+        <v>4.2</v>
+      </c>
+      <c r="G36">
+        <v>4.5</v>
+      </c>
+      <c r="H36" s="2">
+        <v>1700</v>
+      </c>
+      <c r="I36" s="2">
+        <v>1600</v>
+      </c>
+      <c r="J36" s="2">
+        <v>250</v>
+      </c>
+      <c r="K36" s="2">
+        <v>15</v>
+      </c>
+      <c r="L36" s="2">
+        <v>1550</v>
+      </c>
+      <c r="M36" s="2">
+        <v>550</v>
+      </c>
+      <c r="N36" s="2">
+        <v>60</v>
+      </c>
+      <c r="O36" s="2">
+        <v>37</v>
+      </c>
+      <c r="P36" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q36" s="2">
+        <v>15</v>
+      </c>
+      <c r="R36" s="2">
+        <v>2.6</v>
+      </c>
+      <c r="S36" s="2">
+        <v>15</v>
+      </c>
+      <c r="T36" s="2">
+        <v>67</v>
+      </c>
+      <c r="U36" s="3">
+        <v>4.8</v>
+      </c>
+      <c r="V36" s="3">
+        <v>2.7</v>
+      </c>
+      <c r="W36" s="2">
+        <v>1.4</v>
+      </c>
+      <c r="X36" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="Y36" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="Z36" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="AA36" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:27" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A37" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37" t="s">
+        <v>46</v>
+      </c>
+      <c r="C37">
+        <v>30</v>
+      </c>
+      <c r="D37">
+        <v>11.56</v>
+      </c>
+      <c r="E37">
+        <v>40</v>
+      </c>
+      <c r="F37">
+        <v>4.7</v>
+      </c>
+      <c r="G37">
+        <v>10</v>
+      </c>
+      <c r="H37">
+        <v>2000</v>
+      </c>
+      <c r="I37">
+        <v>2500</v>
+      </c>
+      <c r="J37">
+        <v>360</v>
+      </c>
+      <c r="K37">
+        <v>25</v>
+      </c>
+      <c r="L37">
+        <v>1800</v>
+      </c>
+      <c r="M37">
+        <v>500</v>
+      </c>
+      <c r="N37">
+        <v>17</v>
+      </c>
+      <c r="O37">
+        <v>44</v>
+      </c>
+      <c r="P37">
+        <v>20</v>
+      </c>
+      <c r="Q37">
+        <v>20</v>
+      </c>
+      <c r="R37">
+        <v>3.2</v>
+      </c>
+      <c r="S37">
+        <v>20</v>
+      </c>
+      <c r="T37">
+        <v>100</v>
+      </c>
+      <c r="U37">
+        <v>2.8</v>
+      </c>
+      <c r="V37">
+        <v>2.1</v>
+      </c>
+      <c r="W37">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="X37">
+        <v>0.5</v>
+      </c>
+      <c r="Y37">
+        <v>0.5</v>
+      </c>
+      <c r="Z37">
+        <v>0.79</v>
+      </c>
+      <c r="AA37">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:27" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A38" t="s">
+        <v>5</v>
+      </c>
+      <c r="B38" t="s">
+        <v>46</v>
+      </c>
+      <c r="C38">
+        <v>30</v>
+      </c>
+      <c r="D38">
         <f>3.4*3.4</f>
         <v>11.559999999999999</v>
       </c>
-      <c r="E15">
+      <c r="E38">
         <v>80</v>
       </c>
-      <c r="F15">
-        <v>7.5</v>
-      </c>
-      <c r="G15">
-        <v>10</v>
-      </c>
-      <c r="H15">
-        <v>2750</v>
-      </c>
-      <c r="I15">
-        <v>1700</v>
-      </c>
-      <c r="J15">
-        <v>200</v>
-      </c>
-      <c r="K15">
+      <c r="F38">
+        <v>5</v>
+      </c>
+      <c r="G38">
+        <v>4.5</v>
+      </c>
+      <c r="H38">
+        <v>2100</v>
+      </c>
+      <c r="I38">
+        <v>1200</v>
+      </c>
+      <c r="J38">
+        <v>300</v>
+      </c>
+      <c r="K38">
         <v>40</v>
       </c>
-      <c r="L15">
-        <v>2400</v>
-      </c>
-      <c r="M15">
-        <v>250</v>
-      </c>
-      <c r="N15">
-        <v>10</v>
-      </c>
-      <c r="O15">
+      <c r="L38">
+        <v>1900</v>
+      </c>
+      <c r="M38">
+        <v>280</v>
+      </c>
+      <c r="N38">
+        <v>12</v>
+      </c>
+      <c r="O38">
+        <v>27</v>
+      </c>
+      <c r="P38">
+        <v>20</v>
+      </c>
+      <c r="Q38">
+        <v>40</v>
+      </c>
+      <c r="R38">
+        <v>4</v>
+      </c>
+      <c r="S38">
+        <v>40</v>
+      </c>
+      <c r="T38">
+        <v>52</v>
+      </c>
+      <c r="U38">
+        <v>7.4</v>
+      </c>
+      <c r="V38">
+        <v>5.9</v>
+      </c>
+      <c r="W38">
+        <v>1.3</v>
+      </c>
+      <c r="X38">
+        <v>0.5</v>
+      </c>
+      <c r="Y38">
+        <v>0.5</v>
+      </c>
+      <c r="Z38">
+        <v>0.85</v>
+      </c>
+      <c r="AA38">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:27" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A39" t="s">
+        <v>7</v>
+      </c>
+      <c r="B39" t="s">
+        <v>46</v>
+      </c>
+      <c r="C39">
+        <v>30</v>
+      </c>
+      <c r="D39">
+        <v>11.56</v>
+      </c>
+      <c r="E39">
+        <v>60</v>
+      </c>
+      <c r="F39">
+        <v>5</v>
+      </c>
+      <c r="G39">
+        <v>4.5</v>
+      </c>
+      <c r="H39">
+        <v>2300</v>
+      </c>
+      <c r="I39">
+        <v>1500</v>
+      </c>
+      <c r="J39">
+        <v>400</v>
+      </c>
+      <c r="K39">
+        <v>40</v>
+      </c>
+      <c r="L39">
+        <v>1900</v>
+      </c>
+      <c r="M39">
+        <v>330</v>
+      </c>
+      <c r="N39">
+        <v>16</v>
+      </c>
+      <c r="O39">
+        <v>17</v>
+      </c>
+      <c r="P39">
+        <v>20</v>
+      </c>
+      <c r="Q39">
+        <v>30</v>
+      </c>
+      <c r="R39">
+        <v>4.8</v>
+      </c>
+      <c r="S39">
+        <v>30</v>
+      </c>
+      <c r="T39">
+        <v>66</v>
+      </c>
+      <c r="U39">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="V39">
+        <v>3.9</v>
+      </c>
+      <c r="W39">
+        <v>1.8</v>
+      </c>
+      <c r="X39">
+        <v>0.5</v>
+      </c>
+      <c r="Y39">
+        <v>0.5</v>
+      </c>
+      <c r="Z39">
+        <v>0.83</v>
+      </c>
+      <c r="AA39">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:27" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A40" t="s">
+        <v>120</v>
+      </c>
+      <c r="B40" t="s">
+        <v>46</v>
+      </c>
+      <c r="C40">
+        <v>30</v>
+      </c>
+      <c r="D40">
+        <v>11.56</v>
+      </c>
+      <c r="E40">
+        <v>30</v>
+      </c>
+      <c r="F40">
+        <v>5.7</v>
+      </c>
+      <c r="G40">
+        <v>10</v>
+      </c>
+      <c r="H40" s="2">
+        <v>2050</v>
+      </c>
+      <c r="I40" s="2">
+        <v>1600</v>
+      </c>
+      <c r="J40" s="2">
+        <v>270</v>
+      </c>
+      <c r="K40" s="2">
+        <v>10</v>
+      </c>
+      <c r="L40" s="2">
+        <v>1800</v>
+      </c>
+      <c r="M40" s="2">
+        <v>600</v>
+      </c>
+      <c r="N40" s="2">
+        <v>50</v>
+      </c>
+      <c r="O40" s="2">
+        <v>24</v>
+      </c>
+      <c r="P40" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q40" s="2">
+        <v>15</v>
+      </c>
+      <c r="R40" s="6">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="S40" s="2">
+        <v>15</v>
+      </c>
+      <c r="T40" s="2">
         <v>100</v>
       </c>
-      <c r="P15">
-        <v>18</v>
-      </c>
-      <c r="Q15">
-        <v>40</v>
-      </c>
-      <c r="R15">
-        <v>4</v>
-      </c>
-      <c r="S15">
-        <v>40</v>
-      </c>
-      <c r="T15">
+      <c r="U40" s="6">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="V40" s="6">
+        <v>2.8</v>
+      </c>
+      <c r="W40" s="6">
+        <v>2</v>
+      </c>
+      <c r="X40" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="Y40" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="Z40" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="AA40" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:27" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A41" t="s">
+        <v>9</v>
+      </c>
+      <c r="B41" t="s">
+        <v>46</v>
+      </c>
+      <c r="C41">
+        <v>30</v>
+      </c>
+      <c r="D41">
+        <v>11.56</v>
+      </c>
+      <c r="E41">
+        <v>60</v>
+      </c>
+      <c r="F41">
+        <v>6.2</v>
+      </c>
+      <c r="G41">
+        <v>4.5</v>
+      </c>
+      <c r="H41">
+        <v>2200</v>
+      </c>
+      <c r="I41">
+        <v>1600</v>
+      </c>
+      <c r="J41">
+        <v>300</v>
+      </c>
+      <c r="K41">
+        <v>24</v>
+      </c>
+      <c r="L41">
+        <v>2000</v>
+      </c>
+      <c r="M41">
+        <v>560</v>
+      </c>
+      <c r="N41">
+        <v>32</v>
+      </c>
+      <c r="O41">
+        <v>20</v>
+      </c>
+      <c r="P41">
+        <v>10</v>
+      </c>
+      <c r="Q41">
+        <v>30</v>
+      </c>
+      <c r="R41">
+        <v>4.5</v>
+      </c>
+      <c r="S41">
+        <v>30</v>
+      </c>
+      <c r="T41">
         <v>54</v>
       </c>
-      <c r="U15">
-        <v>5.5</v>
-      </c>
-      <c r="V15">
-        <v>5.5</v>
-      </c>
-      <c r="W15">
-        <v>1.35</v>
-      </c>
-      <c r="X15">
+      <c r="U41">
+        <v>4.8</v>
+      </c>
+      <c r="V41">
+        <v>3.4</v>
+      </c>
+      <c r="W41">
+        <v>0.85</v>
+      </c>
+      <c r="X41">
         <v>0.5</v>
       </c>
-      <c r="Y15">
+      <c r="Y41">
         <v>0.5</v>
       </c>
-      <c r="Z15">
-        <v>0.7</v>
-      </c>
-      <c r="AA15">
-        <v>1</v>
+      <c r="Z41">
+        <v>0.75</v>
+      </c>
+      <c r="AA41">
+        <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" t="s">
+    <row r="42" spans="1:27" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A42" t="s">
+        <v>8</v>
+      </c>
+      <c r="B42" t="s">
         <v>46</v>
       </c>
-      <c r="C16">
-        <v>30</v>
-      </c>
-      <c r="D16">
+      <c r="C42">
+        <v>30</v>
+      </c>
+      <c r="D42">
         <v>11.56</v>
       </c>
-      <c r="E16">
-        <v>40</v>
-      </c>
-      <c r="F16" s="7">
-        <v>2.75</v>
-      </c>
-      <c r="G16" s="7">
+      <c r="E42">
+        <v>60</v>
+      </c>
+      <c r="F42">
+        <v>7</v>
+      </c>
+      <c r="G42">
         <v>4.5</v>
       </c>
-      <c r="H16" s="2">
-        <v>1550</v>
-      </c>
-      <c r="I16" s="2">
-        <v>1000</v>
-      </c>
-      <c r="J16" s="2">
-        <v>100</v>
-      </c>
-      <c r="K16" s="2">
-        <v>30</v>
-      </c>
-      <c r="L16" s="2">
-        <v>1450</v>
-      </c>
-      <c r="M16" s="2">
-        <v>200</v>
-      </c>
-      <c r="N16" s="2">
-        <v>13</v>
-      </c>
-      <c r="O16" s="2">
-        <v>21</v>
-      </c>
-      <c r="P16" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q16" s="2">
-        <v>20</v>
-      </c>
-      <c r="R16" s="6">
-        <v>3</v>
-      </c>
-      <c r="S16" s="2">
-        <v>20</v>
-      </c>
-      <c r="T16" s="2">
-        <v>70</v>
-      </c>
-      <c r="U16" s="6">
-        <v>7.4</v>
-      </c>
-      <c r="V16" s="6">
+      <c r="H42">
+        <v>3000</v>
+      </c>
+      <c r="I42">
+        <v>2000</v>
+      </c>
+      <c r="J42">
+        <v>300</v>
+      </c>
+      <c r="K42">
+        <v>24</v>
+      </c>
+      <c r="L42">
+        <v>2500</v>
+      </c>
+      <c r="M42">
+        <v>700</v>
+      </c>
+      <c r="N42">
+        <v>35</v>
+      </c>
+      <c r="O42">
+        <v>25</v>
+      </c>
+      <c r="P42">
+        <v>10</v>
+      </c>
+      <c r="Q42">
+        <v>30</v>
+      </c>
+      <c r="R42">
+        <v>4.7</v>
+      </c>
+      <c r="S42">
+        <v>30</v>
+      </c>
+      <c r="T42">
+        <v>57</v>
+      </c>
+      <c r="U42">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="V42">
+        <v>2.9</v>
+      </c>
+      <c r="W42">
+        <v>0.85</v>
+      </c>
+      <c r="X42">
+        <v>0.5</v>
+      </c>
+      <c r="Y42">
+        <v>0.5</v>
+      </c>
+      <c r="Z42">
+        <v>0.74</v>
+      </c>
+      <c r="AA42">
         <v>5</v>
       </c>
-      <c r="W16" s="6">
-        <v>1.8</v>
-      </c>
-      <c r="X16" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="Y16" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="Z16" s="6">
-        <v>0.7</v>
-      </c>
-      <c r="AA16" s="3">
-        <v>1</v>
-      </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" t="s">
+    <row r="43" spans="1:27" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A43" t="s">
+        <v>6</v>
+      </c>
+      <c r="B43" t="s">
         <v>46</v>
       </c>
-      <c r="C17">
-        <v>30</v>
-      </c>
-      <c r="D17">
-        <v>11.56</v>
-      </c>
-      <c r="E17">
-        <v>30</v>
-      </c>
-      <c r="F17">
-        <v>4.2</v>
-      </c>
-      <c r="G17">
-        <v>4.5</v>
-      </c>
-      <c r="H17" s="2">
-        <v>1700</v>
-      </c>
-      <c r="I17" s="2">
-        <v>1600</v>
-      </c>
-      <c r="J17" s="2">
-        <v>250</v>
-      </c>
-      <c r="K17" s="2">
-        <v>15</v>
-      </c>
-      <c r="L17" s="2">
-        <v>1550</v>
-      </c>
-      <c r="M17" s="2">
-        <v>550</v>
-      </c>
-      <c r="N17" s="2">
-        <v>60</v>
-      </c>
-      <c r="O17" s="2">
-        <v>37</v>
-      </c>
-      <c r="P17" s="2">
-        <v>10</v>
-      </c>
-      <c r="Q17" s="2">
-        <v>15</v>
-      </c>
-      <c r="R17" s="2">
-        <v>2.6</v>
-      </c>
-      <c r="S17" s="2">
-        <v>15</v>
-      </c>
-      <c r="T17" s="2">
-        <v>67</v>
-      </c>
-      <c r="U17" s="3">
-        <v>4.8</v>
-      </c>
-      <c r="V17" s="3">
-        <v>2.7</v>
-      </c>
-      <c r="W17" s="2">
-        <v>1.4</v>
-      </c>
-      <c r="X17" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="Y17" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="Z17" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="AA17" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>11</v>
-      </c>
-      <c r="B18" t="s">
-        <v>46</v>
-      </c>
-      <c r="C18">
-        <v>30</v>
-      </c>
-      <c r="D18">
-        <v>11.56</v>
-      </c>
-      <c r="E18">
-        <v>40</v>
-      </c>
-      <c r="F18">
-        <v>4.7</v>
-      </c>
-      <c r="G18">
-        <v>10</v>
-      </c>
-      <c r="H18">
-        <v>2000</v>
-      </c>
-      <c r="I18">
-        <v>2500</v>
-      </c>
-      <c r="J18">
-        <v>360</v>
-      </c>
-      <c r="K18">
-        <v>25</v>
-      </c>
-      <c r="L18">
-        <v>1800</v>
-      </c>
-      <c r="M18">
-        <v>500</v>
-      </c>
-      <c r="N18">
-        <v>17</v>
-      </c>
-      <c r="O18">
-        <v>44</v>
-      </c>
-      <c r="P18">
-        <v>20</v>
-      </c>
-      <c r="Q18">
-        <v>20</v>
-      </c>
-      <c r="R18">
-        <v>3.2</v>
-      </c>
-      <c r="S18">
-        <v>20</v>
-      </c>
-      <c r="T18">
-        <v>100</v>
-      </c>
-      <c r="U18">
-        <v>2.8</v>
-      </c>
-      <c r="V18">
-        <v>2.1</v>
-      </c>
-      <c r="W18">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="X18">
-        <v>0.5</v>
-      </c>
-      <c r="Y18">
-        <v>0.5</v>
-      </c>
-      <c r="Z18">
-        <v>0.79</v>
-      </c>
-      <c r="AA18">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B19" t="s">
-        <v>46</v>
-      </c>
-      <c r="C19">
-        <v>30</v>
-      </c>
-      <c r="D19">
-        <v>11.56</v>
-      </c>
-      <c r="E19">
-        <v>40</v>
-      </c>
-      <c r="F19">
-        <v>0.9</v>
-      </c>
-      <c r="G19">
-        <v>4.5</v>
-      </c>
-      <c r="H19">
-        <v>760</v>
-      </c>
-      <c r="I19">
-        <v>900</v>
-      </c>
-      <c r="J19">
-        <v>100</v>
-      </c>
-      <c r="K19">
-        <v>25</v>
-      </c>
-      <c r="L19">
-        <v>650</v>
-      </c>
-      <c r="M19">
-        <v>95</v>
-      </c>
-      <c r="N19">
-        <v>11</v>
-      </c>
-      <c r="O19">
-        <v>21</v>
-      </c>
-      <c r="P19">
-        <v>20</v>
-      </c>
-      <c r="Q19">
-        <v>20</v>
-      </c>
-      <c r="R19">
-        <v>0.65</v>
-      </c>
-      <c r="S19">
-        <v>20</v>
-      </c>
-      <c r="T19">
-        <v>64</v>
-      </c>
-      <c r="U19">
-        <v>7</v>
-      </c>
-      <c r="V19">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="W19">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="X19">
-        <v>1</v>
-      </c>
-      <c r="Y19">
-        <v>1</v>
-      </c>
-      <c r="Z19">
-        <v>0.85</v>
-      </c>
-      <c r="AA19">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>5</v>
-      </c>
-      <c r="B20" t="s">
-        <v>46</v>
-      </c>
-      <c r="C20">
-        <v>30</v>
-      </c>
-      <c r="D20">
+      <c r="C43">
+        <v>30</v>
+      </c>
+      <c r="D43">
         <f>3.4*3.4</f>
         <v>11.559999999999999</v>
       </c>
-      <c r="E20">
+      <c r="E43">
         <v>80</v>
       </c>
-      <c r="F20">
-        <v>5</v>
-      </c>
-      <c r="G20">
-        <v>4.5</v>
-      </c>
-      <c r="H20">
-        <v>2100</v>
-      </c>
-      <c r="I20">
-        <v>1200</v>
-      </c>
-      <c r="J20">
-        <v>300</v>
-      </c>
-      <c r="K20">
+      <c r="F43">
+        <v>7.5</v>
+      </c>
+      <c r="G43">
+        <v>10</v>
+      </c>
+      <c r="H43">
+        <v>2750</v>
+      </c>
+      <c r="I43">
+        <v>1700</v>
+      </c>
+      <c r="J43">
+        <v>200</v>
+      </c>
+      <c r="K43">
         <v>40</v>
       </c>
-      <c r="L20">
-        <v>1900</v>
-      </c>
-      <c r="M20">
-        <v>280</v>
-      </c>
-      <c r="N20">
-        <v>12</v>
-      </c>
-      <c r="O20">
-        <v>27</v>
-      </c>
-      <c r="P20">
-        <v>20</v>
-      </c>
-      <c r="Q20">
+      <c r="L43">
+        <v>2400</v>
+      </c>
+      <c r="M43">
+        <v>250</v>
+      </c>
+      <c r="N43">
+        <v>10</v>
+      </c>
+      <c r="O43">
+        <v>100</v>
+      </c>
+      <c r="P43">
+        <v>18</v>
+      </c>
+      <c r="Q43">
         <v>40</v>
       </c>
-      <c r="R20">
+      <c r="R43">
         <v>4</v>
       </c>
-      <c r="S20">
+      <c r="S43">
         <v>40</v>
       </c>
-      <c r="T20">
-        <v>52</v>
-      </c>
-      <c r="U20">
-        <v>7.4</v>
-      </c>
-      <c r="V20">
-        <v>5.9</v>
-      </c>
-      <c r="W20">
-        <v>1.3</v>
-      </c>
-      <c r="X20">
+      <c r="T43">
+        <v>54</v>
+      </c>
+      <c r="U43">
+        <v>5.5</v>
+      </c>
+      <c r="V43">
+        <v>5.5</v>
+      </c>
+      <c r="W43">
+        <v>1.35</v>
+      </c>
+      <c r="X43">
         <v>0.5</v>
       </c>
-      <c r="Y20">
+      <c r="Y43">
         <v>0.5</v>
       </c>
-      <c r="Z20">
-        <v>0.85</v>
-      </c>
-      <c r="AA20">
-        <v>20</v>
+      <c r="Z43">
+        <v>0.7</v>
+      </c>
+      <c r="AA43">
+        <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>7</v>
-      </c>
-      <c r="B21" t="s">
+    <row r="44" spans="1:27" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A44" t="s">
+        <v>23</v>
+      </c>
+      <c r="B44" t="s">
         <v>46</v>
       </c>
-      <c r="C21">
-        <v>30</v>
-      </c>
-      <c r="D21">
+      <c r="C44">
+        <v>30</v>
+      </c>
+      <c r="D44">
         <v>11.56</v>
-      </c>
-      <c r="E21">
-        <v>60</v>
-      </c>
-      <c r="F21">
-        <v>5</v>
-      </c>
-      <c r="G21">
-        <v>4.5</v>
-      </c>
-      <c r="H21">
-        <v>2300</v>
-      </c>
-      <c r="I21">
-        <v>1500</v>
-      </c>
-      <c r="J21">
-        <v>400</v>
-      </c>
-      <c r="K21">
-        <v>40</v>
-      </c>
-      <c r="L21">
-        <v>1900</v>
-      </c>
-      <c r="M21">
-        <v>330</v>
-      </c>
-      <c r="N21">
-        <v>16</v>
-      </c>
-      <c r="O21">
-        <v>17</v>
-      </c>
-      <c r="P21">
-        <v>20</v>
-      </c>
-      <c r="Q21">
-        <v>30</v>
-      </c>
-      <c r="R21">
-        <v>4.8</v>
-      </c>
-      <c r="S21">
-        <v>30</v>
-      </c>
-      <c r="T21">
-        <v>66</v>
-      </c>
-      <c r="U21">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="V21">
-        <v>3.9</v>
-      </c>
-      <c r="W21">
-        <v>1.8</v>
-      </c>
-      <c r="X21">
-        <v>0.5</v>
-      </c>
-      <c r="Y21">
-        <v>0.5</v>
-      </c>
-      <c r="Z21">
-        <v>0.83</v>
-      </c>
-      <c r="AA21">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>19</v>
-      </c>
-      <c r="B22" t="s">
-        <v>46</v>
-      </c>
-      <c r="C22">
-        <v>30</v>
-      </c>
-      <c r="D22">
-        <v>11.56</v>
-      </c>
-      <c r="E22">
-        <v>40</v>
-      </c>
-      <c r="F22">
-        <v>3.2</v>
-      </c>
-      <c r="G22">
-        <v>4.5</v>
-      </c>
-      <c r="H22" s="2">
-        <v>2500</v>
-      </c>
-      <c r="I22" s="2">
-        <v>1500</v>
-      </c>
-      <c r="J22" s="2">
-        <v>200</v>
-      </c>
-      <c r="K22" s="2">
-        <v>24</v>
-      </c>
-      <c r="L22" s="2">
-        <v>1375</v>
-      </c>
-      <c r="M22" s="2">
-        <v>1130</v>
-      </c>
-      <c r="N22" s="2">
-        <v>50</v>
-      </c>
-      <c r="O22" s="2">
-        <v>17</v>
-      </c>
-      <c r="P22" s="2">
-        <v>10</v>
-      </c>
-      <c r="Q22" s="2">
-        <v>20</v>
-      </c>
-      <c r="R22" s="2">
-        <v>2.5</v>
-      </c>
-      <c r="S22" s="2">
-        <v>20</v>
-      </c>
-      <c r="T22" s="2">
-        <v>65</v>
-      </c>
-      <c r="U22" s="3">
-        <v>6.2</v>
-      </c>
-      <c r="V22" s="3">
-        <v>4.5</v>
-      </c>
-      <c r="W22" s="3">
-        <v>0.9</v>
-      </c>
-      <c r="X22" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23">
-        <v>30</v>
-      </c>
-      <c r="D23">
-        <v>11.56</v>
-      </c>
-      <c r="E23">
-        <v>30</v>
-      </c>
-      <c r="F23">
-        <v>3.7</v>
-      </c>
-      <c r="G23">
-        <v>4.5</v>
-      </c>
-      <c r="H23" s="2">
-        <v>1200</v>
-      </c>
-      <c r="I23" s="2">
-        <v>1200</v>
-      </c>
-      <c r="J23" s="2">
-        <v>150</v>
-      </c>
-      <c r="K23" s="2">
-        <v>12</v>
-      </c>
-      <c r="L23" s="2">
-        <v>1175</v>
-      </c>
-      <c r="M23" s="2">
-        <v>450</v>
-      </c>
-      <c r="N23" s="2">
-        <v>30</v>
-      </c>
-      <c r="O23" s="2">
-        <v>10</v>
-      </c>
-      <c r="P23" s="2">
-        <v>10</v>
-      </c>
-      <c r="Q23">
-        <v>15</v>
-      </c>
-      <c r="R23">
-        <v>1.4</v>
-      </c>
-      <c r="S23">
-        <v>15</v>
-      </c>
-      <c r="T23">
-        <v>53</v>
-      </c>
-      <c r="U23">
-        <v>3.8</v>
-      </c>
-      <c r="V23">
-        <v>2.7</v>
-      </c>
-      <c r="W23">
-        <v>0.9</v>
-      </c>
-      <c r="X23" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="Y23" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="Z23">
-        <v>0.76</v>
-      </c>
-      <c r="AA23">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>23</v>
-      </c>
-      <c r="B24" t="s">
-        <v>46</v>
-      </c>
-      <c r="C24">
-        <v>30</v>
-      </c>
-      <c r="D24">
-        <v>11.56</v>
-      </c>
-      <c r="E24">
-        <v>40</v>
-      </c>
-      <c r="F24">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="G24">
-        <v>4.5</v>
-      </c>
-      <c r="H24">
-        <v>2700</v>
-      </c>
-      <c r="I24">
-        <v>1400</v>
-      </c>
-      <c r="J24">
-        <v>70</v>
-      </c>
-      <c r="K24">
-        <v>30</v>
-      </c>
-      <c r="L24">
-        <v>2450</v>
-      </c>
-      <c r="M24">
-        <v>350</v>
-      </c>
-      <c r="N24">
-        <v>20</v>
-      </c>
-      <c r="O24">
-        <v>10</v>
-      </c>
-      <c r="P24">
-        <v>20.8</v>
-      </c>
-      <c r="Q24">
-        <v>20</v>
-      </c>
-      <c r="R24">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="S24">
-        <v>20</v>
-      </c>
-      <c r="T24">
-        <v>76</v>
-      </c>
-      <c r="U24">
-        <v>3.88</v>
-      </c>
-      <c r="V24">
-        <v>2.71</v>
-      </c>
-      <c r="W24">
-        <v>1.3</v>
-      </c>
-      <c r="X24">
-        <v>0.8</v>
-      </c>
-      <c r="Y24">
-        <v>0.8</v>
-      </c>
-      <c r="Z24">
-        <v>0.74</v>
-      </c>
-      <c r="AA24">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>22</v>
-      </c>
-      <c r="B25" t="s">
-        <v>46</v>
-      </c>
-      <c r="C25">
-        <v>30</v>
-      </c>
-      <c r="D25">
-        <v>11.56</v>
-      </c>
-      <c r="E25">
-        <v>40</v>
-      </c>
-      <c r="F25">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="G25">
-        <v>4.5</v>
-      </c>
-      <c r="H25">
-        <v>3600</v>
-      </c>
-      <c r="I25">
-        <v>1600</v>
-      </c>
-      <c r="J25">
-        <v>350</v>
-      </c>
-      <c r="K25">
-        <v>24</v>
-      </c>
-      <c r="L25">
-        <v>3250</v>
-      </c>
-      <c r="M25">
-        <v>400</v>
-      </c>
-      <c r="N25">
-        <v>50</v>
-      </c>
-      <c r="O25">
-        <v>23</v>
-      </c>
-      <c r="P25">
-        <v>10</v>
-      </c>
-      <c r="Q25">
-        <v>20</v>
-      </c>
-      <c r="R25">
-        <v>4.2</v>
-      </c>
-      <c r="S25">
-        <v>20</v>
-      </c>
-      <c r="T25">
-        <v>70</v>
-      </c>
-      <c r="U25">
-        <v>3.85</v>
-      </c>
-      <c r="V25">
-        <v>2.85</v>
-      </c>
-      <c r="W25">
-        <v>1.4</v>
-      </c>
-      <c r="X25">
-        <v>0.5</v>
-      </c>
-      <c r="Y25">
-        <v>0.5</v>
-      </c>
-      <c r="Z25">
-        <v>0.74</v>
-      </c>
-      <c r="AA25">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>8</v>
-      </c>
-      <c r="B26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C26">
-        <v>30</v>
-      </c>
-      <c r="D26">
-        <v>11.56</v>
-      </c>
-      <c r="E26">
-        <v>60</v>
-      </c>
-      <c r="F26">
-        <v>7</v>
-      </c>
-      <c r="G26">
-        <v>4.5</v>
-      </c>
-      <c r="H26">
-        <v>3000</v>
-      </c>
-      <c r="I26">
-        <v>2000</v>
-      </c>
-      <c r="J26">
-        <v>300</v>
-      </c>
-      <c r="K26">
-        <v>24</v>
-      </c>
-      <c r="L26">
-        <v>2500</v>
-      </c>
-      <c r="M26">
-        <v>700</v>
-      </c>
-      <c r="N26">
-        <v>35</v>
-      </c>
-      <c r="O26">
-        <v>25</v>
-      </c>
-      <c r="P26">
-        <v>10</v>
-      </c>
-      <c r="Q26">
-        <v>30</v>
-      </c>
-      <c r="R26">
-        <v>4.7</v>
-      </c>
-      <c r="S26">
-        <v>30</v>
-      </c>
-      <c r="T26">
-        <v>57</v>
-      </c>
-      <c r="U26">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="V26">
-        <v>2.9</v>
-      </c>
-      <c r="W26">
-        <v>0.85</v>
-      </c>
-      <c r="X26">
-        <v>0.5</v>
-      </c>
-      <c r="Y26">
-        <v>0.5</v>
-      </c>
-      <c r="Z26">
-        <v>0.74</v>
-      </c>
-      <c r="AA26">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>9</v>
-      </c>
-      <c r="B27" t="s">
-        <v>46</v>
-      </c>
-      <c r="C27">
-        <v>30</v>
-      </c>
-      <c r="D27">
-        <v>11.56</v>
-      </c>
-      <c r="E27">
-        <v>60</v>
-      </c>
-      <c r="F27">
-        <v>6.2</v>
-      </c>
-      <c r="G27">
-        <v>4.5</v>
-      </c>
-      <c r="H27">
-        <v>2200</v>
-      </c>
-      <c r="I27">
-        <v>1600</v>
-      </c>
-      <c r="J27">
-        <v>300</v>
-      </c>
-      <c r="K27">
-        <v>24</v>
-      </c>
-      <c r="L27">
-        <v>2000</v>
-      </c>
-      <c r="M27">
-        <v>560</v>
-      </c>
-      <c r="N27">
-        <v>32</v>
-      </c>
-      <c r="O27">
-        <v>20</v>
-      </c>
-      <c r="P27">
-        <v>10</v>
-      </c>
-      <c r="Q27">
-        <v>30</v>
-      </c>
-      <c r="R27">
-        <v>4.5</v>
-      </c>
-      <c r="S27">
-        <v>30</v>
-      </c>
-      <c r="T27">
-        <v>54</v>
-      </c>
-      <c r="U27">
-        <v>4.8</v>
-      </c>
-      <c r="V27">
-        <v>3.4</v>
-      </c>
-      <c r="W27">
-        <v>0.85</v>
-      </c>
-      <c r="X27">
-        <v>0.5</v>
-      </c>
-      <c r="Y27">
-        <v>0.5</v>
-      </c>
-      <c r="Z27">
-        <v>0.75</v>
-      </c>
-      <c r="AA27">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B28" t="s">
-        <v>46</v>
-      </c>
-      <c r="C28">
-        <v>30</v>
-      </c>
-      <c r="D28">
-        <v>11.56</v>
-      </c>
-      <c r="E28">
-        <v>40</v>
-      </c>
-      <c r="F28">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="G28">
-        <v>4.5</v>
-      </c>
-      <c r="H28">
-        <v>4100</v>
-      </c>
-      <c r="I28">
-        <v>2000</v>
-      </c>
-      <c r="J28">
-        <v>350</v>
-      </c>
-      <c r="K28">
-        <v>24</v>
-      </c>
-      <c r="L28">
-        <v>3700</v>
-      </c>
-      <c r="M28">
-        <v>600</v>
-      </c>
-      <c r="N28">
-        <v>90</v>
-      </c>
-      <c r="O28">
-        <v>23</v>
-      </c>
-      <c r="P28">
-        <v>10</v>
-      </c>
-      <c r="Q28">
-        <v>20</v>
-      </c>
-      <c r="R28">
-        <v>4</v>
-      </c>
-      <c r="S28">
-        <v>20</v>
-      </c>
-      <c r="T28">
-        <v>98</v>
-      </c>
-      <c r="U28">
-        <v>2.4</v>
-      </c>
-      <c r="V28">
-        <v>1.8</v>
-      </c>
-      <c r="W28">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="X28">
-        <v>0.5</v>
-      </c>
-      <c r="Y28">
-        <v>0.5</v>
-      </c>
-      <c r="Z28">
-        <v>0.73</v>
-      </c>
-      <c r="AA28">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>20</v>
-      </c>
-      <c r="B29" t="s">
-        <v>46</v>
-      </c>
-      <c r="C29">
-        <v>30</v>
-      </c>
-      <c r="D29">
-        <v>11.56</v>
-      </c>
-      <c r="E29">
-        <v>40</v>
-      </c>
-      <c r="F29">
-        <v>2.9</v>
-      </c>
-      <c r="G29">
-        <v>4.5</v>
-      </c>
-      <c r="H29">
-        <v>950</v>
-      </c>
-      <c r="I29">
-        <v>500</v>
-      </c>
-      <c r="J29">
-        <v>70</v>
-      </c>
-      <c r="K29">
-        <v>25</v>
-      </c>
-      <c r="L29" s="2">
-        <v>875</v>
-      </c>
-      <c r="M29" s="2">
-        <v>150</v>
-      </c>
-      <c r="N29" s="2">
-        <v>16</v>
-      </c>
-      <c r="O29" s="2">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="P29" s="2">
-        <v>10</v>
-      </c>
-      <c r="Q29" s="2">
-        <v>20</v>
-      </c>
-      <c r="R29" s="6">
-        <v>0.9</v>
-      </c>
-      <c r="S29">
-        <v>20</v>
-      </c>
-      <c r="T29" s="2">
-        <v>45</v>
-      </c>
-      <c r="U29">
-        <v>9.6</v>
-      </c>
-      <c r="V29">
-        <v>6.7</v>
-      </c>
-      <c r="W29" s="4">
-        <v>3.2</v>
-      </c>
-      <c r="X29" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="Y29" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="Z29" s="3">
-        <v>0.82</v>
-      </c>
-      <c r="AA29" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>29</v>
-      </c>
-      <c r="B30" t="s">
-        <v>46</v>
-      </c>
-      <c r="C30">
-        <v>30</v>
-      </c>
-      <c r="D30">
-        <v>11.56</v>
-      </c>
-      <c r="E30">
-        <v>30</v>
-      </c>
-      <c r="F30">
-        <v>3.6</v>
-      </c>
-      <c r="G30">
-        <v>10</v>
-      </c>
-      <c r="H30" s="2">
-        <v>1450</v>
-      </c>
-      <c r="I30" s="2">
-        <v>1100</v>
-      </c>
-      <c r="J30" s="2">
-        <v>200</v>
-      </c>
-      <c r="K30" s="2">
-        <v>25</v>
-      </c>
-      <c r="L30" s="2">
-        <v>1300</v>
-      </c>
-      <c r="M30" s="2">
-        <v>250</v>
-      </c>
-      <c r="N30" s="2">
-        <v>30</v>
-      </c>
-      <c r="O30" s="2">
-        <v>18</v>
-      </c>
-      <c r="P30" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q30" s="2">
-        <v>15</v>
-      </c>
-      <c r="R30" s="6">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="S30" s="2">
-        <v>15</v>
-      </c>
-      <c r="T30" s="2">
-        <v>77</v>
-      </c>
-      <c r="U30" s="6">
-        <v>6</v>
-      </c>
-      <c r="V30" s="6">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="W30" s="6">
-        <v>1.7</v>
-      </c>
-      <c r="X30" s="6">
-        <v>0.8</v>
-      </c>
-      <c r="Y30" s="6">
-        <v>0.8</v>
-      </c>
-      <c r="Z30" s="6">
-        <v>0.7</v>
-      </c>
-      <c r="AA30" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>31</v>
-      </c>
-      <c r="B31" t="s">
-        <v>46</v>
-      </c>
-      <c r="C31">
-        <v>30</v>
-      </c>
-      <c r="D31">
-        <v>11.56</v>
-      </c>
-      <c r="E31">
-        <v>30</v>
-      </c>
-      <c r="F31">
-        <v>4</v>
-      </c>
-      <c r="G31">
-        <v>4.5</v>
-      </c>
-      <c r="H31">
-        <v>1600</v>
-      </c>
-      <c r="I31">
-        <v>1280</v>
-      </c>
-      <c r="J31">
-        <v>200</v>
-      </c>
-      <c r="K31" s="2">
-        <v>25</v>
-      </c>
-      <c r="L31">
-        <v>1400</v>
-      </c>
-      <c r="M31">
-        <v>250</v>
-      </c>
-      <c r="N31">
-        <v>36</v>
-      </c>
-      <c r="O31" s="2">
-        <v>14</v>
-      </c>
-      <c r="P31" s="2">
-        <v>10</v>
-      </c>
-      <c r="Q31" s="2">
-        <v>15</v>
-      </c>
-      <c r="R31" s="2">
-        <v>1.8</v>
-      </c>
-      <c r="S31" s="2">
-        <v>15</v>
-      </c>
-      <c r="T31" s="2">
-        <v>65</v>
-      </c>
-      <c r="U31">
-        <v>6.8</v>
-      </c>
-      <c r="V31">
-        <v>4.25</v>
-      </c>
-      <c r="W31">
-        <v>1.65</v>
-      </c>
-      <c r="X31">
-        <v>0.8</v>
-      </c>
-      <c r="Y31">
-        <v>0.8</v>
-      </c>
-      <c r="Z31">
-        <v>0.76</v>
-      </c>
-      <c r="AA31">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>34</v>
-      </c>
-      <c r="B32" t="s">
-        <v>46</v>
-      </c>
-      <c r="C32">
-        <v>30</v>
-      </c>
-      <c r="D32">
-        <v>11.56</v>
-      </c>
-      <c r="E32">
-        <v>30</v>
-      </c>
-      <c r="F32">
-        <v>2.8</v>
-      </c>
-      <c r="G32">
-        <v>4.5</v>
-      </c>
-      <c r="H32" s="2">
-        <v>1060</v>
-      </c>
-      <c r="I32" s="2">
-        <v>900</v>
-      </c>
-      <c r="J32" s="2">
-        <v>140</v>
-      </c>
-      <c r="K32" s="2">
-        <v>10</v>
-      </c>
-      <c r="L32" s="2">
-        <v>960</v>
-      </c>
-      <c r="M32" s="2">
-        <v>460</v>
-      </c>
-      <c r="N32" s="2">
-        <v>40</v>
-      </c>
-      <c r="O32" s="2">
-        <v>30</v>
-      </c>
-      <c r="P32" s="2">
-        <v>15</v>
-      </c>
-      <c r="Q32" s="2">
-        <v>15</v>
-      </c>
-      <c r="R32" s="6">
-        <v>1.2</v>
-      </c>
-      <c r="S32" s="2">
-        <v>15</v>
-      </c>
-      <c r="T32" s="2">
-        <v>46</v>
-      </c>
-      <c r="U32" s="6">
-        <v>7.87</v>
-      </c>
-      <c r="V32" s="6">
-        <v>5.63</v>
-      </c>
-      <c r="W32" s="6">
-        <v>0.8</v>
-      </c>
-      <c r="X32" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="Y32" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="Z32" s="6">
-        <v>0.85</v>
-      </c>
-      <c r="AA32" s="6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>33</v>
-      </c>
-      <c r="B33" t="s">
-        <v>46</v>
-      </c>
-      <c r="C33">
-        <v>30</v>
-      </c>
-      <c r="D33">
-        <v>11.56</v>
-      </c>
-      <c r="E33">
-        <v>30</v>
-      </c>
-      <c r="F33">
-        <v>2.1</v>
-      </c>
-      <c r="G33">
-        <v>4.5</v>
-      </c>
-      <c r="H33" s="2">
-        <v>735</v>
-      </c>
-      <c r="I33" s="2">
-        <v>680</v>
-      </c>
-      <c r="J33" s="2">
-        <v>100</v>
-      </c>
-      <c r="K33" s="2">
-        <v>12</v>
-      </c>
-      <c r="L33" s="2">
-        <v>640</v>
-      </c>
-      <c r="M33" s="2">
-        <v>310</v>
-      </c>
-      <c r="N33" s="2">
-        <v>21</v>
-      </c>
-      <c r="O33" s="2">
-        <v>10</v>
-      </c>
-      <c r="P33" s="2">
-        <v>10</v>
-      </c>
-      <c r="Q33" s="2">
-        <v>15</v>
-      </c>
-      <c r="R33" s="2">
-        <v>0.7</v>
-      </c>
-      <c r="S33" s="2">
-        <v>15</v>
-      </c>
-      <c r="T33" s="2">
-        <v>37</v>
-      </c>
-      <c r="U33" s="6">
-        <v>11</v>
-      </c>
-      <c r="V33" s="6">
-        <v>8.4</v>
-      </c>
-      <c r="W33" s="6">
-        <v>1.4</v>
-      </c>
-      <c r="X33" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="Y33" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="Z33" s="6">
-        <v>0.8</v>
-      </c>
-      <c r="AA33" s="6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>4</v>
-      </c>
-      <c r="B34" t="s">
-        <v>45</v>
-      </c>
-      <c r="C34">
-        <v>1</v>
-      </c>
-      <c r="D34" s="2">
-        <v>1</v>
-      </c>
-      <c r="E34" s="2">
-        <v>0</v>
-      </c>
-      <c r="F34" s="5">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="G34" s="5">
-        <v>4.5</v>
-      </c>
-      <c r="H34" s="5">
-        <v>1</v>
-      </c>
-      <c r="I34" s="5">
-        <v>1</v>
-      </c>
-      <c r="J34" s="5">
-        <v>1</v>
-      </c>
-      <c r="K34" s="5">
-        <v>25</v>
-      </c>
-      <c r="L34" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="M34" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="N34" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="O34" s="5">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="P34" s="5">
-        <v>1</v>
-      </c>
-      <c r="Q34" s="5">
-        <v>20</v>
-      </c>
-      <c r="R34" s="5">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="S34" s="5">
-        <v>20</v>
-      </c>
-      <c r="T34" s="5">
-        <v>20</v>
-      </c>
-      <c r="U34" s="6">
-        <v>1E-3</v>
-      </c>
-      <c r="V34" s="6">
-        <v>1E-3</v>
-      </c>
-      <c r="W34" s="5">
-        <v>1</v>
-      </c>
-      <c r="X34" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="Y34" s="5">
-        <v>0.1</v>
-      </c>
-      <c r="Z34" s="5">
-        <v>0.01</v>
-      </c>
-      <c r="AA34" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35" t="s">
-        <v>49</v>
-      </c>
-      <c r="C35">
-        <v>32</v>
-      </c>
-      <c r="D35">
-        <v>11.56</v>
-      </c>
-      <c r="E35">
-        <v>30</v>
-      </c>
-      <c r="F35">
-        <v>5.5</v>
-      </c>
-      <c r="G35">
-        <v>5</v>
-      </c>
-      <c r="H35" s="2">
-        <v>1500</v>
-      </c>
-      <c r="I35" s="2">
-        <v>1500</v>
-      </c>
-      <c r="J35" s="2">
-        <v>200</v>
-      </c>
-      <c r="K35" s="2">
-        <v>10</v>
-      </c>
-      <c r="L35" s="2">
-        <v>1450</v>
-      </c>
-      <c r="M35" s="2">
-        <v>700</v>
-      </c>
-      <c r="N35" s="2">
-        <v>48</v>
-      </c>
-      <c r="O35" s="2">
-        <v>6</v>
-      </c>
-      <c r="P35" s="2">
-        <v>15</v>
-      </c>
-      <c r="Q35" s="2">
-        <v>15</v>
-      </c>
-      <c r="R35" s="6">
-        <v>1.7</v>
-      </c>
-      <c r="S35" s="2">
-        <v>15</v>
-      </c>
-      <c r="T35" s="2">
-        <v>61</v>
-      </c>
-      <c r="U35" s="6">
-        <v>2.9</v>
-      </c>
-      <c r="V35" s="6">
-        <v>2</v>
-      </c>
-      <c r="W35" s="6">
-        <v>0.9</v>
-      </c>
-      <c r="X35" s="6">
-        <v>1</v>
-      </c>
-      <c r="Y35" s="6">
-        <v>1</v>
-      </c>
-      <c r="Z35" s="3">
-        <v>0.85</v>
-      </c>
-      <c r="AA35" s="6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" t="s">
-        <v>49</v>
-      </c>
-      <c r="C36">
-        <v>32</v>
-      </c>
-      <c r="D36">
-        <v>11.56</v>
-      </c>
-      <c r="E36">
-        <v>30</v>
-      </c>
-      <c r="F36">
-        <v>3.8</v>
-      </c>
-      <c r="G36">
-        <v>5</v>
-      </c>
-      <c r="H36" s="2">
-        <v>1050</v>
-      </c>
-      <c r="I36" s="2">
-        <v>1000</v>
-      </c>
-      <c r="J36" s="2">
-        <v>150</v>
-      </c>
-      <c r="K36" s="2">
-        <v>10</v>
-      </c>
-      <c r="L36" s="2">
-        <v>1000</v>
-      </c>
-      <c r="M36" s="2">
-        <v>460</v>
-      </c>
-      <c r="N36" s="2">
-        <v>39</v>
-      </c>
-      <c r="O36" s="2">
-        <v>3</v>
-      </c>
-      <c r="P36" s="2">
-        <v>15</v>
-      </c>
-      <c r="Q36" s="2">
-        <v>15</v>
-      </c>
-      <c r="R36" s="6">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="S36" s="2">
-        <v>15</v>
-      </c>
-      <c r="T36" s="2">
-        <v>57</v>
-      </c>
-      <c r="U36" s="6">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="V36" s="6">
-        <v>2.7</v>
-      </c>
-      <c r="W36" s="6">
-        <v>1.2</v>
-      </c>
-      <c r="X36" s="6">
-        <v>1</v>
-      </c>
-      <c r="Y36" s="6">
-        <v>1</v>
-      </c>
-      <c r="Z36" s="3">
-        <v>0.85</v>
-      </c>
-      <c r="AA36" s="6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>113</v>
-      </c>
-      <c r="B37" t="s">
-        <v>47</v>
-      </c>
-      <c r="C37">
-        <v>15</v>
-      </c>
-      <c r="D37">
-        <v>45</v>
-      </c>
-      <c r="E37">
-        <v>30</v>
-      </c>
-      <c r="F37">
-        <v>11.4</v>
-      </c>
-      <c r="G37">
-        <v>4.5</v>
-      </c>
-      <c r="H37" s="2">
-        <v>4600</v>
-      </c>
-      <c r="I37" s="2">
-        <v>5500</v>
-      </c>
-      <c r="J37" s="2">
-        <v>250</v>
-      </c>
-      <c r="K37" s="2">
-        <v>15</v>
-      </c>
-      <c r="L37" s="2">
-        <v>4200</v>
-      </c>
-      <c r="M37" s="2">
-        <v>1800</v>
-      </c>
-      <c r="N37" s="2">
-        <v>68</v>
-      </c>
-      <c r="O37" s="2">
-        <v>45</v>
-      </c>
-      <c r="P37" s="2">
-        <v>10</v>
-      </c>
-      <c r="Q37" s="2">
-        <v>15</v>
-      </c>
-      <c r="R37" s="6">
-        <v>2.4</v>
-      </c>
-      <c r="S37" s="2">
-        <v>15</v>
-      </c>
-      <c r="T37" s="2">
-        <v>67</v>
-      </c>
-      <c r="U37" s="6">
-        <v>1.8</v>
-      </c>
-      <c r="V37" s="6">
-        <v>1</v>
-      </c>
-      <c r="W37" s="6">
-        <v>1.2</v>
-      </c>
-      <c r="X37" s="6">
-        <v>0.9</v>
-      </c>
-      <c r="Y37" s="6">
-        <v>0.9</v>
-      </c>
-      <c r="Z37" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="AA37" s="6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>32</v>
-      </c>
-      <c r="B38" t="s">
-        <v>47</v>
-      </c>
-      <c r="C38">
-        <v>15</v>
-      </c>
-      <c r="D38">
-        <v>45</v>
-      </c>
-      <c r="E38">
-        <v>30</v>
-      </c>
-      <c r="F38">
-        <v>19</v>
-      </c>
-      <c r="G38">
-        <v>4.5</v>
-      </c>
-      <c r="H38" s="2">
-        <v>8500</v>
-      </c>
-      <c r="I38" s="2">
-        <v>6000</v>
-      </c>
-      <c r="J38" s="2">
-        <v>1000</v>
-      </c>
-      <c r="K38" s="2">
-        <v>24</v>
-      </c>
-      <c r="L38" s="2">
-        <v>7500</v>
-      </c>
-      <c r="M38" s="2">
-        <v>1400</v>
-      </c>
-      <c r="N38" s="2">
-        <v>75</v>
-      </c>
-      <c r="O38" s="2">
-        <v>20</v>
-      </c>
-      <c r="P38" s="2">
-        <v>87</v>
-      </c>
-      <c r="Q38" s="2">
-        <v>15</v>
-      </c>
-      <c r="R38" s="2">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="S38" s="2">
-        <v>15</v>
-      </c>
-      <c r="T38" s="2">
-        <v>120</v>
-      </c>
-      <c r="U38" s="3">
-        <v>2</v>
-      </c>
-      <c r="V38" s="3">
-        <v>1.7</v>
-      </c>
-      <c r="W38" s="3">
-        <v>1.9</v>
-      </c>
-      <c r="X38" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="Y38" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="Z38" s="3">
-        <v>0.81</v>
-      </c>
-      <c r="AA38" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>36</v>
-      </c>
-      <c r="B39" t="s">
-        <v>47</v>
-      </c>
-      <c r="C39">
-        <v>15</v>
-      </c>
-      <c r="D39">
-        <v>45</v>
-      </c>
-      <c r="E39">
-        <v>60</v>
-      </c>
-      <c r="F39">
-        <v>10</v>
-      </c>
-      <c r="G39">
-        <v>10</v>
-      </c>
-      <c r="H39" s="2">
-        <v>4000</v>
-      </c>
-      <c r="I39" s="2">
-        <v>3000</v>
-      </c>
-      <c r="J39" s="2">
-        <v>700</v>
-      </c>
-      <c r="K39" s="2">
-        <v>25</v>
-      </c>
-      <c r="L39" s="2">
-        <v>3300</v>
-      </c>
-      <c r="M39" s="2">
-        <v>1000</v>
-      </c>
-      <c r="N39" s="2">
-        <v>50</v>
-      </c>
-      <c r="O39" s="2">
-        <v>73</v>
-      </c>
-      <c r="P39" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q39" s="2">
-        <v>30</v>
-      </c>
-      <c r="R39" s="6">
-        <v>8.5</v>
-      </c>
-      <c r="S39" s="2">
-        <v>30</v>
-      </c>
-      <c r="T39" s="2">
-        <v>100</v>
-      </c>
-      <c r="U39" s="6">
-        <v>3.1</v>
-      </c>
-      <c r="V39" s="6">
-        <v>2.4</v>
-      </c>
-      <c r="W39" s="6">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="X39" s="6">
-        <v>0.75</v>
-      </c>
-      <c r="Y39" s="6">
-        <v>0.75</v>
-      </c>
-      <c r="Z39" s="3">
-        <v>0.69</v>
-      </c>
-      <c r="AA39" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>35</v>
-      </c>
-      <c r="B40" t="s">
-        <v>47</v>
-      </c>
-      <c r="C40">
-        <v>15</v>
-      </c>
-      <c r="D40">
-        <v>45</v>
-      </c>
-      <c r="E40">
-        <v>30</v>
-      </c>
-      <c r="F40">
-        <v>4.5</v>
-      </c>
-      <c r="G40">
-        <v>10</v>
-      </c>
-      <c r="H40" s="2">
-        <v>2200</v>
-      </c>
-      <c r="I40" s="2">
-        <v>1300</v>
-      </c>
-      <c r="J40" s="2">
-        <v>300</v>
-      </c>
-      <c r="K40" s="2">
-        <v>15</v>
-      </c>
-      <c r="L40" s="2">
-        <v>1900</v>
-      </c>
-      <c r="M40" s="2">
-        <v>400</v>
-      </c>
-      <c r="N40" s="2">
-        <v>50</v>
-      </c>
-      <c r="O40" s="2">
-        <v>21.5</v>
-      </c>
-      <c r="P40" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q40" s="2">
-        <v>15</v>
-      </c>
-      <c r="R40" s="6">
-        <v>3.6</v>
-      </c>
-      <c r="S40" s="2">
-        <v>15</v>
-      </c>
-      <c r="T40" s="2">
-        <v>165</v>
-      </c>
-      <c r="U40" s="10">
-        <v>2.8</v>
-      </c>
-      <c r="V40" s="10">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="W40" s="6">
-        <v>1.8</v>
-      </c>
-      <c r="X40" s="6">
-        <v>0.8</v>
-      </c>
-      <c r="Y40" s="6">
-        <v>0.8</v>
-      </c>
-      <c r="Z40" s="3">
-        <v>0.68</v>
-      </c>
-      <c r="AA40" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>16</v>
-      </c>
-      <c r="B41" t="s">
-        <v>47</v>
-      </c>
-      <c r="C41">
-        <v>15</v>
-      </c>
-      <c r="D41">
-        <v>45</v>
-      </c>
-      <c r="E41">
-        <v>40</v>
-      </c>
-      <c r="F41">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="G41">
-        <v>10</v>
-      </c>
-      <c r="H41" s="2">
-        <v>2900</v>
-      </c>
-      <c r="I41" s="2">
-        <v>2500</v>
-      </c>
-      <c r="J41" s="2">
-        <v>250</v>
-      </c>
-      <c r="K41" s="2">
-        <v>30</v>
-      </c>
-      <c r="L41" s="2">
-        <v>2800</v>
-      </c>
-      <c r="M41" s="2">
-        <v>400</v>
-      </c>
-      <c r="N41" s="2">
-        <v>30</v>
-      </c>
-      <c r="O41" s="2">
-        <v>41</v>
-      </c>
-      <c r="P41" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q41" s="2">
-        <v>20</v>
-      </c>
-      <c r="R41" s="6">
-        <v>2.5</v>
-      </c>
-      <c r="S41" s="2">
-        <v>20</v>
-      </c>
-      <c r="T41" s="2">
-        <v>203</v>
-      </c>
-      <c r="U41" s="6">
-        <v>3.5</v>
-      </c>
-      <c r="V41" s="6">
-        <v>2.6</v>
-      </c>
-      <c r="W41" s="3">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="X41" s="3">
-        <v>0.25</v>
-      </c>
-      <c r="Y41" s="6">
-        <v>0.5</v>
-      </c>
-      <c r="Z41" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="AA41" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>109</v>
-      </c>
-      <c r="B42" t="s">
-        <v>47</v>
-      </c>
-      <c r="C42">
-        <v>15</v>
-      </c>
-      <c r="D42">
-        <v>45</v>
-      </c>
-      <c r="E42">
-        <v>40</v>
-      </c>
-      <c r="F42">
-        <v>5.5</v>
-      </c>
-      <c r="G42">
-        <v>10</v>
-      </c>
-      <c r="H42" s="2">
-        <v>2200</v>
-      </c>
-      <c r="I42" s="2">
-        <v>2400</v>
-      </c>
-      <c r="J42" s="2">
-        <v>300</v>
-      </c>
-      <c r="K42" s="2">
-        <v>15</v>
-      </c>
-      <c r="L42" s="2">
-        <v>2000</v>
-      </c>
-      <c r="M42" s="2">
-        <v>900</v>
-      </c>
-      <c r="N42" s="2">
-        <v>28</v>
-      </c>
-      <c r="O42" s="2">
-        <v>42</v>
-      </c>
-      <c r="P42" s="2">
-        <v>10</v>
-      </c>
-      <c r="Q42" s="2">
-        <v>20</v>
-      </c>
-      <c r="R42" s="6">
-        <v>3.6</v>
-      </c>
-      <c r="S42" s="2">
-        <v>20</v>
-      </c>
-      <c r="T42" s="2">
-        <v>170</v>
-      </c>
-      <c r="U42" s="6">
-        <v>2.4</v>
-      </c>
-      <c r="V42" s="6">
-        <v>1.8</v>
-      </c>
-      <c r="W42" s="3">
-        <v>1.2</v>
-      </c>
-      <c r="X42" s="6">
-        <v>1</v>
-      </c>
-      <c r="Y42" s="6">
-        <v>1</v>
-      </c>
-      <c r="Z42" s="3">
-        <v>0.84</v>
-      </c>
-      <c r="AA42" s="2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>110</v>
-      </c>
-      <c r="B43" t="s">
-        <v>47</v>
-      </c>
-      <c r="C43">
-        <v>15</v>
-      </c>
-      <c r="D43">
-        <v>45</v>
-      </c>
-      <c r="E43">
-        <v>40</v>
-      </c>
-      <c r="F43">
-        <v>4.8</v>
-      </c>
-      <c r="G43">
-        <v>10</v>
-      </c>
-      <c r="H43" s="2">
-        <v>2000</v>
-      </c>
-      <c r="I43" s="2">
-        <v>2000</v>
-      </c>
-      <c r="J43" s="2">
-        <v>300</v>
-      </c>
-      <c r="K43" s="2">
-        <v>15</v>
-      </c>
-      <c r="L43" s="2">
-        <v>1800</v>
-      </c>
-      <c r="M43" s="2">
-        <v>750</v>
-      </c>
-      <c r="N43" s="2">
-        <v>90</v>
-      </c>
-      <c r="O43" s="2">
-        <v>52</v>
-      </c>
-      <c r="P43" s="2">
-        <v>50</v>
-      </c>
-      <c r="Q43" s="2">
-        <v>20</v>
-      </c>
-      <c r="R43" s="6">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="S43" s="2">
-        <v>20</v>
-      </c>
-      <c r="T43" s="2">
-        <v>150</v>
-      </c>
-      <c r="U43" s="6">
-        <v>3.3</v>
-      </c>
-      <c r="V43" s="6">
-        <v>2.5</v>
-      </c>
-      <c r="W43" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="X43" s="6">
-        <v>1</v>
-      </c>
-      <c r="Y43" s="6">
-        <v>1</v>
-      </c>
-      <c r="Z43" s="3">
-        <v>0.88</v>
-      </c>
-      <c r="AA43" s="2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" t="s">
-        <v>47</v>
-      </c>
-      <c r="C44">
-        <v>15</v>
-      </c>
-      <c r="D44">
-        <v>45</v>
       </c>
       <c r="E44">
         <v>40</v>
       </c>
       <c r="F44">
-        <v>2.1</v>
+        <v>8.1999999999999993</v>
       </c>
       <c r="G44">
-        <v>10</v>
-      </c>
-      <c r="H44" s="2">
-        <v>750</v>
-      </c>
-      <c r="I44" s="2">
-        <v>900</v>
-      </c>
-      <c r="J44" s="2">
-        <v>100</v>
-      </c>
-      <c r="K44" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="H44">
+        <v>2700</v>
+      </c>
+      <c r="I44">
+        <v>1400</v>
+      </c>
+      <c r="J44">
+        <v>70</v>
+      </c>
+      <c r="K44">
+        <v>30</v>
+      </c>
+      <c r="L44">
+        <v>2450</v>
+      </c>
+      <c r="M44">
+        <v>350</v>
+      </c>
+      <c r="N44">
+        <v>20</v>
+      </c>
+      <c r="O44">
+        <v>10</v>
+      </c>
+      <c r="P44">
+        <v>20.8</v>
+      </c>
+      <c r="Q44">
+        <v>20</v>
+      </c>
+      <c r="R44">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="S44">
+        <v>20</v>
+      </c>
+      <c r="T44">
+        <v>76</v>
+      </c>
+      <c r="U44">
+        <v>3.88</v>
+      </c>
+      <c r="V44">
+        <v>2.71</v>
+      </c>
+      <c r="W44">
+        <v>1.3</v>
+      </c>
+      <c r="X44">
+        <v>0.8</v>
+      </c>
+      <c r="Y44">
+        <v>0.8</v>
+      </c>
+      <c r="Z44">
+        <v>0.74</v>
+      </c>
+      <c r="AA44">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" spans="1:27" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A45" t="s">
+        <v>30</v>
+      </c>
+      <c r="B45" t="s">
+        <v>46</v>
+      </c>
+      <c r="C45">
+        <v>30</v>
+      </c>
+      <c r="D45">
+        <v>11.56</v>
+      </c>
+      <c r="E45">
+        <v>30</v>
+      </c>
+      <c r="F45">
+        <v>8.5</v>
+      </c>
+      <c r="G45">
+        <v>10</v>
+      </c>
+      <c r="H45" s="2">
+        <v>3200</v>
+      </c>
+      <c r="I45" s="2">
+        <v>2500</v>
+      </c>
+      <c r="J45" s="2">
+        <v>500</v>
+      </c>
+      <c r="K45" s="2">
         <v>25</v>
       </c>
-      <c r="L44" s="2">
-        <v>650</v>
-      </c>
-      <c r="M44" s="2">
-        <v>190</v>
-      </c>
-      <c r="N44" s="2">
-        <v>12</v>
-      </c>
-      <c r="O44" s="2">
+      <c r="L45" s="2">
+        <v>2800</v>
+      </c>
+      <c r="M45" s="2">
+        <v>600</v>
+      </c>
+      <c r="N45" s="2">
+        <v>50</v>
+      </c>
+      <c r="O45" s="2">
+        <v>36.5</v>
+      </c>
+      <c r="P45" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q45" s="2">
+        <v>15</v>
+      </c>
+      <c r="R45" s="6">
+        <v>4</v>
+      </c>
+      <c r="S45" s="2">
+        <v>15</v>
+      </c>
+      <c r="T45" s="2">
+        <v>125</v>
+      </c>
+      <c r="U45" s="6">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="V45" s="6">
+        <v>1.55</v>
+      </c>
+      <c r="W45" s="6">
+        <v>0.7</v>
+      </c>
+      <c r="X45" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Y45" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Z45" s="6">
+        <v>0.68</v>
+      </c>
+      <c r="AA45" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:27" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A46" t="s">
         <v>22</v>
       </c>
-      <c r="P44" s="2">
-        <v>10</v>
-      </c>
-      <c r="Q44" s="2">
-        <v>20</v>
-      </c>
-      <c r="R44" s="6">
-        <v>1.4</v>
-      </c>
-      <c r="S44" s="2">
-        <v>20</v>
-      </c>
-      <c r="T44" s="2">
-        <v>100</v>
-      </c>
-      <c r="U44" s="6">
-        <v>6.8</v>
-      </c>
-      <c r="V44" s="6">
-        <v>4.7</v>
-      </c>
-      <c r="W44" s="6">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="X44" s="6">
-        <v>1</v>
-      </c>
-      <c r="Y44" s="6">
-        <v>1</v>
-      </c>
-      <c r="Z44" s="3">
-        <v>0.92</v>
-      </c>
-      <c r="AA44" s="2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>14</v>
-      </c>
-      <c r="B45" t="s">
-        <v>47</v>
-      </c>
-      <c r="C45">
-        <v>15</v>
-      </c>
-      <c r="D45">
-        <v>45</v>
-      </c>
-      <c r="E45">
-        <v>40</v>
-      </c>
-      <c r="F45">
-        <v>7.6</v>
-      </c>
-      <c r="G45">
-        <v>10</v>
-      </c>
-      <c r="H45" s="2">
-        <v>2400</v>
-      </c>
-      <c r="I45" s="2">
-        <v>1800</v>
-      </c>
-      <c r="J45" s="2">
-        <v>300</v>
-      </c>
-      <c r="K45" s="2">
-        <v>30</v>
-      </c>
-      <c r="L45" s="2">
-        <v>2200</v>
-      </c>
-      <c r="M45" s="2">
-        <v>380</v>
-      </c>
-      <c r="N45" s="2">
-        <v>15</v>
-      </c>
-      <c r="O45" s="2">
-        <v>23</v>
-      </c>
-      <c r="P45" s="2">
-        <v>42</v>
-      </c>
-      <c r="Q45" s="2">
-        <v>20</v>
-      </c>
-      <c r="R45" s="6">
-        <v>3.2</v>
-      </c>
-      <c r="S45" s="2">
-        <v>20</v>
-      </c>
-      <c r="T45" s="2">
-        <v>96</v>
-      </c>
-      <c r="U45" s="6">
-        <v>6.8</v>
-      </c>
-      <c r="V45" s="6">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="W45" s="6">
-        <v>1.4</v>
-      </c>
-      <c r="X45" s="6">
-        <v>1</v>
-      </c>
-      <c r="Y45" s="6">
-        <v>1</v>
-      </c>
-      <c r="Z45" s="3">
-        <v>0.88</v>
-      </c>
-      <c r="AA45" s="2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="46" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>111</v>
-      </c>
       <c r="B46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C46">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D46">
-        <v>45</v>
+        <v>11.56</v>
       </c>
       <c r="E46">
         <v>40</v>
       </c>
       <c r="F46">
-        <v>7</v>
+        <v>8.6999999999999993</v>
       </c>
       <c r="G46">
-        <v>10</v>
-      </c>
-      <c r="H46" s="2">
-        <v>1900</v>
-      </c>
-      <c r="I46" s="2">
-        <v>2000</v>
-      </c>
-      <c r="J46" s="2">
-        <v>300</v>
-      </c>
-      <c r="K46" s="2">
-        <v>15</v>
-      </c>
-      <c r="L46" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="H46">
+        <v>3600</v>
+      </c>
+      <c r="I46">
         <v>1600</v>
       </c>
-      <c r="M46" s="2">
-        <v>780</v>
-      </c>
-      <c r="N46" s="2">
-        <v>80</v>
-      </c>
-      <c r="O46" s="2">
+      <c r="J46">
+        <v>350</v>
+      </c>
+      <c r="K46">
+        <v>24</v>
+      </c>
+      <c r="L46">
+        <v>3250</v>
+      </c>
+      <c r="M46">
+        <v>400</v>
+      </c>
+      <c r="N46">
+        <v>50</v>
+      </c>
+      <c r="O46">
         <v>23</v>
       </c>
-      <c r="P46" s="2">
-        <v>50</v>
-      </c>
-      <c r="Q46" s="2">
-        <v>20</v>
-      </c>
-      <c r="R46" s="6">
-        <v>4</v>
-      </c>
-      <c r="S46" s="2">
-        <v>20</v>
-      </c>
-      <c r="T46" s="2">
-        <v>140</v>
-      </c>
-      <c r="U46" s="6">
-        <v>3.1</v>
-      </c>
-      <c r="V46" s="6">
-        <v>2.7</v>
-      </c>
-      <c r="W46" s="3">
-        <v>2.8</v>
-      </c>
-      <c r="X46" s="6">
-        <v>1</v>
-      </c>
-      <c r="Y46" s="6">
-        <v>1</v>
-      </c>
-      <c r="Z46" s="3">
-        <v>0.89</v>
-      </c>
-      <c r="AA46" s="2">
-        <v>49</v>
+      <c r="P46">
+        <v>10</v>
+      </c>
+      <c r="Q46">
+        <v>20</v>
+      </c>
+      <c r="R46">
+        <v>4.2</v>
+      </c>
+      <c r="S46">
+        <v>20</v>
+      </c>
+      <c r="T46">
+        <v>70</v>
+      </c>
+      <c r="U46">
+        <v>3.85</v>
+      </c>
+      <c r="V46">
+        <v>2.85</v>
+      </c>
+      <c r="W46">
+        <v>1.4</v>
+      </c>
+      <c r="X46">
+        <v>0.5</v>
+      </c>
+      <c r="Y46">
+        <v>0.5</v>
+      </c>
+      <c r="Z46">
+        <v>0.74</v>
+      </c>
+      <c r="AA46">
+        <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A47" t="s">
-        <v>112</v>
+        <v>12</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C47">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D47">
-        <v>45</v>
+        <v>11.56</v>
       </c>
       <c r="E47">
         <v>40</v>
       </c>
       <c r="F47">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="G47">
+        <v>4.5</v>
+      </c>
+      <c r="H47">
+        <v>4100</v>
+      </c>
+      <c r="I47">
+        <v>2000</v>
+      </c>
+      <c r="J47">
+        <v>350</v>
+      </c>
+      <c r="K47">
+        <v>24</v>
+      </c>
+      <c r="L47">
+        <v>3700</v>
+      </c>
+      <c r="M47">
+        <v>600</v>
+      </c>
+      <c r="N47">
+        <v>90</v>
+      </c>
+      <c r="O47">
+        <v>23</v>
+      </c>
+      <c r="P47">
+        <v>10</v>
+      </c>
+      <c r="Q47">
+        <v>20</v>
+      </c>
+      <c r="R47">
+        <v>4</v>
+      </c>
+      <c r="S47">
+        <v>20</v>
+      </c>
+      <c r="T47">
+        <v>98</v>
+      </c>
+      <c r="U47">
+        <v>2.4</v>
+      </c>
+      <c r="V47">
+        <v>1.8</v>
+      </c>
+      <c r="W47">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="X47">
+        <v>0.5</v>
+      </c>
+      <c r="Y47">
+        <v>0.5</v>
+      </c>
+      <c r="Z47">
+        <v>0.73</v>
+      </c>
+      <c r="AA47">
         <v>5</v>
       </c>
-      <c r="G47">
-        <v>10</v>
-      </c>
-      <c r="H47" s="2">
-        <v>1400</v>
-      </c>
-      <c r="I47" s="2">
-        <v>1500</v>
-      </c>
-      <c r="J47" s="2">
-        <v>200</v>
-      </c>
-      <c r="K47" s="2">
-        <v>15</v>
-      </c>
-      <c r="L47" s="2">
-        <v>1100</v>
-      </c>
-      <c r="M47" s="2">
-        <v>580</v>
-      </c>
-      <c r="N47" s="2">
-        <v>60</v>
-      </c>
-      <c r="O47" s="2">
-        <v>19</v>
-      </c>
-      <c r="P47" s="2">
-        <v>50</v>
-      </c>
-      <c r="Q47" s="2">
-        <v>20</v>
-      </c>
-      <c r="R47" s="6">
-        <v>3</v>
-      </c>
-      <c r="S47" s="2">
-        <v>20</v>
-      </c>
-      <c r="T47" s="2">
-        <v>100</v>
-      </c>
-      <c r="U47" s="6">
-        <v>4</v>
-      </c>
-      <c r="V47" s="6">
-        <v>3.5</v>
-      </c>
-      <c r="W47" s="3">
-        <v>2.1</v>
-      </c>
-      <c r="X47" s="3">
-        <v>1</v>
-      </c>
-      <c r="Y47" s="3">
-        <v>1</v>
-      </c>
-      <c r="Z47" s="3">
-        <v>0.88</v>
-      </c>
-      <c r="AA47" s="2">
-        <v>35</v>
-      </c>
     </row>
-    <row r="48" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A48" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B48" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C48">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D48">
-        <v>45</v>
+        <v>11.56</v>
       </c>
       <c r="E48">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F48">
-        <v>6.3</v>
+        <v>9.6</v>
       </c>
       <c r="G48">
         <v>4.5</v>
       </c>
       <c r="H48" s="2">
-        <v>2100</v>
+        <v>3000</v>
       </c>
       <c r="I48" s="2">
-        <v>1400</v>
+        <v>3000</v>
       </c>
       <c r="J48" s="2">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="K48" s="2">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="L48" s="2">
-        <v>2000</v>
+        <v>2975</v>
       </c>
       <c r="M48" s="2">
-        <v>350</v>
+        <v>1200</v>
       </c>
       <c r="N48" s="2">
-        <v>14</v>
+        <v>200</v>
       </c>
       <c r="O48" s="2">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="P48" s="2">
         <v>10</v>
       </c>
-      <c r="Q48" s="2">
-        <v>20</v>
-      </c>
-      <c r="R48" s="6">
-        <v>2.1</v>
-      </c>
-      <c r="S48" s="2">
-        <v>20</v>
-      </c>
-      <c r="T48" s="2">
-        <v>50</v>
-      </c>
-      <c r="U48" s="3">
+      <c r="Q48">
+        <v>15</v>
+      </c>
+      <c r="R48">
+        <v>3.9</v>
+      </c>
+      <c r="S48">
+        <v>15</v>
+      </c>
+      <c r="T48">
+        <v>95</v>
+      </c>
+      <c r="U48">
+        <v>1.5</v>
+      </c>
+      <c r="V48">
+        <v>0.95</v>
+      </c>
+      <c r="W48">
+        <v>0.42</v>
+      </c>
+      <c r="X48" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="Y48" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="Z48">
+        <v>0.73</v>
+      </c>
+      <c r="AA48">
         <v>5</v>
       </c>
-      <c r="V48" s="3">
-        <v>3.5</v>
-      </c>
-      <c r="W48" s="3">
-        <v>1.45</v>
-      </c>
-      <c r="X48" s="3">
-        <v>1</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>1</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>0.74</v>
-      </c>
-      <c r="AA48" s="2">
-        <v>5</v>
-      </c>
     </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:27" hidden="1" x14ac:dyDescent="0.15">
       <c r="A49" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="B49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C49">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D49">
-        <v>45</v>
+        <v>11.56</v>
       </c>
       <c r="E49">
         <v>30</v>
       </c>
       <c r="F49">
-        <v>4.5</v>
+        <v>11.2</v>
       </c>
       <c r="G49">
         <v>4.5</v>
       </c>
       <c r="H49" s="2">
-        <v>1600</v>
+        <v>4000</v>
       </c>
       <c r="I49" s="2">
+        <v>4000</v>
+      </c>
+      <c r="J49" s="2">
+        <v>550</v>
+      </c>
+      <c r="K49" s="2">
+        <v>15</v>
+      </c>
+      <c r="L49" s="2">
+        <v>3700</v>
+      </c>
+      <c r="M49" s="2">
+        <v>1800</v>
+      </c>
+      <c r="N49" s="2">
+        <v>160</v>
+      </c>
+      <c r="O49" s="2">
+        <v>45</v>
+      </c>
+      <c r="P49" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q49" s="2">
+        <v>15</v>
+      </c>
+      <c r="R49" s="2">
+        <v>5.8</v>
+      </c>
+      <c r="S49" s="2">
+        <v>15</v>
+      </c>
+      <c r="T49" s="2">
+        <v>84</v>
+      </c>
+      <c r="U49" s="3">
+        <v>1.75</v>
+      </c>
+      <c r="V49" s="3">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="W49" s="3">
+        <v>0.6</v>
+      </c>
+      <c r="X49" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="Y49" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="Z49" s="3">
+        <v>0.45</v>
+      </c>
+      <c r="AA49" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:27" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A50" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" t="s">
+        <v>49</v>
+      </c>
+      <c r="C50">
+        <v>32</v>
+      </c>
+      <c r="D50">
+        <v>11.56</v>
+      </c>
+      <c r="E50">
+        <v>30</v>
+      </c>
+      <c r="F50">
+        <v>5.5</v>
+      </c>
+      <c r="G50">
+        <v>5</v>
+      </c>
+      <c r="H50" s="2">
         <v>1500</v>
       </c>
-      <c r="J49" s="2">
+      <c r="I50" s="2">
+        <v>1500</v>
+      </c>
+      <c r="J50" s="2">
         <v>200</v>
       </c>
-      <c r="K49" s="2">
-        <v>15</v>
-      </c>
-      <c r="L49" s="2">
-        <v>1500</v>
-      </c>
-      <c r="M49" s="2">
-        <v>520</v>
-      </c>
-      <c r="N49" s="2">
-        <v>38</v>
-      </c>
-      <c r="O49" s="2">
-        <v>13</v>
-      </c>
-      <c r="P49" s="2">
-        <v>10</v>
-      </c>
-      <c r="Q49" s="2">
-        <v>15</v>
-      </c>
-      <c r="R49" s="2">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="S49" s="2">
-        <v>15</v>
-      </c>
-      <c r="T49" s="2">
-        <v>80</v>
-      </c>
-      <c r="U49" s="6">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="V49" s="6">
-        <v>2.8</v>
-      </c>
-      <c r="W49" s="3">
-        <v>1.4</v>
-      </c>
-      <c r="X49" s="6">
-        <v>1</v>
-      </c>
-      <c r="Y49" s="6">
-        <v>1</v>
-      </c>
-      <c r="Z49" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="AA49" s="6">
-        <v>10</v>
+      <c r="K50" s="2">
+        <v>10</v>
+      </c>
+      <c r="L50" s="2">
+        <v>1450</v>
+      </c>
+      <c r="M50" s="2">
+        <v>700</v>
+      </c>
+      <c r="N50" s="2">
+        <v>48</v>
+      </c>
+      <c r="O50" s="2">
+        <v>6</v>
+      </c>
+      <c r="P50" s="2">
+        <v>15</v>
+      </c>
+      <c r="Q50" s="2">
+        <v>15</v>
+      </c>
+      <c r="R50" s="6">
+        <v>1.7</v>
+      </c>
+      <c r="S50" s="2">
+        <v>15</v>
+      </c>
+      <c r="T50" s="2">
+        <v>61</v>
+      </c>
+      <c r="U50" s="6">
+        <v>2.9</v>
+      </c>
+      <c r="V50" s="6">
+        <v>2</v>
+      </c>
+      <c r="W50" s="6">
+        <v>0.9</v>
+      </c>
+      <c r="X50" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y50" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z50" s="3">
+        <v>0.85</v>
+      </c>
+      <c r="AA50" s="6">
+        <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>114</v>
-      </c>
-      <c r="B50" t="s">
-        <v>47</v>
-      </c>
-      <c r="C50">
-        <v>15</v>
-      </c>
-      <c r="D50">
-        <v>45</v>
-      </c>
-      <c r="E50">
-        <v>40</v>
-      </c>
-      <c r="F50">
-        <v>13</v>
-      </c>
-      <c r="G50">
-        <v>10</v>
-      </c>
-      <c r="H50" s="2">
-        <v>3600</v>
-      </c>
-      <c r="I50" s="2">
-        <v>3800</v>
-      </c>
-      <c r="J50" s="2">
+    <row r="51" spans="1:27" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A51" t="s">
+        <v>37</v>
+      </c>
+      <c r="B51" t="s">
+        <v>49</v>
+      </c>
+      <c r="C51">
+        <v>32</v>
+      </c>
+      <c r="D51">
+        <v>11.56</v>
+      </c>
+      <c r="E51">
+        <v>30</v>
+      </c>
+      <c r="F51">
+        <v>3.8</v>
+      </c>
+      <c r="G51">
+        <v>5</v>
+      </c>
+      <c r="H51" s="2">
+        <v>1050</v>
+      </c>
+      <c r="I51" s="2">
         <v>1000</v>
       </c>
-      <c r="K50" s="2">
-        <v>15</v>
-      </c>
-      <c r="L50" s="2">
-        <v>2900</v>
-      </c>
-      <c r="M50" s="2">
-        <v>380</v>
-      </c>
-      <c r="N50" s="2">
-        <v>270</v>
-      </c>
-      <c r="O50" s="2">
-        <v>41</v>
-      </c>
-      <c r="P50" s="2">
-        <v>40</v>
-      </c>
-      <c r="Q50" s="2">
-        <v>20</v>
-      </c>
-      <c r="R50" s="6">
-        <v>15</v>
-      </c>
-      <c r="S50" s="2">
-        <v>20</v>
-      </c>
-      <c r="T50" s="11">
-        <v>100</v>
-      </c>
-      <c r="U50" s="6">
-        <v>20</v>
-      </c>
-      <c r="V50" s="6">
-        <v>2.5</v>
-      </c>
-      <c r="W50" s="3">
-        <v>2.1</v>
-      </c>
-      <c r="X50" s="6">
-        <v>1</v>
-      </c>
-      <c r="Y50" s="6">
-        <v>1</v>
-      </c>
-      <c r="Z50" s="3">
-        <v>0.83</v>
-      </c>
-      <c r="AA50" s="2">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>115</v>
-      </c>
-      <c r="B51" t="s">
-        <v>47</v>
-      </c>
-      <c r="C51">
-        <v>15</v>
-      </c>
-      <c r="D51">
-        <v>45</v>
-      </c>
-      <c r="E51">
-        <v>40</v>
-      </c>
-      <c r="F51">
-        <v>16</v>
-      </c>
-      <c r="G51">
-        <v>10</v>
-      </c>
-      <c r="H51" s="2">
-        <v>5000</v>
-      </c>
-      <c r="I51" s="2">
-        <v>4000</v>
-      </c>
       <c r="J51" s="2">
-        <v>1100</v>
+        <v>150</v>
       </c>
       <c r="K51" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="L51" s="2">
-        <v>3300</v>
+        <v>1000</v>
       </c>
       <c r="M51" s="2">
         <v>460</v>
       </c>
       <c r="N51" s="2">
+        <v>39</v>
+      </c>
+      <c r="O51" s="2">
+        <v>3</v>
+      </c>
+      <c r="P51" s="2">
+        <v>15</v>
+      </c>
+      <c r="Q51" s="2">
+        <v>15</v>
+      </c>
+      <c r="R51" s="6">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="S51" s="2">
+        <v>15</v>
+      </c>
+      <c r="T51" s="2">
+        <v>57</v>
+      </c>
+      <c r="U51" s="6">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="V51" s="6">
+        <v>2.7</v>
+      </c>
+      <c r="W51" s="6">
+        <v>1.2</v>
+      </c>
+      <c r="X51" s="6">
+        <v>1</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z51" s="3">
+        <v>0.85</v>
+      </c>
+      <c r="AA51" s="6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="1:27" hidden="1" x14ac:dyDescent="0.15">
+      <c r="A52" t="s">
+        <v>27</v>
+      </c>
+      <c r="B52" t="s">
+        <v>46</v>
+      </c>
+      <c r="C52">
+        <v>30</v>
+      </c>
+      <c r="D52">
+        <v>11.56</v>
+      </c>
+      <c r="E52">
+        <v>30</v>
+      </c>
+      <c r="F52">
+        <v>11.3</v>
+      </c>
+      <c r="G52">
+        <v>4.5</v>
+      </c>
+      <c r="H52" s="2">
+        <v>4000</v>
+      </c>
+      <c r="I52" s="2">
+        <v>3000</v>
+      </c>
+      <c r="J52" s="2">
+        <v>500</v>
+      </c>
+      <c r="K52" s="2">
+        <v>12</v>
+      </c>
+      <c r="L52" s="2">
+        <v>3500</v>
+      </c>
+      <c r="M52" s="2">
+        <v>1400</v>
+      </c>
+      <c r="N52" s="2">
+        <v>100</v>
+      </c>
+      <c r="O52" s="2">
+        <v>34</v>
+      </c>
+      <c r="P52" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q52">
+        <v>15</v>
+      </c>
+      <c r="R52">
+        <v>3</v>
+      </c>
+      <c r="S52">
+        <v>15</v>
+      </c>
+      <c r="T52">
+        <v>117</v>
+      </c>
+      <c r="U52">
+        <v>1.25</v>
+      </c>
+      <c r="V52">
+        <v>0.88</v>
+      </c>
+      <c r="W52">
+        <v>0.75</v>
+      </c>
+      <c r="X52" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="Y52" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="Z52">
+        <v>0.73</v>
+      </c>
+      <c r="AA52">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="A53" t="s">
+        <v>121</v>
+      </c>
+      <c r="B53" t="s">
+        <v>47</v>
+      </c>
+      <c r="C53">
+        <v>15</v>
+      </c>
+      <c r="D53">
+        <v>45</v>
+      </c>
+      <c r="E53">
+        <v>30</v>
+      </c>
+      <c r="F53">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="G53">
+        <v>4.5</v>
+      </c>
+      <c r="H53" s="2">
+        <v>1050</v>
+      </c>
+      <c r="I53" s="2">
+        <v>800</v>
+      </c>
+      <c r="J53" s="2">
+        <v>200</v>
+      </c>
+      <c r="K53" s="2">
+        <v>15</v>
+      </c>
+      <c r="L53" s="2">
+        <v>810</v>
+      </c>
+      <c r="M53" s="2">
+        <v>330</v>
+      </c>
+      <c r="N53" s="2">
+        <v>35</v>
+      </c>
+      <c r="O53" s="2">
+        <v>17</v>
+      </c>
+      <c r="P53" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q53" s="2">
+        <v>15</v>
+      </c>
+      <c r="R53" s="2">
+        <v>2.6</v>
+      </c>
+      <c r="S53" s="2">
+        <v>15</v>
+      </c>
+      <c r="T53" s="2">
+        <v>40</v>
+      </c>
+      <c r="U53" s="2">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="V53" s="2">
+        <v>5.6</v>
+      </c>
+      <c r="W53" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="X53" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="Y53" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="Z53" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="AA53" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="A54" t="s">
+        <v>122</v>
+      </c>
+      <c r="B54" t="s">
+        <v>47</v>
+      </c>
+      <c r="C54">
+        <v>15</v>
+      </c>
+      <c r="D54">
+        <v>45</v>
+      </c>
+      <c r="E54">
+        <v>30</v>
+      </c>
+      <c r="F54">
+        <v>2.8</v>
+      </c>
+      <c r="G54">
+        <v>10</v>
+      </c>
+      <c r="H54" s="2">
+        <v>1400</v>
+      </c>
+      <c r="I54" s="2">
+        <v>1200</v>
+      </c>
+      <c r="J54" s="2">
+        <v>180</v>
+      </c>
+      <c r="K54" s="2">
+        <v>15</v>
+      </c>
+      <c r="L54" s="2">
+        <v>1270</v>
+      </c>
+      <c r="M54" s="2">
+        <v>380</v>
+      </c>
+      <c r="N54" s="2">
+        <v>30</v>
+      </c>
+      <c r="O54" s="2">
+        <v>22</v>
+      </c>
+      <c r="P54" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q54" s="2">
+        <v>15</v>
+      </c>
+      <c r="R54" s="2">
+        <v>3.2</v>
+      </c>
+      <c r="S54" s="2">
+        <v>15</v>
+      </c>
+      <c r="T54" s="2">
+        <v>100</v>
+      </c>
+      <c r="U54" s="2">
+        <v>4.2</v>
+      </c>
+      <c r="V54" s="2">
+        <v>2.7</v>
+      </c>
+      <c r="W54" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="X54" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="Y54" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="Z54" s="3">
+        <v>0.7</v>
+      </c>
+      <c r="AA54" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="A55" t="s">
+        <v>123</v>
+      </c>
+      <c r="B55" t="s">
+        <v>47</v>
+      </c>
+      <c r="C55">
+        <v>15</v>
+      </c>
+      <c r="D55">
+        <v>45</v>
+      </c>
+      <c r="E55">
+        <v>30</v>
+      </c>
+      <c r="F55">
+        <v>6.8</v>
+      </c>
+      <c r="G55">
+        <v>4.5</v>
+      </c>
+      <c r="H55" s="2">
+        <v>2500</v>
+      </c>
+      <c r="I55" s="2">
+        <v>2400</v>
+      </c>
+      <c r="J55" s="2">
         <v>300</v>
       </c>
-      <c r="O51" s="2">
-        <v>48</v>
-      </c>
-      <c r="P51" s="2">
-        <v>40</v>
-      </c>
-      <c r="Q51" s="2">
-        <v>20</v>
-      </c>
-      <c r="R51" s="6">
-        <v>16</v>
-      </c>
-      <c r="S51" s="2">
-        <v>20</v>
-      </c>
-      <c r="T51" s="11">
-        <v>100</v>
-      </c>
-      <c r="U51" s="6">
-        <v>7</v>
-      </c>
-      <c r="V51" s="6">
-        <v>1.86</v>
-      </c>
-      <c r="W51" s="3">
+      <c r="K55" s="2">
+        <v>15</v>
+      </c>
+      <c r="L55" s="2">
+        <v>2400</v>
+      </c>
+      <c r="M55" s="2">
+        <v>900</v>
+      </c>
+      <c r="N55" s="2">
+        <v>38</v>
+      </c>
+      <c r="O55" s="2">
+        <v>15</v>
+      </c>
+      <c r="P55" s="2">
+        <v>10</v>
+      </c>
+      <c r="Q55" s="2">
+        <v>15</v>
+      </c>
+      <c r="R55" s="2">
+        <v>3.4</v>
+      </c>
+      <c r="S55" s="2">
+        <v>15</v>
+      </c>
+      <c r="T55" s="2">
+        <v>90</v>
+      </c>
+      <c r="U55" s="2">
+        <v>2.7</v>
+      </c>
+      <c r="V55" s="2">
         <v>1.7</v>
       </c>
-      <c r="X51" s="6">
-        <v>1</v>
-      </c>
-      <c r="Y51" s="6">
-        <v>1</v>
-      </c>
-      <c r="Z51" s="3">
-        <v>0.83</v>
-      </c>
-      <c r="AA51" s="2">
-        <v>50</v>
+      <c r="W55" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="X55" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="Y55" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="Z55" s="3">
+        <v>0.77</v>
+      </c>
+      <c r="AA55" s="6">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:AA51" xr:uid="{E69B3F4A-D7AE-43B6-8CEC-20724C077B7B}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:AA51">
-      <sortCondition ref="B4:B51"/>
+  <autoFilter ref="A4:AA55" xr:uid="{E69B3F4A-D7AE-43B6-8CEC-20724C077B7B}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="PPAK5x6"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="4">
+      <filters>
+        <filter val="30"/>
+        <filter val="40"/>
+      </filters>
+    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A8:AA52">
+      <sortCondition ref="F4:F52"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
